--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -219,7 +219,7 @@
     <t xml:space="preserve">작성일</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-05</t>
+    <t xml:space="preserve">2026-10-06</t>
   </si>
   <si>
     <t xml:space="preserve">기준</t>
@@ -242,7 +242,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8d87234 — </t>
+      <t xml:space="preserve">8ba23bd — </t>
     </r>
     <r>
       <rPr>
@@ -574,6 +574,44 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">) + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원 모바일 웹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개발 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">) + REST API. </t>
     </r>
     <r>
@@ -583,7 +621,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">회원 앱은 범위 제외</t>
+      <t xml:space="preserve">대상 지점은 수도권 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">83</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">곳</t>
     </r>
     <r>
       <rPr>
@@ -602,7 +659,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">회원 기능은 </t>
+      <t xml:space="preserve">지방 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">곳 제외</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원 기능 </t>
     </r>
     <r>
       <rPr>
@@ -621,36 +716,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">로 구현</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원 계정으로 관리자 웹에서 사용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">는 구현 완료</t>
     </r>
   </si>
   <si>
@@ -6306,7 +6372,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">오프라인 회원 ↔ 앱 계정 연동</t>
+      <t xml:space="preserve">오프라인 회원 ↔ 온라인 계정 연동</t>
     </r>
     <r>
       <rPr>
@@ -6363,7 +6429,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">회원 앱 범위 제외로 화면 없음</t>
+      <t xml:space="preserve">회원 모바일 웹에서 화면 개발 예정</t>
     </r>
   </si>
   <si>
@@ -6380,7 +6446,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">회원 앱 자체 가입</t>
+      <t xml:space="preserve">회원 자체 가입</t>
     </r>
     <r>
       <rPr>
@@ -6418,7 +6484,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">회원 앱 범위 제외로 화면 없음</t>
+      <t xml:space="preserve">회원 모바일 웹에서 화면 개발 예정</t>
     </r>
   </si>
   <si>
@@ -16161,7 +16227,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8d87234)</t>
+      <t xml:space="preserve">8ba23bd)</t>
     </r>
   </si>
   <si>
@@ -17267,7 +17333,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8d87234)</t>
+      <t xml:space="preserve">8ba23bd)</t>
     </r>
   </si>
   <si>
@@ -18246,7 +18312,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8d87234)</t>
+      <t xml:space="preserve">8ba23bd)</t>
     </r>
   </si>
   <si>
@@ -18900,7 +18966,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8d87234)</t>
+      <t xml:space="preserve">8ba23bd)</t>
     </r>
   </si>
   <si>
@@ -19293,7 +19359,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8d87234)</t>
+      <t xml:space="preserve">8ba23bd)</t>
     </r>
   </si>
   <si>
@@ -19658,7 +19724,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">회원 앱 범위 제외</t>
+      <t xml:space="preserve">회원 모바일 웹 예정</t>
     </r>
     <r>
       <rPr>
@@ -19920,7 +19986,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8d87234)</t>
+      <t xml:space="preserve">8ba23bd)</t>
     </r>
   </si>
   <si>
@@ -20701,7 +20767,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8d87234)</t>
+      <t xml:space="preserve">8ba23bd)</t>
     </r>
   </si>
   <si>
@@ -21275,7 +21341,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8d87234)</t>
+      <t xml:space="preserve">8ba23bd)</t>
     </r>
   </si>
   <si>
@@ -21720,7 +21786,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8d87234)</t>
+      <t xml:space="preserve">8ba23bd)</t>
     </r>
   </si>
   <si>
@@ -22998,7 +23064,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">회원 앱 가입</t>
+      <t xml:space="preserve">회원 가입</t>
     </r>
     <r>
       <rPr>
@@ -23017,7 +23083,88 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">연동은 회원 앱 범위 제외에 따른 것이다</t>
+      <t xml:space="preserve">연동 화면은 회원 모바일 웹에서 만든다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(D40).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">설계는 있지만 미구현인 도메인 규칙</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점 계약이 종료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(TERMINATED)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">되면 그 지점에 파견 중인 직원의 파견을 종료하고 재배치 대상에 올리는 처리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(architecture/entities.md §2-1). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지금은 신규 활동 차단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(409)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 동작한다</t>
     </r>
     <r>
       <rPr>
@@ -23031,74 +23178,1337 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">설계는 있지만 미구현인 도메인 규칙</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점 계약이 종료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(TERMINATED)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">되면 그 지점에 파견 중인 직원의 파견을 종료하고 재배치 대상에 올리는 처리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(architecture/entities.md §2-1). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지금은 신규 활동 차단</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(409)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만 동작한다</t>
+    <t xml:space="preserve">범위 제외 — 의도적으로 만들지 않은 것</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원천</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요구사항추적표 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">§2-4, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">각 도메인 문서 부록 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A-8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 제외 항목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">향후 확장</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">권한관리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">범용 계정 발급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목록 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로그인 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회 잠금</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">필드 추가 수준으로 가능</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">03 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">근태관리</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">자동 결근 배치</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조회 시점 계산 또는 스케줄러 도입 시</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">04 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">게시판</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">읽음 확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상단 고정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">가능</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예약및결제</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강사 정산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원천징수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(commissionRate </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·UI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">도 코드에서 제거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노쇼 자동처리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분 결제 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TTL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정산 필요 시 모델 복원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">나머지는 스케줄러 도입 시</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프로그램게시</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시설 충돌 검사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">휴강 예약자 알림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상태 자동 전이 배치</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스케줄러 도입 시</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">08 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">혼잡도관리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">QR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">체크인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아웃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분 자동계산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미체크아웃 마감</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 이용자 목록</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">회원 모바일 웹 착수 후 체크인 데이터 위에 확장</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자원문서관리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">감가상각 배치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(bookValue), STAFF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본인 인사서류 조회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">코드에서 제거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실무 확장 목록 전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(reference/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기업구조및관리시스템분석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.md §7)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">소유 구분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이관</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점검 이력 등은 가치가 커서 우선 후보</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1E3A5F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대상 지점</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1E3A5F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1E3A5F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원 앱 형태</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대상 지점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원 앱 형태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-06, D40): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점은 수도권 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">83</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">곳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인천</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 대상으로 하고 지방 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">곳은 뺀다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. 98</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">곳 전체면 회원 기능까지 열었을 때 하루 요청이 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 건으로 엣지 무료 한도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 넘고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 83</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">곳이면 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 건이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(design-constants ⑬, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점당 하루 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 가정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원 기능은 네이티브 앱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(apps/member-app, React Native)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 아니라 모바일 웹으로 만든다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개발 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">관리자 웹과 같은 스택</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Worker</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라 인프라를 더 붙이지 않는다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. RFP 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">번의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모바일결제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 모바일 웹의 모의 결제로 대응한다</t>
     </r>
     <r>
       <rPr>
@@ -23109,1415 +24519,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 제외 — 의도적으로 만들지 않은 것</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원천</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요구사항추적표 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">§2-4, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">각 도메인 문서 부록 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A-8</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 제외 항목</t>
-  </si>
-  <si>
-    <t xml:space="preserve">향후 확장</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">01 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">권한관리</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">범용 계정 발급</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">목록 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">API, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로그인 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회 잠금</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">필드 추가 수준으로 가능</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">03 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">근태관리</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">자동 결근 배치</t>
-  </si>
-  <si>
-    <t xml:space="preserve">조회 시점 계산 또는 스케줄러 도입 시</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">04 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">게시판</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">읽음 확인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상단 고정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">가능</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예약및결제</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">강사 정산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원천징수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(commissionRate </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">필드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·UI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">도 코드에서 제거</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">노쇼 자동처리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분 결제 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TTL</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정산 필요 시 모델 복원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">나머지는 스케줄러 도입 시</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">07 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">강사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">프로그램게시</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시설 충돌 검사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">휴강 예약자 알림</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상태 자동 전이 배치</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알림</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">스케줄러 도입 시</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">08 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">혼잡도관리</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">QR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">체크인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아웃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분 자동계산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미체크아웃 마감</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현재 이용자 목록</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">회원 앱 착수 후 체크인 데이터 위에 확장</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자원문서관리</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">감가상각 배치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(bookValue), STAFF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">본인 인사서류 조회</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">코드에서 제거</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실무 확장 목록 전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(reference/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기업구조및관리시스템분석</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.md §7)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">소유 구분</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이관</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점검 이력 등은 가치가 커서 우선 후보</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">회원 앱</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원 앱 전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(2026-09-30 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">추가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 2-1 D37): apps/member-app(React Native)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 개발 범위에서 뺀다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">웹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(admin-web)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 집중한다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(MEMBER) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">역할의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">API</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 이미 있으므로 그대로 둔다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가입</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예약</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">게시판 조회 — 테스트가 계속 본다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다만 회원이 직접 쓰는 화면은 만들지 않는다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. RFP 6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">번의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모바일결제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 모의결제 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">API</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">까지만 있는 상태로 남는다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원 앱을 다시 넣게 되면 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D37 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결정 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">무료 요청 한도 초과 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Workers </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">유료 전환</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">와 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이전 조건을 먼저 다시 본다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보류 이유</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원 앱을 받으면 하루 요청이 약 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">19.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만 건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">계산값</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">으로 엣지 무료 한도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만 건을 넘는다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">유료 전환이나 인프라를 더 구성해 연결해야 해 개발 범위가 과하게 넓어지므로 보류했다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(D37 §5, log/057).</t>
     </r>
   </si>
 </sst>
@@ -27169,7 +27170,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
         <v>860</v>
       </c>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -242,7 +242,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8ba23bd — </t>
+      <t xml:space="preserve">8fce286 — </t>
     </r>
     <r>
       <rPr>
@@ -16227,7 +16227,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8ba23bd)</t>
+      <t xml:space="preserve">8fce286)</t>
     </r>
   </si>
   <si>
@@ -17333,7 +17333,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8ba23bd)</t>
+      <t xml:space="preserve">8fce286)</t>
     </r>
   </si>
   <si>
@@ -18312,7 +18312,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8ba23bd)</t>
+      <t xml:space="preserve">8fce286)</t>
     </r>
   </si>
   <si>
@@ -18966,7 +18966,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8ba23bd)</t>
+      <t xml:space="preserve">8fce286)</t>
     </r>
   </si>
   <si>
@@ -19359,7 +19359,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8ba23bd)</t>
+      <t xml:space="preserve">8fce286)</t>
     </r>
   </si>
   <si>
@@ -19986,7 +19986,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8ba23bd)</t>
+      <t xml:space="preserve">8fce286)</t>
     </r>
   </si>
   <si>
@@ -20767,7 +20767,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8ba23bd)</t>
+      <t xml:space="preserve">8fce286)</t>
     </r>
   </si>
   <si>
@@ -21341,7 +21341,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8ba23bd)</t>
+      <t xml:space="preserve">8fce286)</t>
     </r>
   </si>
   <si>
@@ -21786,7 +21786,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8ba23bd)</t>
+      <t xml:space="preserve">8fce286)</t>
     </r>
   </si>
   <si>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -242,7 +242,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8fce286 — </t>
+      <t xml:space="preserve">b4f9e1e — </t>
     </r>
     <r>
       <rPr>
@@ -16227,7 +16227,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8fce286)</t>
+      <t xml:space="preserve">b4f9e1e)</t>
     </r>
   </si>
   <si>
@@ -17333,7 +17333,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8fce286)</t>
+      <t xml:space="preserve">b4f9e1e)</t>
     </r>
   </si>
   <si>
@@ -18312,7 +18312,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8fce286)</t>
+      <t xml:space="preserve">b4f9e1e)</t>
     </r>
   </si>
   <si>
@@ -18966,7 +18966,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8fce286)</t>
+      <t xml:space="preserve">b4f9e1e)</t>
     </r>
   </si>
   <si>
@@ -19359,7 +19359,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8fce286)</t>
+      <t xml:space="preserve">b4f9e1e)</t>
     </r>
   </si>
   <si>
@@ -19986,7 +19986,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8fce286)</t>
+      <t xml:space="preserve">b4f9e1e)</t>
     </r>
   </si>
   <si>
@@ -20767,7 +20767,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8fce286)</t>
+      <t xml:space="preserve">b4f9e1e)</t>
     </r>
   </si>
   <si>
@@ -21341,7 +21341,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8fce286)</t>
+      <t xml:space="preserve">b4f9e1e)</t>
     </r>
   </si>
   <si>
@@ -21786,7 +21786,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8fce286)</t>
+      <t xml:space="preserve">b4f9e1e)</t>
     </r>
   </si>
   <si>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2369" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="864">
   <si>
     <r>
       <rPr>
@@ -242,7 +242,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">b4f9e1e — </t>
+      <t xml:space="preserve">02f7e1d — </t>
     </r>
     <r>
       <rPr>
@@ -484,7 +484,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">26</t>
+      <t xml:space="preserve">27</t>
     </r>
     <r>
       <rPr>
@@ -2283,7 +2283,7 @@
     <t xml:space="preserve">구현</t>
   </si>
   <si>
-    <t xml:space="preserve">auth-lifecycle·hr-authority·contract-termination·branch-isolation spec</t>
+    <t xml:space="preserve">auth-lifecycle·auth-refresh-token·hr-authority·contract-termination·branch-isolation spec</t>
   </si>
   <si>
     <t xml:space="preserve">AUTH-INV-02</t>
@@ -16227,7 +16227,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">b4f9e1e)</t>
+      <t xml:space="preserve">02f7e1d)</t>
     </r>
   </si>
   <si>
@@ -17123,6 +17123,49 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">ADR-AUTH-04</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Refresh Token </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">발급 시 그 계정의 만료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">폐기 토큰 정리</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -17333,7 +17376,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">b4f9e1e)</t>
+      <t xml:space="preserve">02f7e1d)</t>
     </r>
   </si>
   <si>
@@ -18312,7 +18355,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">b4f9e1e)</t>
+      <t xml:space="preserve">02f7e1d)</t>
     </r>
   </si>
   <si>
@@ -18966,7 +19009,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">b4f9e1e)</t>
+      <t xml:space="preserve">02f7e1d)</t>
     </r>
   </si>
   <si>
@@ -19359,7 +19402,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">b4f9e1e)</t>
+      <t xml:space="preserve">02f7e1d)</t>
     </r>
   </si>
   <si>
@@ -19986,7 +20029,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">b4f9e1e)</t>
+      <t xml:space="preserve">02f7e1d)</t>
     </r>
   </si>
   <si>
@@ -20767,7 +20810,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">b4f9e1e)</t>
+      <t xml:space="preserve">02f7e1d)</t>
     </r>
   </si>
   <si>
@@ -21341,7 +21384,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">b4f9e1e)</t>
+      <t xml:space="preserve">02f7e1d)</t>
     </r>
   </si>
   <si>
@@ -21786,7 +21829,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">b4f9e1e)</t>
+      <t xml:space="preserve">02f7e1d)</t>
     </r>
   </si>
   <si>
@@ -25331,12 +25374,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25349,7 +25392,7 @@
         <v>596</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
@@ -25361,7 +25404,7 @@
         <v>596</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -25373,7 +25416,7 @@
         <v>596</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -25536,7 +25579,7 @@
         <v>619</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>621</v>
@@ -25556,10 +25599,10 @@
         <v>613</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>616</v>
@@ -25573,13 +25616,13 @@
         <v>337</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>616</v>
@@ -25596,10 +25639,10 @@
         <v>622</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>616</v>
@@ -25616,7 +25659,7 @@
         <v>619</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>621</v>
@@ -25636,10 +25679,10 @@
         <v>613</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>616</v>
@@ -25656,10 +25699,10 @@
         <v>622</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F29" s="14" t="s">
         <v>616</v>
@@ -25676,7 +25719,7 @@
         <v>619</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>621</v>
@@ -25696,10 +25739,10 @@
         <v>613</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F31" s="14" t="s">
         <v>616</v>
@@ -25713,13 +25756,13 @@
         <v>358</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F32" s="14" t="s">
         <v>616</v>
@@ -25736,10 +25779,10 @@
         <v>622</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F33" s="14" t="s">
         <v>616</v>
@@ -25756,10 +25799,10 @@
         <v>619</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F34" s="14" t="s">
         <v>616</v>
@@ -25786,10 +25829,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -25800,10 +25843,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -25814,26 +25857,26 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="14" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="22" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
@@ -25885,12 +25928,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25903,7 +25946,7 @@
         <v>596</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
@@ -25915,7 +25958,7 @@
         <v>596</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -25927,7 +25970,7 @@
         <v>596</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -26104,7 +26147,7 @@
         <v>619</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>621</v>
@@ -26124,10 +26167,10 @@
         <v>613</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>616</v>
@@ -26144,10 +26187,10 @@
         <v>622</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>616</v>
@@ -26164,10 +26207,10 @@
         <v>613</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F27" s="14" t="s">
         <v>616</v>
@@ -26194,10 +26237,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -26208,10 +26251,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -26222,10 +26265,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -26236,12 +26279,12 @@
     </row>
     <row r="35" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
@@ -26294,12 +26337,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26312,7 +26355,7 @@
         <v>596</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
@@ -26324,7 +26367,7 @@
         <v>596</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -26336,7 +26379,7 @@
         <v>596</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -26348,7 +26391,7 @@
         <v>596</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
@@ -26360,7 +26403,7 @@
         <v>596</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
@@ -26593,10 +26636,10 @@
         <v>619</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F30" s="14" t="s">
         <v>616</v>
@@ -26613,10 +26656,10 @@
         <v>613</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F31" s="14" t="s">
         <v>616</v>
@@ -26633,10 +26676,10 @@
         <v>622</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F32" s="21" t="s">
         <v>624</v>
@@ -26653,10 +26696,10 @@
         <v>622</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F33" s="14" t="s">
         <v>616</v>
@@ -26673,10 +26716,10 @@
         <v>619</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F34" s="14" t="s">
         <v>616</v>
@@ -26693,10 +26736,10 @@
         <v>613</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F35" s="14" t="s">
         <v>616</v>
@@ -26710,10 +26753,10 @@
         <v>433</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>627</v>
@@ -26733,10 +26776,10 @@
         <v>619</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F37" s="14" t="s">
         <v>616</v>
@@ -26753,7 +26796,7 @@
         <v>619</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>627</v>
@@ -26783,10 +26826,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -26797,10 +26840,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -26811,10 +26854,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -26872,26 +26915,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>49</v>
@@ -26905,10 +26948,10 @@
         <v>452</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>30</v>
@@ -26922,10 +26965,10 @@
         <v>455</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>30</v>
@@ -26939,10 +26982,10 @@
         <v>458</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>30</v>
@@ -26956,10 +26999,10 @@
         <v>461</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>30</v>
@@ -26973,10 +27016,10 @@
         <v>464</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>30</v>
@@ -26990,10 +27033,10 @@
         <v>467</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>30</v>
@@ -27007,10 +27050,10 @@
         <v>470</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>30</v>
@@ -27018,12 +27061,12 @@
     </row>
     <row r="13" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -27032,12 +27075,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -27074,12 +27117,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27087,97 +27130,97 @@
         <v>46</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -31342,7 +31385,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -31844,23 +31887,37 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="22" t="s">
+      <c r="B43" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="22" t="s">
+        <v>642</v>
+      </c>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B7:F7"/>
@@ -31880,7 +31937,8 @@
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="B42:E42"/>
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="A46:F46"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -31910,12 +31968,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31928,7 +31986,7 @@
         <v>596</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
@@ -31940,7 +31998,7 @@
         <v>596</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -31952,7 +32010,7 @@
         <v>596</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -31964,7 +32022,7 @@
         <v>596</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
@@ -31976,7 +32034,7 @@
         <v>596</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
@@ -31988,7 +32046,7 @@
         <v>596</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
@@ -32179,10 +32237,10 @@
         <v>619</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>616</v>
@@ -32199,7 +32257,7 @@
         <v>613</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>627</v>
@@ -32219,10 +32277,10 @@
         <v>619</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F30" s="14" t="s">
         <v>616</v>
@@ -32239,10 +32297,10 @@
         <v>622</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F31" s="21" t="s">
         <v>624</v>
@@ -32259,10 +32317,10 @@
         <v>619</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F32" s="21" t="s">
         <v>624</v>
@@ -32279,7 +32337,7 @@
         <v>613</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>627</v>
@@ -32299,10 +32357,10 @@
         <v>622</v>
       </c>
       <c r="D34" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>655</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>653</v>
       </c>
       <c r="F34" s="21" t="s">
         <v>624</v>
@@ -32319,7 +32377,7 @@
         <v>619</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>621</v>
@@ -32349,68 +32407,68 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="14" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="14" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="14" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="14" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="22" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B45" s="22"/>
       <c r="C45" s="22"/>
@@ -32468,12 +32526,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32486,7 +32544,7 @@
         <v>596</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
@@ -32498,7 +32556,7 @@
         <v>596</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -32510,7 +32568,7 @@
         <v>596</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -32522,7 +32580,7 @@
         <v>596</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
@@ -32713,10 +32771,10 @@
         <v>619</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>616</v>
@@ -32733,10 +32791,10 @@
         <v>613</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F27" s="21" t="s">
         <v>624</v>
@@ -32753,10 +32811,10 @@
         <v>619</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F28" s="21" t="s">
         <v>624</v>
@@ -32773,10 +32831,10 @@
         <v>613</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F29" s="14" t="s">
         <v>616</v>
@@ -32793,10 +32851,10 @@
         <v>613</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F30" s="14" t="s">
         <v>616</v>
@@ -32813,10 +32871,10 @@
         <v>619</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F31" s="14" t="s">
         <v>616</v>
@@ -32833,10 +32891,10 @@
         <v>619</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F32" s="14" t="s">
         <v>616</v>
@@ -32853,10 +32911,10 @@
         <v>613</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F33" s="14" t="s">
         <v>616</v>
@@ -32873,10 +32931,10 @@
         <v>622</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F34" s="14" t="s">
         <v>616</v>
@@ -32893,10 +32951,10 @@
         <v>622</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F35" s="14" t="s">
         <v>616</v>
@@ -32913,10 +32971,10 @@
         <v>619</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F36" s="14" t="s">
         <v>616</v>
@@ -32933,10 +32991,10 @@
         <v>619</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F37" s="14" t="s">
         <v>616</v>
@@ -32953,10 +33011,10 @@
         <v>613</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F38" s="14" t="s">
         <v>616</v>
@@ -32983,10 +33041,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -32997,10 +33055,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -33011,10 +33069,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -33025,12 +33083,12 @@
     </row>
     <row r="46" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="22" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
@@ -33085,12 +33143,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33103,7 +33161,7 @@
         <v>596</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
@@ -33115,7 +33173,7 @@
         <v>596</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -33127,7 +33185,7 @@
         <v>596</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -33304,7 +33362,7 @@
         <v>619</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>621</v>
@@ -33324,7 +33382,7 @@
         <v>613</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>621</v>
@@ -33341,10 +33399,10 @@
         <v>220</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>621</v>
@@ -33364,7 +33422,7 @@
         <v>619</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>621</v>
@@ -33384,7 +33442,7 @@
         <v>622</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>621</v>
@@ -33414,10 +33472,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -33428,10 +33486,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -33442,12 +33500,12 @@
     </row>
     <row r="35" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -33499,12 +33557,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33517,7 +33575,7 @@
         <v>596</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
@@ -33529,7 +33587,7 @@
         <v>596</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -33541,7 +33599,7 @@
         <v>596</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -33553,7 +33611,7 @@
         <v>596</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
@@ -33758,10 +33816,10 @@
         <v>619</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F27" s="14" t="s">
         <v>616</v>
@@ -33778,10 +33836,10 @@
         <v>613</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>616</v>
@@ -33798,10 +33856,10 @@
         <v>619</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="F29" s="14" t="s">
         <v>616</v>
@@ -33818,10 +33876,10 @@
         <v>622</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="F30" s="14" t="s">
         <v>616</v>
@@ -33838,10 +33896,10 @@
         <v>619</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="F31" s="14" t="s">
         <v>616</v>
@@ -33858,10 +33916,10 @@
         <v>613</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F32" s="14" t="s">
         <v>616</v>
@@ -33878,10 +33936,10 @@
         <v>619</v>
       </c>
       <c r="D33" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>718</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>716</v>
       </c>
       <c r="F33" s="14" t="s">
         <v>616</v>
@@ -33898,10 +33956,10 @@
         <v>613</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F34" s="14" t="s">
         <v>616</v>
@@ -33918,10 +33976,10 @@
         <v>613</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F35" s="14" t="s">
         <v>616</v>
@@ -33938,10 +33996,10 @@
         <v>622</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F36" s="14" t="s">
         <v>616</v>
@@ -33958,13 +34016,13 @@
         <v>613</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>615</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33978,13 +34036,13 @@
         <v>613</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>615</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34008,10 +34066,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -34022,24 +34080,24 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="14" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -34050,12 +34108,12 @@
     </row>
     <row r="46" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="22" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
@@ -34111,12 +34169,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34129,7 +34187,7 @@
         <v>596</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
@@ -34141,7 +34199,7 @@
         <v>596</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -34153,7 +34211,7 @@
         <v>596</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -34165,7 +34223,7 @@
         <v>596</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
@@ -34177,7 +34235,7 @@
         <v>596</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
@@ -34396,10 +34454,10 @@
         <v>619</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F29" s="14" t="s">
         <v>616</v>
@@ -34416,10 +34474,10 @@
         <v>613</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="F30" s="14" t="s">
         <v>616</v>
@@ -34436,10 +34494,10 @@
         <v>622</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="F31" s="14" t="s">
         <v>616</v>
@@ -34456,10 +34514,10 @@
         <v>622</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F32" s="14" t="s">
         <v>616</v>
@@ -34476,10 +34534,10 @@
         <v>619</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="F33" s="14" t="s">
         <v>616</v>
@@ -34496,10 +34554,10 @@
         <v>613</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="F34" s="14" t="s">
         <v>616</v>
@@ -34526,54 +34584,54 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="14" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="14" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="15" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="22" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -229,20 +229,49 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">저장소 커밋 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">02f7e1d — </t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(dev </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">브랜치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) — </t>
     </r>
     <r>
       <rPr>
@@ -484,7 +513,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">27</t>
+      <t xml:space="preserve">28</t>
     </r>
     <r>
       <rPr>
@@ -12731,7 +12760,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">계측 장비 없음 → 체크인 데이터 자동계산 </t>
+      <t xml:space="preserve">계측 장비 없음 → 관리자 수동 입력 </t>
     </r>
     <r>
       <rPr>
@@ -12750,45 +12779,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">관리자 수동보정 하이브리드로 대체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분 주기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원본의 </t>
+      <t xml:space="preserve">정원 기준 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계 자동 판정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 즉시 반영이라 원본의 </t>
     </r>
     <r>
       <rPr>
@@ -12807,21 +12836,87 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">분 요건 상회</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">D10</t>
+      <t xml:space="preserve">분 요건 충족</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). D10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 계획한 체크인 기반 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분 주기 자동계산은 범위 제외</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(§2-4)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D10, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">혼잡도관리 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A-8</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">10</t>
@@ -16208,7 +16303,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">(2026-10-06 </t>
     </r>
     <r>
       <rPr>
@@ -16217,7 +16312,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">커밋 </t>
+      <t xml:space="preserve">저장소 기준</t>
     </r>
     <r>
       <rPr>
@@ -16227,7 +16322,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">02f7e1d)</t>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -17357,16 +17452,938 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">(2026-10-06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장소 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본사 관리자로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">신규 채용한 직원을 특정 지점에 배치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최초 파견</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본사 관리자로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직원을 다른 지점으로 재배치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파견 전환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하고 그 이력을 남기고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점 관리자로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 우리 지점에 파견된 직원들의 직급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연락처 등 일상적인 인사정보를 관리하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본사 관리자로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전 지점 직원 현황을 하나의 화면에서 조회하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원본 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한 화면 조회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직원으로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내 인적사항 변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연락처 등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">을 신청하면 관리자 승인 후 반영되길 원한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점 관리자로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">퇴사 처리 시 퇴사일을 기록하고 계정을 자동으로 비활성화하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">/staff</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">/staff/:id</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">지점</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/staff/:id/assignments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/staff/:id/resign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/staff/me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-STF-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">퇴사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파견 발령은 단일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트랜잭션</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(D30)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-STF-02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">staffCode </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">채번 — 시퀀스 테이블 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">행 락</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(allocateBranchCode)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(D28·D30)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-STF-03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">활성 파견 유일성 — 부분 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">unique </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인덱스</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(D27)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-STF-04</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파견 발령 시 담당 회원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강사 프로필 해제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 트랜잭션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(D30, DI-02)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">변경 신청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">승인 워크플로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파견 이력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UI, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연락처 마스킹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, offDays </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력 화면</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">근태관리 — 요구사항</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color rgb="FF4B5563"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">커밋 </t>
+      <t xml:space="preserve">원천</t>
     </r>
     <r>
       <rPr>
@@ -17376,7 +18393,718 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">02f7e1d)</t>
+      <t xml:space="preserve">: docs/domains/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">근태관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.md · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기능 명세는 코드 실측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장소 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직원으로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출근</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">퇴근 시 앱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">또는 웹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에서 버튼 하나로 체크인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아웃하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직원으로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연차를 신청하면 지점 관리자가 승인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">반려할 수 있길 원한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점 관리자로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">우리 지점 직원들의 이번 달 근태 현황</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지각</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결근</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">휴가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">을 한눈에 보고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직원으로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">오늘 업무일지를 작성해 관리자와 공유하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">/attendance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/attendance/absence-confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/attendance/absence-preview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/attendance/check-in</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">/attendance/check-out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/attendance/summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/leave-requests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/leave-requests/:id/approve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/leave-requests/:id/reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/leave-balance/:staffId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/work-logs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-ATT-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연차 차감은 승인 시점에만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">반려 복구 로직 불필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-ATT-02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결근은 관리자의 명시적 확정 액션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배치 아님</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-ATT-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근태 기록 지점 귀속 — 그 날짜의 파견 지점 스냅샷</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">근태 정정 이력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(AuditLog). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업무일지 하루 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">unique </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대신 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">advisory lock(D33) — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제약 추가는 승인 대기</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">게시판 — 요구사항</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원천</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/domains/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">게시판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.md · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기능 명세는 코드 실측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장소 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -17406,7 +19134,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">신규 채용한 직원을 특정 지점에 배치</t>
+      <t xml:space="preserve">전 지점</t>
     </r>
     <r>
       <rPr>
@@ -17425,7 +19153,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">최초 파견</t>
+      <t xml:space="preserve">또는 특정 지점</t>
     </r>
     <r>
       <rPr>
@@ -17444,7 +19172,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">하고 싶다</t>
+      <t xml:space="preserve">에 공지를 올리고 필요시 교육자료 파일을 첨부하고 싶다</t>
     </r>
     <r>
       <rPr>
@@ -17465,7 +19193,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">본사 관리자로서</t>
+      <t xml:space="preserve">지점 관리자로서</t>
     </r>
     <r>
       <rPr>
@@ -17484,7 +19212,104 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">직원을 다른 지점으로 재배치</t>
+      <t xml:space="preserve">본사 공지를 확인하고 우리 지점 회원들에게 전달할 공지를 따로 작성하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원으로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내가 다니는 지점의 공지사항을 앱에서 확인하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">/posts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/posts/:id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-BRD-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원 대상 공지 가시성 필터 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">visibleToMember</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-BRD-02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목록 페이지네이션</t>
     </r>
     <r>
       <rPr>
@@ -17503,26 +19328,206 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">파견 전환</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
+      <t xml:space="preserve">기본 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">limit 20)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">첨부파일 업로드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, pinned·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">읽음 확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">범위 제외</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), category </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필터 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UI, TrainingLog</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">회원관리 — 요구사항</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원천</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/domains/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.md · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기능 명세는 코드 실측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장소 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">하고 그 이력을 남기고 싶다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원으로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">앱에서 회원가입 후 내가 다니는 지점을 선택하고 이용을 시작하고 싶다</t>
     </r>
     <r>
       <rPr>
@@ -17562,7 +19567,85 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">현재 우리 지점에 파견된 직원들의 직급</t>
+      <t xml:space="preserve">신규 방문 회원을 현장에서 직접 등록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">오프라인 등록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">할 수도 있어야 한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점 관리자로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원의 수강</t>
     </r>
     <r>
       <rPr>
@@ -17581,7 +19664,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">연락처 등 일상적인 인사정보를 관리하고 싶다</t>
+      <t xml:space="preserve">예약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/PT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">잔여 세션을 한 화면에서 확인하고 싶다</t>
     </r>
     <r>
       <rPr>
@@ -17602,7 +19704,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">본사 관리자로서</t>
+      <t xml:space="preserve">회원으로서</t>
     </r>
     <r>
       <rPr>
@@ -17621,7 +19723,127 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">전 지점 직원 현황을 하나의 화면에서 조회하고 싶다</t>
+      <t xml:space="preserve">내 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">잔여 세션이 몇 회 남았는지 앱에서 확인하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">/members</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/members/:id</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">/members/:id/enrollments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/members/:id/pt-sessions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/members/:id/pt-sessions/:sessionId/use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/members/:id/status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/members/link</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만</t>
     </r>
     <r>
       <rPr>
@@ -17640,45 +19862,535 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">원본 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한 화면 조회</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요건</t>
+      <t xml:space="preserve">회원 모바일 웹 예정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">/members/register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-MEM-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">오프라인↔앱 연동 — 회원번호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전화번호 동시 일치</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-MEM-02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탈퇴 회원 이메일 재사용 — 활성 계정끼리만 부분 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">unique</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-MEM-03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원 상세 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요약 카운트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탭별 지연 로드</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연동 승인 플로우</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자동 휴면 전환 배치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전화번호 마스킹 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UI</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">예약및결제 — 요구사항</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원천</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/domains/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예약및결제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.md · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기능 명세는 코드 실측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장소 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원으로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원하는 프로그램의 회차를 조회하고 예약하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원으로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유료 회차는 예약 후 모의결제로 확정하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원으로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사정이 생기면 예약을 취소하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">마감시간 전이면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">환불받고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점 관리자로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원이 현장에 도착하면 체크인 처리하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점 관리자로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">우리 지점 예약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결제 현황을 조회하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타 지점은 불가</t>
     </r>
     <r>
       <rPr>
@@ -17692,14 +20404,17 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직원으로서</t>
+    <t xml:space="preserve">/reservations</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원</t>
     </r>
     <r>
       <rPr>
@@ -17718,7 +20433,509 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">내 인적사항 변경</t>
+      <t xml:space="preserve">지점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본사</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">회원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/reservations/:id/cancel</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">/reservations/:id/check-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/payments</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">본사</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">/payments/:reservationId/mock-pay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-RSV-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정원 초과 방지 — 회차 행 락</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(lockScheduleSlot)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(D32)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-RSV-02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중복 예약 — 앱 체크 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부분 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">unique </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인덱스 이중화</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(D27·D32)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-RSV-03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결제 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PaymentGateway </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">어댑터</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(ADR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결제 미완료 자동취소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노쇼 자동 처리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, PT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">패키지 결제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">매출 집계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강사 정산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원천징수</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">강사프로그램게시 — 요구사항</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원천</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/domains/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강사프로그램게시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.md · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기능 명세는 코드 실측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장소 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점 관리자로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">신규 강사를 등록하고 프로필</t>
     </r>
     <r>
       <rPr>
@@ -17737,7 +20954,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">연락처 등</t>
+      <t xml:space="preserve">경력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전문분야</t>
     </r>
     <r>
       <rPr>
@@ -17756,7 +20992,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">을 신청하면 관리자 승인 후 반영되길 원한다</t>
+      <t xml:space="preserve">을 관리하고 싶다</t>
     </r>
     <r>
       <rPr>
@@ -17796,7 +21032,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">퇴사 처리 시 퇴사일을 기록하고 계정을 자동으로 비활성화하고 싶다</t>
+      <t xml:space="preserve">새 프로그램</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, PT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">을 개설하고 시간표를 등록하고 싶다</t>
     </r>
     <r>
       <rPr>
@@ -17810,17 +21103,14 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">/staff</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">본사</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원으로서</t>
     </r>
     <r>
       <rPr>
@@ -17839,21 +21129,219 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">지점</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">/staff/:id</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">본사</t>
+      <t xml:space="preserve">종목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시간대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연령대로 프로그램을 필터링해서 찾고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">/programs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/programs/:id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/programs/:id/slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/programs/:id/status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/instructors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/instructors/:id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/branches/:branchId/programs/summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-PRG-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PAID_SESSION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">capacity </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필수 검증을 생성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수정 시점에</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-PRG-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상태 전이 응답에 영향받는 확정 예약 포함</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-PRG-03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">facilityId </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점 일치 검증</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(+DB </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트리거 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D28)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요일 템플릿 회차 일괄 생성</t>
     </r>
     <r>
       <rPr>
@@ -17872,7 +21360,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">지점</t>
+      <t xml:space="preserve">시설 시간 충돌 검사</t>
     </r>
     <r>
       <rPr>
@@ -17891,33 +21379,341 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">직원</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">지점</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/staff/:id/assignments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/staff/:id/resign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/staff/me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-STF-01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">퇴사</t>
+      <t xml:space="preserve">상태 자동 전이 배치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강사 정산</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">혼잡도관리 — 요구사항</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원천</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/domains/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">혼잡도관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.md · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기능 명세는 코드 실측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장소 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회원으로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">헬스장에 가기 전 앱에서 지금 얼마나 붐비는지 확인하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점 관리자로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자동 계산된 혼잡도가 실제와 다르면 수동으로 보정하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">특별 이벤트로 사람이 몰릴 때</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지점 관리자로서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시설별 정원 대비 이용률을 설정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">관리하고 싶다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">/facilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/facilities/:id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/facilities/:id/congestion/manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-FAC-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">혼잡도 값에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">lastUpdatedAt</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-FAC-02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Facility.isActive + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비활성화</t>
     </r>
     <r>
       <rPr>
@@ -17936,189 +21732,21 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">파견 발령은 단일 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">트랜잭션</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구현</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(D30)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-STF-02</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">staffCode </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">채번 — 시퀀스 테이블 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">행 락</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(allocateBranchCode)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구현</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(D28·D30)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-STF-03</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">활성 파견 유일성 — 부분 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">unique </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인덱스</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구현</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(D27)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-STF-04</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">파견 발령 시 담당 회원</t>
+      <t xml:space="preserve">재활성화</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADR-FAC-03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">계약 종료 지점의 시설 등록</t>
     </r>
     <r>
       <rPr>
@@ -18137,3699 +21765,166 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">강사 프로필 해제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">같은 트랜잭션</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
+      <t xml:space="preserve">보정 차단</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">QR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">체크인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아웃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분 주기 자동계산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF14191C"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미체크아웃 자동 마감 — 구현하려면 사용자 승인</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">자원문서관리 — 요구사항</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원천</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/domains/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자원문서관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.md · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기능 명세는 코드 실측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저장소 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4B5563"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구현</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(D30, DI-02)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">변경 신청</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">승인 워크플로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">파견 이력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">UI, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연락처 마스킹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, offDays </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력 화면</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">근태관리 — 요구사항</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원천</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: docs/domains/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">근태관리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.md · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기능 명세는 코드 실측</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">커밋 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">02f7e1d)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직원으로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">출근</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">퇴근 시 앱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">또는 웹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에서 버튼 하나로 체크인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아웃하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직원으로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연차를 신청하면 지점 관리자가 승인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">반려할 수 있길 원한다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점 관리자로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">우리 지점 직원들의 이번 달 근태 현황</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지각</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결근</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">휴가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">을 한눈에 보고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직원으로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">오늘 업무일지를 작성해 관리자와 공유하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">/attendance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/attendance/absence-confirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/attendance/absence-preview</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/attendance/check-in</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">직원</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">/attendance/check-out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/attendance/summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/leave-requests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/leave-requests/:id/approve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/leave-requests/:id/reject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/leave-balance/:staffId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/work-logs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-ATT-01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연차 차감은 승인 시점에만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">반려 복구 로직 불필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-ATT-02</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결근은 관리자의 명시적 확정 액션</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배치 아님</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-ATT-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">근태 기록 지점 귀속 — 그 날짜의 파견 지점 스냅샷</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">근태 정정 이력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(AuditLog). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">업무일지 하루 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건은 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">unique </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대신 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">advisory lock(D33) — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제약 추가는 승인 대기</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">게시판 — 요구사항</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원천</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: docs/domains/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">게시판</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.md · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기능 명세는 코드 실측</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">커밋 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">02f7e1d)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">본사 관리자로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전 지점</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">또는 특정 지점</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 공지를 올리고 필요시 교육자료 파일을 첨부하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점 관리자로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">본사 공지를 확인하고 우리 지점 회원들에게 전달할 공지를 따로 작성하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원으로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">내가 다니는 지점의 공지사항을 앱에서 확인하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">/posts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/posts/:id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-BRD-01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원 대상 공지 가시성 필터 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">visibleToMember</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-BRD-02</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">목록 페이지네이션</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기본 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">limit 20)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">첨부파일 업로드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, pinned·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">읽음 확인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">범위 제외</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), category </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">필터 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">UI, TrainingLog</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">회원관리 — 요구사항</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원천</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: docs/domains/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원관리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.md · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기능 명세는 코드 실측</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">커밋 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">02f7e1d)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원으로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">앱에서 회원가입 후 내가 다니는 지점을 선택하고 이용을 시작하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점 관리자로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">신규 방문 회원을 현장에서 직접 등록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">오프라인 등록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">할 수도 있어야 한다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점 관리자로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원의 수강</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예약</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/PT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">잔여 세션을 한 화면에서 확인하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원으로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">내 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">잔여 세션이 몇 회 남았는지 앱에서 확인하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">/members</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/members/:id</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">본사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">/members/:id/enrollments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/members/:id/pt-sessions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/members/:id/pt-sessions/:sessionId/use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/members/:id/status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/members/link</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">API</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원 모바일 웹 예정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">/members/register</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-MEM-01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">오프라인↔앱 연동 — 회원번호</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전화번호 동시 일치</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-MEM-02</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">탈퇴 회원 이메일 재사용 — 활성 계정끼리만 부분 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">unique</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-MEM-03</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원 상세 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요약 카운트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">탭별 지연 로드</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연동 승인 플로우</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자동 휴면 전환 배치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전화번호 마스킹 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">UI</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">예약및결제 — 요구사항</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원천</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: docs/domains/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예약및결제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.md · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기능 명세는 코드 실측</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">커밋 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">02f7e1d)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원으로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원하는 프로그램의 회차를 조회하고 예약하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원으로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">유료 회차는 예약 후 모의결제로 확정하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원으로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사정이 생기면 예약을 취소하고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">마감시간 전이면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">환불받고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점 관리자로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원이 현장에 도착하면 체크인 처리하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점 관리자로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">우리 지점 예약</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결제 현황을 조회하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">타 지점은 불가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">).</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">/reservations</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">본사</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">회원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/reservations/:id/cancel</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">/reservations/:id/check-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/payments</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">본사</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">/payments/:reservationId/mock-pay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-RSV-01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정원 초과 방지 — 회차 행 락</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(lockScheduleSlot)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구현</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(D32)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-RSV-02</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중복 예약 — 앱 체크 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부분 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">unique </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인덱스 이중화</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구현</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(D27·D32)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-RSV-03</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결제 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PaymentGateway </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">어댑터</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미구현</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(ADR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결제 미완료 자동취소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">노쇼 자동 처리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, PT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">패키지 결제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">매출 집계 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">API, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">강사 정산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원천징수</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">강사프로그램게시 — 요구사항</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원천</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: docs/domains/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">강사프로그램게시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.md · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기능 명세는 코드 실측</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">커밋 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">02f7e1d)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점 관리자로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">신규 강사를 등록하고 프로필</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전문분야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">을 관리하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점 관리자로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">새 프로그램</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, PT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">을 개설하고 시간표를 등록하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원으로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">종목</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시간대</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연령대로 프로그램을 필터링해서 찾고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">/programs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/programs/:id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/programs/:id/slots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/programs/:id/status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/instructors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/instructors/:id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/branches/:branchId/programs/summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-PRG-01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PAID_SESSION</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">capacity </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">필수 검증을 생성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수정 시점에</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-PRG-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상태 전이 응답에 영향받는 확정 예약 포함</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-PRG-03</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">facilityId </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점 일치 검증</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">구현</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(+DB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">트리거 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D28)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요일 템플릿 회차 일괄 생성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시설 시간 충돌 검사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상태 자동 전이 배치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">강사 정산</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">혼잡도관리 — 요구사항</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원천</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: docs/domains/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">혼잡도관리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.md · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기능 명세는 코드 실측</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">커밋 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">02f7e1d)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회원으로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">헬스장에 가기 전 앱에서 지금 얼마나 붐비는지 확인하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점 관리자로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자동 계산된 혼잡도가 실제와 다르면 수동으로 보정하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">특별 이벤트로 사람이 몰릴 때</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">지점 관리자로서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시설별 정원 대비 이용률을 설정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">관리하고 싶다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">/facilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/facilities/:id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/facilities/:id/congestion/manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-FAC-01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">혼잡도 값에 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">lastUpdatedAt</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-FAC-02</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Facility.isActive + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">비활성화</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">재활성화</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ADR-FAC-03</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">계약 종료 지점의 시설 등록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">보정 차단</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">QR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">체크인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아웃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">분 주기 자동계산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF14191C"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미체크아웃 자동 마감 — 구현하려면 사용자 승인</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">자원문서관리 — 요구사항</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원천</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: docs/domains/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자원문서관리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.md · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기능 명세는 코드 실측</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">커밋 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4B5563"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">02f7e1d)</t>
     </r>
   </si>
   <si>
@@ -25235,7 +25330,7 @@
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
     </row>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -24,7 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범위 제외" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$185</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RFP 충족 판정'!$A$17:$E$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>도메인 9개 · 기능(API) 97개 · 불변규칙 26개 · RFP 미구현·부분 11건 · 자동 테스트 파일 43개</t>
+          <t>도메인 9개 · 기능(API) 97개 · 불변규칙 26개 · RFP 미구현·부분 9건 · 자동 테스트 파일 43개</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 45/64 = 70% / 94%(구현+조정 / 부분 포함)</t>
+          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 47/64 = 73% / 94%(구현+조정 / 부분 포함)</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3949,17 +3949,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>근태관리(1-1 #3)</t>
+          <t>게시판(1-1 #4)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>휴무·병가 일수 관리</t>
+          <t>현장→이용자 "각 시설에 대한" 공지 글·이미지</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>부분 — 휴가 신청에 유형·기간 일수가 남고 연차는 잔여 일수를 관리하지만, 병가·경조사의 연간 누적 일수를 보여 주는 곳이 없다</t>
+          <t>부분 — 공지는 지점 단위라 시설을 지정할 수 없다(이미지는 회원 웹 공지 상세 본문 아래에 보인다, log/137)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -3976,17 +3976,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>게시판(1-1 #4)</t>
+          <t>시스템가용성(1-1 #10)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>현장→이용자 "각 시설에 대한" 공지 글·이미지</t>
+          <t>메모리 평균 85% 이하 유지</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>부분 — 공지는 지점 단위라 시설을 지정할 수 없고, 이미지 첨부는 올릴 수 있지만 회원 웹 공지 상세에 표시되지 않아 이용자가 볼 수 없다</t>
+          <t>부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>시스템가용성(1-1 #10)</t>
+          <t>UI 보안(1-2 #7)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>메모리 평균 85% 이하 유지</t>
+          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
+          <t>부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -4030,17 +4030,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>UI/UX(1-2 #6)</t>
+          <t>설치및운영(1-2 #2)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>필드 속성에 맞는 입력 언어 우선 적용·입력창 크기 최적화</t>
+          <t>소프트웨어 개발보안 준수</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>부분 — 회원 웹 이메일·전화 입력의 inputMode만. 관리자 웹 입력은 속성 지정이 없고 크기 기준을 따로 점검한 적 없다</t>
+          <t>부분 — 개별 조치는 있지만(§1-2 #2) 시큐어코딩 점검 기준표·점검 기록이 없다</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -4057,22 +4057,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>UI 보안(1-2 #7)</t>
+          <t>보안요건(1-2 #8)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인</t>
+          <t>보안관리계획(인원·문서·장비)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+          <t>없다. 개인정보처리방침은 회원 웹 초안으로 작성(D51)</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>미구현</t>
         </is>
       </c>
     </row>
@@ -4084,17 +4084,17 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>설치및운영(1-2 #2)</t>
+          <t>규정의준수(1-2 #10)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>소프트웨어 개발보안 준수</t>
+          <t>지식재산권·저작권 점검</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>부분 — 개별 조치는 있지만(§1-2 #2) 시큐어코딩 점검 기준표·점검 기록이 없다</t>
+          <t>부분 — 오픈소스만 쓰지만 의존성 라이선스 목록·점검 기록이 없다</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -4111,22 +4111,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>보안요건(1-2 #8)</t>
+          <t>과업4·산출물5(p.4·p.7)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>보안관리계획(인원·문서·장비)</t>
+          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>없다. 개인정보처리방침은 회원 웹 초안으로 작성(D51)</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>미구현</t>
+          <t>부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>부분</t>
         </is>
       </c>
     </row>
@@ -4138,17 +4138,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>규정의준수(1-2 #10)</t>
+          <t>산출물4(p.7)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>지식재산권·저작권 점검</t>
+          <t>단계별 개발 진행 보고서 5부</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>부분 — 오픈소스만 쓰지만 의존성 라이선스 목록·점검 기록이 없다</t>
+          <t>부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -4157,83 +4157,29 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>GAP-10</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>과업4·산출물5(p.4·p.7)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>GAP-11</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>산출물4(p.7)</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>단계별 개발 진행 보고서 5부</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>API는 있고 화면이 없는 것</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>지금은 없다(로컬 전용 dev-storage 경로 제외). 마지막 항목이던 관리자의 직원 업무일지 열람은 2026-10-14 직원 상세에 붙였다(D51, log/112).</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>설계는 있지만 미구현인 도메인 규칙</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>결제 PaymentGateway 어댑터(ADR-RSV-03) — 실 PG를 붙일 때 필요하다.</t>
         </is>
@@ -4241,8 +4187,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A19:E19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4440,7 +4386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G187"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4485,7 +4431,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>COUNTIF($C$12:$C$188,"기능")</f>
+        <f>COUNTIF($C$12:$C$186,"기능")</f>
         <v/>
       </c>
     </row>
@@ -4496,7 +4442,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>COUNTIFS($C$12:$C$188,"기능",$F$12:$F$188,"있음")</f>
+        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"있음")</f>
         <v/>
       </c>
     </row>
@@ -4507,7 +4453,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIFS($C$12:$C$188,"기능",$F$12:$F$188,"없음")</f>
+        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"없음")</f>
         <v/>
       </c>
     </row>
@@ -4518,7 +4464,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF($C$12:$C$188,"불변규칙")</f>
+        <f>COUNTIF($C$12:$C$186,"불변규칙")</f>
         <v/>
       </c>
     </row>
@@ -4529,7 +4475,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF($C$12:$C$188,"미구현")</f>
+        <f>COUNTIF($C$12:$C$186,"미구현")</f>
         <v/>
       </c>
     </row>
@@ -10562,7 +10508,7 @@
       </c>
       <c r="D178" s="9" t="inlineStr">
         <is>
-          <t>휴무·병가 일수 관리 — 부분 — 휴가 신청에 유형·기간 일수가 남고 연차는 잔여 일수를 관리하지만, 병가·경조사의 연간 누적 일수를 보여 주는 곳이 없다</t>
+          <t>현장→이용자 "각 시설에 대한" 공지 글·이미지 — 부분 — 공지는 지점 단위라 시설을 지정할 수 없다(이미지는 회원 웹 공지 상세 본문 아래에 보인다, log/137)</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
@@ -10577,7 +10523,7 @@
       </c>
       <c r="G178" s="9" t="inlineStr">
         <is>
-          <t>근태관리(1-1 #3)</t>
+          <t>게시판(1-1 #4)</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10545,7 @@
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>현장→이용자 "각 시설에 대한" 공지 글·이미지 — 부분 — 공지는 지점 단위라 시설을 지정할 수 없고, 이미지 첨부는 올릴 수 있지만 회원 웹 공지 상세에 표시되지 않아 이용자가 볼 수 없다</t>
+          <t>메모리 평균 85% 이하 유지 — 부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
         </is>
       </c>
       <c r="E179" s="11" t="inlineStr">
@@ -10614,7 +10560,7 @@
       </c>
       <c r="G179" s="9" t="inlineStr">
         <is>
-          <t>게시판(1-1 #4)</t>
+          <t>시스템가용성(1-1 #10)</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10582,7 @@
       </c>
       <c r="D180" s="9" t="inlineStr">
         <is>
-          <t>메모리 평균 85% 이하 유지 — 부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
+          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인 — 부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
         </is>
       </c>
       <c r="E180" s="11" t="inlineStr">
@@ -10651,7 +10597,7 @@
       </c>
       <c r="G180" s="9" t="inlineStr">
         <is>
-          <t>시스템가용성(1-1 #10)</t>
+          <t>UI 보안(1-2 #7)</t>
         </is>
       </c>
     </row>
@@ -10673,7 +10619,7 @@
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>필드 속성에 맞는 입력 언어 우선 적용·입력창 크기 최적화 — 부분 — 회원 웹 이메일·전화 입력의 inputMode만. 관리자 웹 입력은 속성 지정이 없고 크기 기준을 따로 점검한 적 없다</t>
+          <t>소프트웨어 개발보안 준수 — 부분 — 개별 조치는 있지만(§1-2 #2) 시큐어코딩 점검 기준표·점검 기록이 없다</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
@@ -10688,7 +10634,7 @@
       </c>
       <c r="G181" s="9" t="inlineStr">
         <is>
-          <t>UI/UX(1-2 #6)</t>
+          <t>설치및운영(1-2 #2)</t>
         </is>
       </c>
     </row>
@@ -10710,12 +10656,12 @@
       </c>
       <c r="D182" s="9" t="inlineStr">
         <is>
-          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인 — 부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
-        </is>
-      </c>
-      <c r="E182" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+          <t>보안관리계획(인원·문서·장비) — 없다. 개인정보처리방침은 회원 웹 초안으로 작성(D51)</t>
+        </is>
+      </c>
+      <c r="E182" s="12" t="inlineStr">
+        <is>
+          <t>미구현</t>
         </is>
       </c>
       <c r="F182" s="9" t="inlineStr">
@@ -10725,7 +10671,7 @@
       </c>
       <c r="G182" s="9" t="inlineStr">
         <is>
-          <t>UI 보안(1-2 #7)</t>
+          <t>보안요건(1-2 #8)</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10693,7 @@
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>소프트웨어 개발보안 준수 — 부분 — 개별 조치는 있지만(§1-2 #2) 시큐어코딩 점검 기준표·점검 기록이 없다</t>
+          <t>지식재산권·저작권 점검 — 부분 — 오픈소스만 쓰지만 의존성 라이선스 목록·점검 기록이 없다</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
@@ -10762,7 +10708,7 @@
       </c>
       <c r="G183" s="9" t="inlineStr">
         <is>
-          <t>설치및운영(1-2 #2)</t>
+          <t>규정의준수(1-2 #10)</t>
         </is>
       </c>
     </row>
@@ -10784,12 +10730,12 @@
       </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>보안관리계획(인원·문서·장비) — 없다. 개인정보처리방침은 회원 웹 초안으로 작성(D51)</t>
-        </is>
-      </c>
-      <c r="E184" s="12" t="inlineStr">
-        <is>
-          <t>미구현</t>
+          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료 — 부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
+        </is>
+      </c>
+      <c r="E184" s="11" t="inlineStr">
+        <is>
+          <t>부분</t>
         </is>
       </c>
       <c r="F184" s="9" t="inlineStr">
@@ -10799,7 +10745,7 @@
       </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>보안요건(1-2 #8)</t>
+          <t>과업4·산출물5(p.4·p.7)</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10767,7 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>지식재산권·저작권 점검 — 부분 — 오픈소스만 쓰지만 의존성 라이선스 목록·점검 기록이 없다</t>
+          <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
@@ -10836,86 +10782,12 @@
       </c>
       <c r="G185" s="9" t="inlineStr">
         <is>
-          <t>규정의준수(1-2 #10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="9" t="inlineStr">
-        <is>
-          <t>GAP-10</t>
-        </is>
-      </c>
-      <c r="B186" s="9" t="inlineStr">
-        <is>
-          <t>RFP 공통</t>
-        </is>
-      </c>
-      <c r="C186" s="9" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-      <c r="D186" s="9" t="inlineStr">
-        <is>
-          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료 — 부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
-        </is>
-      </c>
-      <c r="E186" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="F186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G186" s="9" t="inlineStr">
-        <is>
-          <t>과업4·산출물5(p.4·p.7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="9" t="inlineStr">
-        <is>
-          <t>GAP-11</t>
-        </is>
-      </c>
-      <c r="B187" s="9" t="inlineStr">
-        <is>
-          <t>RFP 공통</t>
-        </is>
-      </c>
-      <c r="C187" s="9" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-      <c r="D187" s="9" t="inlineStr">
-        <is>
-          <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
-        </is>
-      </c>
-      <c r="E187" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="F187" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G187" s="9" t="inlineStr">
-        <is>
           <t>산출물4(p.7)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A11:G187"/>
+  <autoFilter ref="A11:G185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11558,7 +11430,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>admin-web 디자인 토큰화(D15)로 통일성 확보. "페이지 위치 정보를 MAP형태로"는 현재 화면의 경로 표시로 해석해 구현(D51 — 홈 › 메뉴 › 화면). 예약 달력은 회원 웹 날짜 띠·관리자 주간 시간표(ADR-RSV-06). 입력 필드 언어 우선 적용은 회원 웹 일부 입력(inputMode 이메일·전화)만</t>
+          <t>admin-web 디자인 토큰화(D15)로 통일성 확보. "페이지 위치 정보를 MAP형태로"는 현재 화면의 경로 표시로 해석해 구현(D51 — 홈 › 메뉴 › 화면). 예약 달력은 회원 웹 날짜 띠·관리자 주간 시간표(ADR-RSV-06). 입력 필드는 전화·숫자·이메일·URL에 맞는 자판과 자동완성 속성을 두 앱 모두에 지정(log/137)</t>
         </is>
       </c>
     </row>
@@ -11931,7 +11803,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -11941,7 +11813,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -11956,7 +11828,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>24/28 = 86% / 100%</t>
+          <t>25/28 = 89% / 100%</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11845,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -11983,7 +11855,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -11998,7 +11870,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>11/19 = 58% / 95%</t>
+          <t>12/19 = 63% / 95%</t>
         </is>
       </c>
     </row>
@@ -12057,7 +11929,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -12067,7 +11939,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -12082,7 +11954,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>45/64 = 70% / 94%</t>
+          <t>47/64 = 73% / 94%</t>
         </is>
       </c>
     </row>
@@ -12432,14 +12304,14 @@
           <t>휴무·연차·병가 등 기록 및 일수 관리</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>유형별 휴가 신청·승인·기간 일수, 연차 잔여 관리. 병가·경조사 누적 일수 집계 없음</t>
+          <t>유형별 휴가 신청·승인·기간 일수, 연차 잔여, 올해 유형별 사용 일수(log/137) — attendance-rules</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12419,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>지점 공지 글은 됨. 시설 지정 없음, 이미지 첨부가 회원 웹에 안 보임</t>
+          <t>지점 공지 글·이미지(회원 웹 본문 아래 표시, log/137)는 됨. 시설 지정 없음</t>
         </is>
       </c>
     </row>
@@ -13350,14 +13222,14 @@
           <t>필드 속성에 맞는 입력 언어 우선 적용, 입력창 크기 최적화</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>회원 웹 일부 inputMode만(§2-3)</t>
+          <t>두 앱 입력 103곳 점검 — 전화·숫자·이메일·URL에 type·inputMode·autoComplete, 서버 길이 제한이 있는 칸에 maxLength, 고정 폭 입력 없음·텍스트 영역 9개 모두 rows(log/137). 한글 자판을 강제하는 웹 표준은 없어 텍스트 칸은 기본값</t>
         </is>
       </c>
     </row>
@@ -17456,7 +17328,7 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>구현(API+화면: 관리자 웹)</t>
+          <t>구현(API+화면: 관리자 웹·회원 웹)</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17481,7 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>pinned·읽음 확인(범위 제외), category 필터 UI, TrainingLog, 회원 웹 공지의 첨부 표시</t>
+          <t>pinned·읽음 확인(범위 제외), category 필터 UI, TrainingLog</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -24,7 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범위 제외" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$182</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RFP 충족 판정'!$A$17:$E$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>도메인 9개 · 기능(API) 97개 · 불변규칙 26개 · RFP 미구현·부분 9건 · 자동 테스트 파일 43개</t>
+          <t>도메인 9개 · 기능(API) 97개 · 불변규칙 26개 · RFP 미구현·부분 6건 · 자동 테스트 파일 43개</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 47/64 = 73% / 94%(구현+조정 / 부분 포함)</t>
+          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 51/64 = 80% / 95%(구현+조정 / 부분 포함)</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4030,17 +4030,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>설치및운영(1-2 #2)</t>
+          <t>과업4·산출물5(p.4·p.7)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>소프트웨어 개발보안 준수</t>
+          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>부분 — 개별 조치는 있지만(§1-2 #2) 시큐어코딩 점검 기준표·점검 기록이 없다</t>
+          <t>부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -4057,129 +4057,48 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>보안요건(1-2 #8)</t>
+          <t>산출물4(p.7)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>보안관리계획(인원·문서·장비)</t>
+          <t>단계별 개발 진행 보고서 5부</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>없다. 개인정보처리방침은 회원 웹 초안으로 작성(D51)</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>GAP-07</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>규정의준수(1-2 #10)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>지식재산권·저작권 점검</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>부분 — 오픈소스만 쓰지만 의존성 라이선스 목록·점검 기록이 없다</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
+          <t>부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>부분</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>GAP-08</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>과업4·산출물5(p.4·p.7)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>GAP-09</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>산출물4(p.7)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>단계별 개발 진행 보고서 5부</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>API는 있고 화면이 없는 것</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>지금은 없다(로컬 전용 dev-storage 경로 제외). 마지막 항목이던 관리자의 직원 업무일지 열람은 2026-10-14 직원 상세에 붙였다(D51, log/112).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>API는 있고 화면이 없는 것</t>
+          <t>설계는 있지만 미구현인 도메인 규칙</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>지금은 없다(로컬 전용 dev-storage 경로 제외). 마지막 항목이던 관리자의 직원 업무일지 열람은 2026-10-14 직원 상세에 붙였다(D51, log/112).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>설계는 있지만 미구현인 도메인 규칙</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>결제 PaymentGateway 어댑터(ADR-RSV-03) — 실 PG를 붙일 때 필요하다.</t>
         </is>
@@ -4188,7 +4107,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4386,7 +4305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4431,7 +4350,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>COUNTIF($C$12:$C$186,"기능")</f>
+        <f>COUNTIF($C$12:$C$183,"기능")</f>
         <v/>
       </c>
     </row>
@@ -4442,7 +4361,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"있음")</f>
+        <f>COUNTIFS($C$12:$C$183,"기능",$F$12:$F$183,"있음")</f>
         <v/>
       </c>
     </row>
@@ -4453,7 +4372,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"없음")</f>
+        <f>COUNTIFS($C$12:$C$183,"기능",$F$12:$F$183,"없음")</f>
         <v/>
       </c>
     </row>
@@ -4464,7 +4383,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF($C$12:$C$186,"불변규칙")</f>
+        <f>COUNTIF($C$12:$C$183,"불변규칙")</f>
         <v/>
       </c>
     </row>
@@ -4475,7 +4394,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF($C$12:$C$186,"미구현")</f>
+        <f>COUNTIF($C$12:$C$183,"미구현")</f>
         <v/>
       </c>
     </row>
@@ -10619,7 +10538,7 @@
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>소프트웨어 개발보안 준수 — 부분 — 개별 조치는 있지만(§1-2 #2) 시큐어코딩 점검 기준표·점검 기록이 없다</t>
+          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료 — 부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
@@ -10634,7 +10553,7 @@
       </c>
       <c r="G181" s="9" t="inlineStr">
         <is>
-          <t>설치및운영(1-2 #2)</t>
+          <t>과업4·산출물5(p.4·p.7)</t>
         </is>
       </c>
     </row>
@@ -10656,12 +10575,12 @@
       </c>
       <c r="D182" s="9" t="inlineStr">
         <is>
-          <t>보안관리계획(인원·문서·장비) — 없다. 개인정보처리방침은 회원 웹 초안으로 작성(D51)</t>
-        </is>
-      </c>
-      <c r="E182" s="12" t="inlineStr">
-        <is>
-          <t>미구현</t>
+          <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
+        </is>
+      </c>
+      <c r="E182" s="11" t="inlineStr">
+        <is>
+          <t>부분</t>
         </is>
       </c>
       <c r="F182" s="9" t="inlineStr">
@@ -10671,123 +10590,12 @@
       </c>
       <c r="G182" s="9" t="inlineStr">
         <is>
-          <t>보안요건(1-2 #8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="9" t="inlineStr">
-        <is>
-          <t>GAP-07</t>
-        </is>
-      </c>
-      <c r="B183" s="9" t="inlineStr">
-        <is>
-          <t>RFP 공통</t>
-        </is>
-      </c>
-      <c r="C183" s="9" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-      <c r="D183" s="9" t="inlineStr">
-        <is>
-          <t>지식재산권·저작권 점검 — 부분 — 오픈소스만 쓰지만 의존성 라이선스 목록·점검 기록이 없다</t>
-        </is>
-      </c>
-      <c r="E183" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="F183" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G183" s="9" t="inlineStr">
-        <is>
-          <t>규정의준수(1-2 #10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="9" t="inlineStr">
-        <is>
-          <t>GAP-08</t>
-        </is>
-      </c>
-      <c r="B184" s="9" t="inlineStr">
-        <is>
-          <t>RFP 공통</t>
-        </is>
-      </c>
-      <c r="C184" s="9" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-      <c r="D184" s="9" t="inlineStr">
-        <is>
-          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료 — 부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
-        </is>
-      </c>
-      <c r="E184" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="F184" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G184" s="9" t="inlineStr">
-        <is>
-          <t>과업4·산출물5(p.4·p.7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="9" t="inlineStr">
-        <is>
-          <t>GAP-09</t>
-        </is>
-      </c>
-      <c r="B185" s="9" t="inlineStr">
-        <is>
-          <t>RFP 공통</t>
-        </is>
-      </c>
-      <c r="C185" s="9" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-      <c r="D185" s="9" t="inlineStr">
-        <is>
-          <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
-        </is>
-      </c>
-      <c r="E185" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="F185" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G185" s="9" t="inlineStr">
-        <is>
           <t>산출물4(p.7)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A11:G185"/>
+  <autoFilter ref="A11:G182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11322,7 +11130,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1인 개발 구조상 "발주기관/전문가 검증" 주체가 없음 — CI(lint·빌드·jest·문서 검사)와 커밋 전 hook, 도메인 문서 §11 검증현황으로 대체. 개발보안은 개별 조치(비밀값 부팅 검사·1회용 갱신 토큰·응답 마스킹·지점 격리 가드·로그인 rate limit)만 있고 점검 기준표는 없음</t>
+          <t>1인 개발 구조상 "발주기관/전문가 검증" 주체가 없음 — CI(lint·빌드·jest·문서 검사)와 커밋 전 hook, 도메인 문서 §11 검증현황으로 대체. 개발보안은 행안부 구현단계 보안약점 49개로 점검했다(secure-coding-checklist — 대응 34·부분 4·해당 없음 11, 점검 중 찾은 문서 주소 XSS는 수정, log/139)</t>
         </is>
       </c>
     </row>
@@ -11484,7 +11292,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>개인정보처리방침을 회원 웹 화면(/m/privacy)으로 작성 — 수집 항목·열람 범위·보관·처리 위탁(26조: Supabase·AWS·Cloudflare). 시연용 초안, 가입 시 동의는 화면에서만 받음(D51). 보안관리계획(인원·문서·장비)은 없음</t>
+          <t>개인정보처리방침을 회원 웹 화면(/m/privacy)으로 작성 — 수집 항목·열람 범위·보관·처리 위탁(26조: Supabase·AWS·Cloudflare). 시연용 초안, 가입 시 동의는 화면에서만 받음(D51). 보안관리계획은 security-plan(인원·문서·장비·비밀값·위탁, 지금 약점 9건과 조치 계획 — log/139)</t>
         </is>
       </c>
     </row>
@@ -11538,7 +11346,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>오픈소스 라이선스(MIT/Apache 등) 패키지만 사용 — 별도 점검 문서는 없음</t>
+          <t>운영 의존성 219개가 모두 허용형 라이선스(MIT·ISC·Apache-2.0·BSD 등, copyleft 없음) — dependency-licenses를 scripts/license-report.mjs가 만들고 --check로 다시 점검(log/139). 이미지·아이콘은 자체 제작</t>
         </is>
       </c>
     </row>
@@ -11845,7 +11653,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -11855,22 +11663,22 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>12/19 = 63% / 95%</t>
+          <t>16/19 = 84% / 100%</t>
         </is>
       </c>
     </row>
@@ -11929,7 +11737,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -11939,12 +11747,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -11954,7 +11762,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>47/64 = 73% / 94%</t>
+          <t>51/64 = 80% / 95%</t>
         </is>
       </c>
     </row>
@@ -12898,14 +12706,14 @@
           <t>소프트웨어 개발보안 준수</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>개별 조치만, 점검 기준표 없음(§2-3)</t>
+          <t>행안부 구현단계 보안약점 49개 점검표(secure-coding-checklist — 대응 34·부분 4·해당 없음 11), 남은 조치 4건 표로 관리, 점검 중 찾은 XSS 수정(document-rules)</t>
         </is>
       </c>
     </row>
@@ -13357,14 +13165,14 @@
           <t>인원·문서·장비 보안관리계획 수립</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
-        <is>
-          <t>미구현</t>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>문서 없음</t>
+          <t>security-plan — 인원·문서·장비·비밀값·운영 보호·위탁, 지금 약점 9건과 조치 계획</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13199,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>처리방침 초안의 위탁 고지(D51), 위탁 계약·점검은 없음</t>
+          <t>처리방침 초안의 위탁 고지(D51), 수탁자·업무·위치 표(security-plan §7). 위탁 계약 문서 보관·수탁자 감독 기록은 없음(실데이터 운영 전 조치)</t>
         </is>
       </c>
     </row>
@@ -13465,14 +13273,14 @@
           <t>산출물의 지식재산권 주의·준수</t>
         </is>
       </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>오픈소스만 사용, 점검 기록 없음</t>
+          <t>운영 의존성 219개 라이선스 목록·허용형 점검(dependency-licenses, license-report.mjs --check)</t>
         </is>
       </c>
     </row>
@@ -13492,14 +13300,14 @@
           <t>저작권 문제가 없는 저작물 구현</t>
         </is>
       </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>같은 이유</t>
+          <t>같은 목록 + 이미지·아이콘 자체 제작, 외부 글꼴·이미지 파일 없음</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -24,7 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범위 제외" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$181</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RFP 충족 판정'!$A$17:$E$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 저장소(dev 브랜치) — 도메인 문서·요구사항추적표·실제 API 라우트에서 자동 생성</t>
+          <t>2026-10-20 저장소(dev 브랜치) — 도메인 문서·요구사항추적표·실제 API 라우트에서 자동 생성</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>도메인 9개 · 기능(API) 97개 · 불변규칙 26개 · RFP 미구현·부분 6건 · 자동 테스트 파일 43개</t>
+          <t>도메인 9개 · 기능(API) 97개 · 불변규칙 26개 · RFP 미구현·부분 5건 · 자동 테스트 파일 45개</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 51/64 = 80% / 95%(구현+조정 / 부분 포함)</t>
+          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 52/64 = 81% / 95%(구현+조정 / 부분 포함)</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/예약및결제.md · 기능 명세는 코드 실측(2026-10-19 저장소 기준)</t>
+          <t>원천: docs/domains/예약및결제.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/강사프로그램게시.md · 기능 명세는 코드 실측(2026-10-19 저장소 기준)</t>
+          <t>원천: docs/domains/강사프로그램게시.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/혼잡도관리.md · 기능 명세는 코드 실측(2026-10-19 저장소 기준)</t>
+          <t>원천: docs/domains/혼잡도관리.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/자원문서관리.md · 기능 명세는 코드 실측(2026-10-19 저장소 기준)</t>
+          <t>원천: docs/domains/자원문서관리.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3949,17 +3949,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>게시판(1-1 #4)</t>
+          <t>시스템가용성(1-1 #10)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>현장→이용자 "각 시설에 대한" 공지 글·이미지</t>
+          <t>메모리 평균 85% 이하 유지</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>부분 — 공지는 지점 단위라 시설을 지정할 수 없다(이미지는 회원 웹 공지 상세 본문 아래에 보인다, log/137)</t>
+          <t>부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -3976,17 +3976,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>시스템가용성(1-1 #10)</t>
+          <t>UI 보안(1-2 #7)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>메모리 평균 85% 이하 유지</t>
+          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
+          <t>부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>UI 보안(1-2 #7)</t>
+          <t>과업4·산출물5(p.4·p.7)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인</t>
+          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
+          <t>부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -4030,17 +4030,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>과업4·산출물5(p.4·p.7)</t>
+          <t>산출물4(p.7)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료</t>
+          <t>단계별 개발 진행 보고서 5부</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
+          <t>부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -4049,56 +4049,29 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>GAP-06</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>산출물4(p.7)</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>단계별 개발 진행 보고서 5부</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>API는 있고 화면이 없는 것</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>지금은 없다(로컬 전용 dev-storage 경로 제외). 마지막 항목이던 관리자의 직원 업무일지 열람은 2026-10-14 직원 상세에 붙였다(D51, log/112).</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>설계는 있지만 미구현인 도메인 규칙</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>결제 PaymentGateway 어댑터(ADR-RSV-03) — 실 PG를 붙일 때 필요하다.</t>
         </is>
@@ -4106,8 +4079,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4305,7 +4278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G182"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4350,7 +4323,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>COUNTIF($C$12:$C$183,"기능")</f>
+        <f>COUNTIF($C$12:$C$182,"기능")</f>
         <v/>
       </c>
     </row>
@@ -4361,7 +4334,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>COUNTIFS($C$12:$C$183,"기능",$F$12:$F$183,"있음")</f>
+        <f>COUNTIFS($C$12:$C$182,"기능",$F$12:$F$182,"있음")</f>
         <v/>
       </c>
     </row>
@@ -4372,7 +4345,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIFS($C$12:$C$183,"기능",$F$12:$F$183,"없음")</f>
+        <f>COUNTIFS($C$12:$C$182,"기능",$F$12:$F$182,"없음")</f>
         <v/>
       </c>
     </row>
@@ -4383,7 +4356,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF($C$12:$C$183,"불변규칙")</f>
+        <f>COUNTIF($C$12:$C$182,"불변규칙")</f>
         <v/>
       </c>
     </row>
@@ -4394,7 +4367,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF($C$12:$C$183,"미구현")</f>
+        <f>COUNTIF($C$12:$C$182,"미구현")</f>
         <v/>
       </c>
     </row>
@@ -6723,7 +6696,7 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
+          <t>post-facility·post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6733,7 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
+          <t>post-facility·post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10400,7 @@
       </c>
       <c r="D178" s="9" t="inlineStr">
         <is>
-          <t>현장→이용자 "각 시설에 대한" 공지 글·이미지 — 부분 — 공지는 지점 단위라 시설을 지정할 수 없다(이미지는 회원 웹 공지 상세 본문 아래에 보인다, log/137)</t>
+          <t>메모리 평균 85% 이하 유지 — 부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
@@ -10442,7 +10415,7 @@
       </c>
       <c r="G178" s="9" t="inlineStr">
         <is>
-          <t>게시판(1-1 #4)</t>
+          <t>시스템가용성(1-1 #10)</t>
         </is>
       </c>
     </row>
@@ -10464,7 +10437,7 @@
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>메모리 평균 85% 이하 유지 — 부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
+          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인 — 부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
         </is>
       </c>
       <c r="E179" s="11" t="inlineStr">
@@ -10479,7 +10452,7 @@
       </c>
       <c r="G179" s="9" t="inlineStr">
         <is>
-          <t>시스템가용성(1-1 #10)</t>
+          <t>UI 보안(1-2 #7)</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10474,7 @@
       </c>
       <c r="D180" s="9" t="inlineStr">
         <is>
-          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인 — 부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
+          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료 — 부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
         </is>
       </c>
       <c r="E180" s="11" t="inlineStr">
@@ -10516,7 +10489,7 @@
       </c>
       <c r="G180" s="9" t="inlineStr">
         <is>
-          <t>UI 보안(1-2 #7)</t>
+          <t>과업4·산출물5(p.4·p.7)</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10511,7 @@
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료 — 부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
+          <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
@@ -10553,49 +10526,12 @@
       </c>
       <c r="G181" s="9" t="inlineStr">
         <is>
-          <t>과업4·산출물5(p.4·p.7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="9" t="inlineStr">
-        <is>
-          <t>GAP-06</t>
-        </is>
-      </c>
-      <c r="B182" s="9" t="inlineStr">
-        <is>
-          <t>RFP 공통</t>
-        </is>
-      </c>
-      <c r="C182" s="9" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-      <c r="D182" s="9" t="inlineStr">
-        <is>
-          <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
-        </is>
-      </c>
-      <c r="E182" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="F182" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G182" s="9" t="inlineStr">
-        <is>
           <t>산출물4(p.7)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A11:G182"/>
+  <autoFilter ref="A11:G181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11611,7 +11547,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -11621,7 +11557,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -11636,7 +11572,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>25/28 = 89% / 100%</t>
+          <t>26/28 = 93% / 100%</t>
         </is>
       </c>
     </row>
@@ -11737,7 +11673,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -11747,7 +11683,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -11762,7 +11698,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>51/64 = 80% / 95%</t>
+          <t>52/64 = 81% / 95%</t>
         </is>
       </c>
     </row>
@@ -12220,14 +12156,14 @@
           <t>현장→이용자 각 시설에 대한 공지 글·이미지 작성</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>지점 공지 글·이미지(회원 웹 본문 아래 표시, log/137)는 됨. 시설 지정 없음</t>
+          <t>지점 공지에 대상 시설 지정(게시판 ADR-BRD-05, log/145) — 관리자 웹 글쓰기·수정에서 선택, 회원 웹 시설로 거르기·표시. 이미지는 두 웹 모두 바로 표시(log/137·144)</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13766,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/권한관리.md · 기능 명세는 코드 실측(2026-10-19 저장소 기준)</t>
+          <t>원천: docs/domains/권한관리.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -14648,7 +14584,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/인사정보관리.md · 기능 명세는 코드 실측(2026-10-19 저장소 기준)</t>
+          <t>원천: docs/domains/인사정보관리.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -15682,7 +15618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15703,7 +15639,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/근태관리.md · 기능 명세는 코드 실측(2026-10-19 저장소 기준)</t>
+          <t>원천: docs/domains/근태관리.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -16562,8 +16498,28 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>ADR-ATT-05</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>겹치는 휴가 신청·승인 금지(직원 행 락, 연차 이중 차감 방지)</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="14" t="n"/>
+      <c r="E47" s="15" t="n"/>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>구현(log/141)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B45:E45"/>
@@ -16575,6 +16531,7 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B44:E44"/>
     <mergeCell ref="C15:F15"/>
+    <mergeCell ref="B47:E47"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B22:F22"/>
@@ -16591,7 +16548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16612,7 +16569,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/게시판.md · 기능 명세는 코드 실측(2026-10-19 저장소 기준)</t>
+          <t>원천: docs/domains/게시판.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16798,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
+          <t>post-facility·post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
@@ -17275,31 +17232,51 @@
       <c r="E39" s="15" t="n"/>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>구현(log/121, 배포 저장소 설정 전)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+          <t>구현(log/121), 배포 실제 파일 확인(log/144)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>ADR-BRD-05</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>지점 공지의 대상 시설(Post.facilityId, 선택) — 다른 지점 시설 403, 본사 공지 400, 목록 facilityId 필터</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>구현(log/145, 배포 DB 적용 대기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>미구현·범위 제외(도메인 문서 기준)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>pinned·읽음 확인(범위 제외), category 필터 UI, TrainingLog</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="B36:E36"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="B40:E40"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B37:E37"/>
@@ -17310,6 +17287,7 @@
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17342,7 +17320,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/회원관리.md · 기능 명세는 코드 실측(2026-10-19 저장소 기준)</t>
+          <t>원천: docs/domains/회원관리.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>도메인 9개 · 기능(API) 97개 · 불변규칙 26개 · RFP 미구현·부분 5건 · 자동 테스트 파일 45개</t>
+          <t>도메인 9개 · 기능(API) 97개 · 불변규칙 26개 · RFP 미구현·부분 5건 · 자동 테스트 파일 47개</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
+          <t>permission-matrix·permission-coverage·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
+          <t>permission-matrix·permission-coverage·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
+          <t>permission-matrix·permission-coverage·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
         </is>
       </c>
     </row>
@@ -11839,7 +11839,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>역할 4개 고정(D1). 출력은 CSV를 역할 기준으로(D54). 세부 권한 표 없음</t>
+          <t>D60(D1 대체) 1단계 — 서버가 기능×동작 권한을 역할 기본값·개인 예외로 판정(log/146). 본사가 바꾸는 화면·API는 2단계</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>역할·지점 단위까지만(D1)</t>
+          <t>역할·지점 단위 + 서버의 역할별·개인별·기능별 판정(D60 1단계, log/146). 설정 화면은 2단계</t>
         </is>
       </c>
     </row>
@@ -13745,7 +13745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14099,7 +14099,7 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
+          <t>permission-matrix·permission-coverage·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
         </is>
       </c>
     </row>
@@ -14447,9 +14447,9 @@
       <c r="C42" s="14" t="n"/>
       <c r="D42" s="14" t="n"/>
       <c r="E42" s="15" t="n"/>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>ADR-AUTH-07이 대체(D60) — 역할 상한으로 유지</t>
         </is>
       </c>
     </row>
@@ -14513,22 +14513,42 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>ADR-AUTH-07</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>세부 권한 — 역할 상한 안에서 역할 기본값 + 개인 예외(조회·입력·수정·삭제·출력), 전역 PermissionGuard</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="14" t="n"/>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>1단계 구현(log/146, 서버 판정) — 설정 화면·변경 API는 2단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>미구현·범위 제외(도메인 문서 기준)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="16" t="inlineStr">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>로그인 잠금, /accounts 범용 API, 비밀번호 재설정·로그인 이력 화면</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C17:F17"/>
@@ -14541,13 +14561,14 @@
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B46:E46"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A48:F48"/>
     <mergeCell ref="B42:E42"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B23:E23"/>
+    <mergeCell ref="A49:F49"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B44:E44"/>
     <mergeCell ref="B5:F5"/>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -24,7 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범위 제외" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$186</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RFP 충족 판정'!$A$17:$E$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>도메인 9개 · 기능(API) 97개 · 불변규칙 26개 · RFP 미구현·부분 5건 · 자동 테스트 파일 47개</t>
+          <t>도메인 9개 · 기능(API) 102개 · 불변규칙 26개 · RFP 미구현·부분 5건 · 자동 테스트 파일 48개</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>COUNTIF($C$12:$C$182,"기능")</f>
+        <f>COUNTIF($C$12:$C$187,"기능")</f>
         <v/>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>COUNTIFS($C$12:$C$182,"기능",$F$12:$F$182,"있음")</f>
+        <f>COUNTIFS($C$12:$C$187,"기능",$F$12:$F$187,"있음")</f>
         <v/>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIFS($C$12:$C$182,"기능",$F$12:$F$182,"없음")</f>
+        <f>COUNTIFS($C$12:$C$187,"기능",$F$12:$F$187,"없음")</f>
         <v/>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF($C$12:$C$182,"불변규칙")</f>
+        <f>COUNTIF($C$12:$C$187,"불변규칙")</f>
         <v/>
       </c>
     </row>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF($C$12:$C$182,"미구현")</f>
+        <f>COUNTIF($C$12:$C$187,"미구현")</f>
         <v/>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>permission-matrix·permission-coverage·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
+          <t>permission-matrix·permission-coverage·permission-admin·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>permission-matrix·permission-coverage·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
+          <t>permission-matrix·permission-coverage·permission-admin·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>permission-matrix·permission-coverage·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
+          <t>permission-matrix·permission-coverage·permission-admin·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>직원 계정과 역할 목록(본사)</t>
+          <t>(설명 없음)</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>GET /permissions/staff</t>
+          <t>GET /permissions/catalog</t>
         </is>
       </c>
     </row>
@@ -4990,198 +4990,214 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
+          <t>(설명 없음)</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>GET /permissions/roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-FN-08</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>권한관리</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>(설명 없음)</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>PUT /permissions/roles/:role</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-FN-09</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>권한관리</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>직원 계정과 역할 목록(본사)</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>GET /permissions/staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-FN-10</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>권한관리</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>(설명 없음)</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>GET /permissions/staff/:staffId/overrides</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-FN-11</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>권한관리</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>(설명 없음)</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>PUT /permissions/staff/:staffId/overrides</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>AUTH-FN-12</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>권한관리</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
           <t>직원 역할 전환(지점 관리자 ↔ 직원, 본사)</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>PATCH /permissions/staff/:staffId/role</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>F02a</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>인사정보관리</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>현장(지점)별 인사관리 탭, 코드 생성</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>F02b</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>인사정보관리</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>모든 인사기록 정보를 한 화면에서 조회</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>F02c</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>인사정보관리</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>권한 부여 혹은 승인 시 수정 가능</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>STF-C04</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>인사정보관리</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>원문 제약</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>C01(과업 기간)이 간접 제약: "승인 기반 수정"의 다단계 결재라인은 1인 개발 범위를 넘어 본인 신청→1단계 승인으로 단순화(아래 §8 참고).</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>STF-INV-01</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>인사정보관리</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>불변규칙</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>채용·재배치는 본사(SUPER_ADMIN)만 한다. (CLAUDE.md 4대 불변식 — 인사 권한 분리. 권한관리 도메인의 불변규칙 2와 같은 원천, 이 도메인은 그 실제 구현 지점이다)</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>staff-assignment·staff-write·staff-change-requests·hr-authority·contract-termination·integrity-helpers·audit-log·phone-view-audit·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>STF-INV-02</t>
+          <t>F02a</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -5191,17 +5207,17 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>한 직원은 활성(endDate=null) StaffAssignment가 항상 최대 1건이어야 한다. (파견이 이 도메인의 핵심 모델인 이상, 한 사람이 동시에 두 지점에 파견될 수는 없다는 건 협의 대상이 아니다)</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>현장(지점)별 인사관리 탭, 코드 생성</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -5209,16 +5225,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>staff-assignment·staff-write·staff-change-requests·hr-authority·contract-termination·integrity-helpers·audit-log·phone-view-audit·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>STF-INV-03</t>
+          <t>F02b</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -5228,17 +5240,17 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>퇴사 처리는 계정 비활성화와 분리될 수 없다. (권한관리 도메인 불변규칙 1 "퇴사 즉시 접근 차단"의 트리거가 바로 이 도메인의 /resign이다 — 두 도메인이 공유하는 불변식의 서로 다른 쪽 절반)</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>모든 인사기록 정보를 한 화면에서 조회</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -5246,16 +5258,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>staff-assignment·staff-write·staff-change-requests·hr-authority·contract-termination·integrity-helpers·audit-log·phone-view-audit·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>STF-FN-01</t>
+          <t>F02c</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -5265,34 +5273,30 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>직원 목록(본사 전체, 지점 관리자는 자기 지점) — 전화번호 마스킹, ?unassigned=true는 재배치 대기(ADR-STF-08)</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>권한 부여 혹은 승인 시 수정 가능</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>GET /staff</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>STF-FN-02</t>
+          <t>STF-C04</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -5302,34 +5306,30 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 제약</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>직원 채용 — 계정·직원·첫 파견을 함께 생성(본사만)</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>C01(과업 기간)이 간접 제약: "승인 기반 수정"의 다단계 결재라인은 1인 개발 범위를 넘어 본인 신청→1단계 승인으로 단순화(아래 §8 참고).</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>POST /staff</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>STF-FN-03</t>
+          <t>STF-INV-01</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>직원 상세 — 관리자가 열면 열람 기록(PHONE_VIEWED, D47)</t>
+          <t>채용·재배치는 본사(SUPER_ADMIN)만 한다. (CLAUDE.md 4대 불변식 — 인사 권한 분리. 권한관리 도메인의 불변규칙 2와 같은 원천, 이 도메인은 그 실제 구현 지점이다)</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -5354,19 +5354,19 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>GET /staff/:id</t>
+          <t>staff-assignment·staff-write·staff-change-requests·hr-authority·contract-termination·integrity-helpers·audit-log·phone-view-audit·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>STF-FN-04</t>
+          <t>STF-INV-02</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -5376,12 +5376,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>직원 정보 수정</t>
+          <t>한 직원은 활성(endDate=null) StaffAssignment가 항상 최대 1건이어야 한다. (파견이 이 도메인의 핵심 모델인 이상, 한 사람이 동시에 두 지점에 파견될 수는 없다는 건 협의 대상이 아니다)</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
@@ -5391,19 +5391,19 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>PATCH /staff/:id</t>
+          <t>staff-assignment·staff-write·staff-change-requests·hr-authority·contract-termination·integrity-helpers·audit-log·phone-view-audit·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>STF-FN-05</t>
+          <t>STF-INV-03</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>파견 이력</t>
+          <t>퇴사 처리는 계정 비활성화와 분리될 수 없다. (권한관리 도메인 불변규칙 1 "퇴사 즉시 접근 차단"의 트리거가 바로 이 도메인의 /resign이다 — 두 도메인이 공유하는 불변식의 서로 다른 쪽 절반)</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>GET /staff/:id/assignments</t>
+          <t>staff-assignment·staff-write·staff-change-requests·hr-authority·contract-termination·integrity-helpers·audit-log·phone-view-audit·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>STF-FN-06</t>
+          <t>STF-FN-01</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>파견 발령(재배치) — 옛 지점 담당 회원 해제, 계약 종료 지점으로는 409(본사만)</t>
+          <t>직원 목록(본사 전체, 지점 관리자는 자기 지점) — 전화번호 마스킹, ?unassigned=true는 재배치 대기(ADR-STF-08)</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
@@ -5470,14 +5470,14 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>POST /staff/:id/assignments</t>
+          <t>GET /staff</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>STF-FN-07</t>
+          <t>STF-FN-02</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>퇴사 처리 — 계정 비활성화, 파견 종료, 담당 회원 해제, 인사서류 보존기한 재계산(지점 관리자. 계약 종료 지점 직원은 본사도 — ADR-STF-08)</t>
+          <t>직원 채용 — 계정·직원·첫 파견을 함께 생성(본사만)</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
@@ -5507,14 +5507,14 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>PATCH /staff/:id/resign</t>
+          <t>POST /staff</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>STF-FN-08</t>
+          <t>STF-FN-03</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>내 직원 정보</t>
+          <t>직원 상세 — 관리자가 열면 열람 기록(PHONE_VIEWED, D47)</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
@@ -5544,14 +5544,14 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>GET /staff/me</t>
+          <t>GET /staff/:id</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>STF-FN-09</t>
+          <t>STF-FN-04</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>인사 변경 신청 목록(지점 관리자는 자기 지점, 본사는 조회)</t>
+          <t>직원 정보 수정</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
@@ -5581,14 +5581,14 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>GET /staff-change-requests</t>
+          <t>PATCH /staff/:id</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>STF-FN-10</t>
+          <t>STF-FN-05</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>인사 변경 신청(직원 본인 — 연락처 등, ADR-STF-09)</t>
+          <t>파견 이력</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
@@ -5618,14 +5618,14 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>POST /staff-change-requests</t>
+          <t>GET /staff/:id/assignments</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>STF-FN-11</t>
+          <t>STF-FN-06</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>인사 변경 신청 취소(대기 중일 때 본인)</t>
+          <t>파견 발령(재배치) — 옛 지점 담당 회원 해제, 계약 종료 지점으로는 409(본사만)</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -5655,14 +5655,14 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>DELETE /staff-change-requests/:id</t>
+          <t>POST /staff/:id/assignments</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>STF-FN-12</t>
+          <t>STF-FN-07</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>인사 변경 승인 — 직원 정보에 반영, 변경 이력 기록(지점 관리자 1단계 승인)</t>
+          <t>퇴사 처리 — 계정 비활성화, 파견 종료, 담당 회원 해제, 인사서류 보존기한 재계산(지점 관리자. 계약 종료 지점 직원은 본사도 — ADR-STF-08)</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
@@ -5692,14 +5692,14 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>PATCH /staff-change-requests/:id/approve</t>
+          <t>PATCH /staff/:id/resign</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>STF-FN-13</t>
+          <t>STF-FN-08</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>인사 변경 반려(사유)</t>
+          <t>내 직원 정보</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -5729,220 +5729,236 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>PATCH /staff-change-requests/:id/reject</t>
+          <t>GET /staff/me</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
+          <t>STF-FN-09</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>인사정보관리</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>인사 변경 신청 목록(지점 관리자는 자기 지점, 본사는 조회)</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>GET /staff-change-requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>STF-FN-10</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>인사정보관리</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>인사 변경 신청(직원 본인 — 연락처 등, ADR-STF-09)</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>POST /staff-change-requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>STF-FN-11</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>인사정보관리</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>인사 변경 신청 취소(대기 중일 때 본인)</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>DELETE /staff-change-requests/:id</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>STF-FN-12</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>인사정보관리</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>인사 변경 승인 — 직원 정보에 반영, 변경 이력 기록(지점 관리자 1단계 승인)</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /staff-change-requests/:id/approve</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>STF-FN-13</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>인사정보관리</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>인사 변경 반려(사유)</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /staff-change-requests/:id/reject</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
           <t>STF-FN-14</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>인사정보관리</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>내 인사 변경 신청 목록</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>GET /staff-change-requests/mine</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>F03a</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>근태관리</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>현장별 &gt; 개인별 근태 등록 관리</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>F03b</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>근태관리</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>휴무·연차·병가 등 기록 및 일수 관리</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>F03c</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>근태관리</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>업무일지 작성 관리</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>ATT-C04</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>근태관리</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>원문 제약</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>C01(과업 기간)이 간접 제약: 다단계 연차 결재라인·정밀 법정 산정(회계연도 이월/소멸 등)은 1인 개발 범위를 넘어 단순화했다(§0).</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>ATT-INV-01</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>근태관리</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>불변규칙</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>같은 직원이 같은 날짜에 두 번 체크인할 수 없다. (ALREADY_CHECKED_IN — 하루 1레코드라는 데이터 모델 자체가 이걸 전제한다)</t>
-        </is>
-      </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>attendance-rules(동시 체크인·동시 승인·업무일지 1건·지각·KST 연차 연도)·attendance-correction·attendance-absence·attendance-branch-snapshot·kst-date·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>ATT-INV-02</t>
+          <t>F03a</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -5952,17 +5968,17 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>연차(ANNUAL) 승인 없이는 LeaveBalance.usedDays가 줄어들지 않는다. (신청만으로 차감되면 반려 시 복구 로직이 필요해지고, 그 복구가 실패하는 경로가 곧 데이터 정합성 버그로 이어진다 — 협의 대상이 아니라 설계 원칙)</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>현장별 &gt; 개인별 근태 등록 관리</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr">
@@ -5970,16 +5986,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>attendance-rules(동시 체크인·동시 승인·업무일지 1건·지각·KST 연차 연도)·attendance-correction·attendance-absence·attendance-branch-snapshot·kst-date·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G55" s="9" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>ATT-INV-03</t>
+          <t>F03b</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -5989,17 +6001,17 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>BRANCH_ADMIN·STAFF는 자기 소속 범위를 벗어난 근태·휴가·업무일지에 접근할 수 없다. (CLAUDE.md 4대 불변식 — 지점 데이터 격리)</t>
-        </is>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>휴무·연차·병가 등 기록 및 일수 관리</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
@@ -6007,16 +6019,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>attendance-rules(동시 체크인·동시 승인·업무일지 1건·지각·KST 연차 연도)·attendance-correction·attendance-absence·attendance-branch-snapshot·kst-date·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>ATT-FN-01</t>
+          <t>F03c</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -6026,34 +6034,30 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>근태 기록 조회(범위별)</t>
-        </is>
-      </c>
-      <c r="E57" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>업무일지 작성 관리</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>GET /attendance</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>ATT-FN-02</t>
+          <t>ATT-C04</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
@@ -6063,34 +6067,30 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 제약</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>관리자 근태 정정·누락일 등록 — 사유 필수, 변경 이력 기록(ADR-ATT-04)</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>C01(과업 기간)이 간접 제약: 다단계 연차 결재라인·정밀 법정 산정(회계연도 이월/소멸 등)은 1인 개발 범위를 넘어 단순화했다(§0).</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>PUT /attendance/:staffId/:date</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>ATT-FN-03</t>
+          <t>ATT-INV-01</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>결근 확정(지점 관리자의 명시적 확정)</t>
+          <t>같은 직원이 같은 날짜에 두 번 체크인할 수 없다. (ALREADY_CHECKED_IN — 하루 1레코드라는 데이터 모델 자체가 이걸 전제한다)</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
@@ -6115,19 +6115,19 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>POST /attendance/absence-confirm</t>
+          <t>attendance-rules(동시 체크인·동시 승인·업무일지 1건·지각·KST 연차 연도)·attendance-correction·attendance-absence·attendance-branch-snapshot·kst-date·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>ATT-FN-04</t>
+          <t>ATT-INV-02</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>결근 예정 미리보기(저장 안 함)</t>
+          <t>연차(ANNUAL) 승인 없이는 LeaveBalance.usedDays가 줄어들지 않는다. (신청만으로 차감되면 반려 시 복구 로직이 필요해지고, 그 복구가 실패하는 경로가 곧 데이터 정합성 버그로 이어진다 — 협의 대상이 아니라 설계 원칙)</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
@@ -6152,19 +6152,19 @@
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>GET /attendance/absence-preview</t>
+          <t>attendance-rules(동시 체크인·동시 승인·업무일지 1건·지각·KST 연차 연도)·attendance-correction·attendance-absence·attendance-branch-snapshot·kst-date·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>ATT-FN-05</t>
+          <t>ATT-INV-03</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>출근 체크 — 하루 1회, 지각 자동 판정</t>
+          <t>BRANCH_ADMIN·STAFF는 자기 소속 범위를 벗어난 근태·휴가·업무일지에 접근할 수 없다. (CLAUDE.md 4대 불변식 — 지점 데이터 격리)</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
@@ -6189,19 +6189,19 @@
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>POST /attendance/check-in</t>
+          <t>attendance-rules(동시 체크인·동시 승인·업무일지 1건·지각·KST 연차 연도)·attendance-correction·attendance-absence·attendance-branch-snapshot·kst-date·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>ATT-FN-06</t>
+          <t>ATT-FN-01</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>퇴근 체크</t>
+          <t>근태 기록 조회(범위별)</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>POST /attendance/check-out</t>
+          <t>GET /attendance</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>ATT-FN-07</t>
+          <t>ATT-FN-02</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>지점 월별 근태 요약</t>
+          <t>관리자 근태 정정·누락일 등록 — 사유 필수, 변경 이력 기록(ADR-ATT-04)</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
@@ -6268,14 +6268,14 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>GET /attendance/summary</t>
+          <t>PUT /attendance/:staffId/:date</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>ATT-FN-08</t>
+          <t>ATT-FN-03</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>휴가 신청 목록</t>
+          <t>결근 확정(지점 관리자의 명시적 확정)</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
@@ -6305,14 +6305,14 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>GET /leave-requests</t>
+          <t>POST /attendance/absence-confirm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>ATT-FN-09</t>
+          <t>ATT-FN-04</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>휴가 신청</t>
+          <t>결근 예정 미리보기(저장 안 함)</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
@@ -6342,14 +6342,14 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>POST /leave-requests</t>
+          <t>GET /attendance/absence-preview</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>ATT-FN-10</t>
+          <t>ATT-FN-05</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>휴가 승인 — 승인 시점에 연차 차감</t>
+          <t>출근 체크 — 하루 1회, 지각 자동 판정</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
@@ -6379,14 +6379,14 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>PATCH /leave-requests/:id/approve</t>
+          <t>POST /attendance/check-in</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>ATT-FN-11</t>
+          <t>ATT-FN-06</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>휴가 반려</t>
+          <t>퇴근 체크</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
@@ -6416,14 +6416,14 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>PATCH /leave-requests/:id/reject</t>
+          <t>POST /attendance/check-out</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>ATT-FN-12</t>
+          <t>ATT-FN-07</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>연차 잔여 조회</t>
+          <t>지점 월별 근태 요약</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
@@ -6453,14 +6453,14 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>GET /leave-balance/:staffId</t>
+          <t>GET /attendance/summary</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>ATT-FN-13</t>
+          <t>ATT-FN-08</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>업무일지 조회</t>
+          <t>휴가 신청 목록</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
@@ -6490,220 +6490,236 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>GET /work-logs</t>
+          <t>GET /leave-requests</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
+          <t>ATT-FN-09</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>근태관리</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>휴가 신청</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>POST /leave-requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>ATT-FN-10</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>근태관리</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>휴가 승인 — 승인 시점에 연차 차감</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>PATCH /leave-requests/:id/approve</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>ATT-FN-11</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>근태관리</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>휴가 반려</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>PATCH /leave-requests/:id/reject</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>ATT-FN-12</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>근태관리</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>연차 잔여 조회</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>GET /leave-balance/:staffId</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>ATT-FN-13</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>근태관리</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>업무일지 조회</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>GET /work-logs</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
           <t>ATT-FN-14</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>근태관리</t>
         </is>
       </c>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="D70" s="9" t="inlineStr">
+      <c r="D75" s="9" t="inlineStr">
         <is>
           <t>업무일지 작성(하루 1건)</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="G70" s="9" t="inlineStr">
+      <c r="G75" s="9" t="inlineStr">
         <is>
           <t>POST /work-logs</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>F04a</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>게시판</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>본사→현장(HQ_TO_BRANCH), 현장→이용자(BRANCH_TO_MEMBER) 별도 게시판</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>F04b</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>게시판</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>본사→현장 게시판에 교육 매뉴얼/자료 탑재</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>F04c</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>게시판</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>팀장급 직원 대상 2회 이상 대면 교육 실적 기록(산출물4 근거)</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>BRD-C04</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>게시판</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>원문 제약</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>첨부파일 실제 업로드 인프라(용량 제한·확장자 검증·스토리지)는 이번 범위에서 제외 — 부록 A-8이 이미 명시, 문서관리(1-10)와 동일하게 URL 방식으로 대체 가능.</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>BRD-INV-01</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>게시판</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>불변규칙</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>BRANCH_TO_MEMBER 게시글은 작성 지점 회원에게만 노출된다. (CLAUDE.md 지점 데이터 격리 정신의 연장 — 타 지점 공지가 새어나가면 안 됨)</t>
-        </is>
-      </c>
-      <c r="E75" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>post-facility·post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>BRD-INV-02</t>
+          <t>F04a</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -6713,17 +6729,17 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>회원(Role=MEMBER)은 직원 대상 내부 공지를 볼 수 없다. (부록 A-7이 이미 "HQ 공지는 기본적으로 직원 대상, 회원에게는 비공개가 기본값"이라고 명시 — 협의 대상이 아니라 이미 확정된 요구사항)</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>본사→현장(HQ_TO_BRANCH), 현장→이용자(BRANCH_TO_MEMBER) 별도 게시판</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -6731,16 +6747,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>post-facility·post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>BRD-FN-01</t>
+          <t>F04b</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -6750,34 +6762,30 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>게시글 목록 — 범위별 권한, 회원 공개 필터, 페이지네이션</t>
-        </is>
-      </c>
-      <c r="E77" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>본사→현장 게시판에 교육 매뉴얼/자료 탑재</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>GET /posts</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>BRD-FN-02</t>
+          <t>F04c</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -6787,34 +6795,30 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>게시글 작성 — 계약 종료 지점 차단</t>
-        </is>
-      </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>팀장급 직원 대상 2회 이상 대면 교육 실적 기록(산출물4 근거)</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>POST /posts</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>BRD-FN-03</t>
+          <t>BRD-C04</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -6824,34 +6828,30 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 제약</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>게시글 삭제(소프트, 작성자 또는 본사)</t>
-        </is>
-      </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>첨부파일 실제 업로드 인프라(용량 제한·확장자 검증·스토리지)는 이번 범위에서 제외 — 부록 A-8이 이미 명시, 문서관리(1-10)와 동일하게 URL 방식으로 대체 가능.</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>DELETE /posts/:id</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>BRD-FN-04</t>
+          <t>BRD-INV-01</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>게시글 상세 — 조회수 증가</t>
+          <t>BRANCH_TO_MEMBER 게시글은 작성 지점 회원에게만 노출된다. (CLAUDE.md 지점 데이터 격리 정신의 연장 — 타 지점 공지가 새어나가면 안 됨)</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
@@ -6876,19 +6876,19 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>GET /posts/:id</t>
+          <t>post-facility·post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>BRD-FN-05</t>
+          <t>BRD-INV-02</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>게시글 수정(작성자)</t>
+          <t>회원(Role=MEMBER)은 직원 대상 내부 공지를 볼 수 없다. (부록 A-7이 이미 "HQ 공지는 기본적으로 직원 대상, 회원에게는 비공개가 기본값"이라고 명시 — 협의 대상이 아니라 이미 확정된 요구사항)</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
@@ -6913,19 +6913,19 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>PATCH /posts/:id</t>
+          <t>post-facility·post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>BRD-FN-06</t>
+          <t>BRD-FN-01</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>첨부 붙이기 — 저장소의 실제 크기·형식 재확인, 글당 5개</t>
+          <t>게시글 목록 — 범위별 권한, 회원 공개 필터, 페이지네이션</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
@@ -6955,14 +6955,14 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>POST /posts/:id/attachments</t>
+          <t>GET /posts</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>BRD-FN-07</t>
+          <t>BRD-FN-02</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>첨부 삭제(작성자 또는 본사)</t>
+          <t>게시글 작성 — 계약 종료 지점 차단</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
@@ -6992,14 +6992,14 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>DELETE /posts/:id/attachments/:attachmentId</t>
+          <t>POST /posts</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>BRD-FN-08</t>
+          <t>BRD-FN-03</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>첨부 내려받기 URL(글을 볼 수 있는 사람, 60초)</t>
+          <t>게시글 삭제(소프트, 작성자 또는 본사)</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
@@ -7029,216 +7029,236 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>GET /posts/:id/attachments/:attachmentId/download</t>
+          <t>DELETE /posts/:id</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
+          <t>BRD-FN-04</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>게시판</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>게시글 상세 — 조회수 증가</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>GET /posts/:id</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>BRD-FN-05</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>게시판</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>게시글 수정(작성자)</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /posts/:id</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>BRD-FN-06</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>게시판</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>첨부 붙이기 — 저장소의 실제 크기·형식 재확인, 글당 5개</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>POST /posts/:id/attachments</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>BRD-FN-07</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>게시판</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>첨부 삭제(작성자 또는 본사)</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>DELETE /posts/:id/attachments/:attachmentId</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>BRD-FN-08</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>게시판</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>첨부 내려받기 URL(글을 볼 수 있는 사람, 60초)</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>GET /posts/:id/attachments/:attachmentId/download</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
           <t>BRD-FN-09</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>게시판</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>첨부 업로드 URL 발급(작성자) — 형식·크기·개수 검사, 1회용 서명 URL(ADR-BRD-04·D57)</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="G90" s="4" t="inlineStr">
         <is>
           <t>POST /posts/:id/attachments/upload-url</t>
         </is>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr">
-        <is>
-          <t>F05a</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>회원관리</t>
-        </is>
-      </c>
-      <c r="C86" s="9" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>각 현장별 회원 인적사항·프로그램 수강내역·예약및결제내역·PT잔여세션 기록</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G86" s="9" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>F05b</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>회원관리</t>
-        </is>
-      </c>
-      <c r="C87" s="9" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>현장관리자는 해당 현장 회원정보만 확인(타 현장 조회 불가)</t>
-        </is>
-      </c>
-      <c r="E87" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F87" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" s="9" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>회원관리</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>원문 품질</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>인사·회원 등 개인정보가 별도 절차 없이 노출되지 않음(전화번호 마스킹 등)</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G88" s="9" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="9" t="inlineStr">
-        <is>
-          <t>Q11</t>
-        </is>
-      </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>회원관리</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>원문 품질</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>접근 통제가 그룹별·개인별·기능별로 구체적이어야 함</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G89" s="9" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="9" t="inlineStr">
-        <is>
-          <t>MEM-C05</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>회원관리</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>원문 제약</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>C03(개인정보보호법 제26조)이 직접 제약: Member는 이 법이 다루는 개인정보 그 자체이고, 본사-지점 위탁관계 하에서 처리된다.</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G90" s="9" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>MEM-INV-01</t>
+          <t>F05a</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -7248,17 +7268,17 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>BRANCH_ADMIN·MEMBER는 자기 소속 범위를 벗어난 회원 데이터에 접근할 수 없다. (CLAUDE.md 4대 불변식 — 지점 데이터 격리. F05b 원문이 괄호로 강조한 그 요구사항)</t>
-        </is>
-      </c>
-      <c r="E91" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>각 현장별 회원 인적사항·프로그램 수강내역·예약및결제내역·PT잔여세션 기록</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
@@ -7266,16 +7286,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>member-register·member-link·branches-public·member-detail-summary·members-validation·phone-masking·phone-view-audit·contract-termination·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G91" s="9" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>MEM-INV-02</t>
+          <t>F05b</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -7285,17 +7301,17 @@
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>위탁계약이 TERMINATED된 지점에는 신규 회원을 등록할 수 없다. (CLAUDE.md 4대 불변식 — 계약 종료 지점 차단)</t>
-        </is>
-      </c>
-      <c r="E92" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>현장관리자는 해당 현장 회원정보만 확인(타 현장 조회 불가)</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
@@ -7303,16 +7319,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>member-register·member-link·branches-public·member-detail-summary·members-validation·phone-masking·phone-view-audit·contract-termination·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G92" s="9" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>MEM-INV-03</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -7322,17 +7334,17 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 품질</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>만 19세 미만 회원은 법정대리인 동의 없이 등록될 수 없다. (민법상 미성년자 단독 계약 취소가능성 — RFP가 아니라 법이 정한 것이라 협의 대상이 아님)</t>
-        </is>
-      </c>
-      <c r="E93" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>인사·회원 등 개인정보가 별도 절차 없이 노출되지 않음(전화번호 마스킹 등)</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr">
@@ -7340,16 +7352,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G93" s="9" t="inlineStr">
-        <is>
-          <t>member-register·member-link·branches-public·member-detail-summary·members-validation·phone-masking·phone-view-audit·contract-termination·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>MEM-FN-01</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -7359,34 +7367,30 @@
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 품질</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>회원 목록(지점 범위) — 페이지네이션(D43), 전화번호 마스킹(ADR-MEM-04)</t>
-        </is>
-      </c>
-      <c r="E94" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>접근 통제가 그룹별·개인별·기능별로 구체적이어야 함</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G94" s="9" t="inlineStr">
-        <is>
-          <t>GET /members</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>MEM-FN-02</t>
+          <t>MEM-C05</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -7396,34 +7400,30 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 제약</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>회원 등록 — 미성년 보호자 동의 확인, 계약 종료 지점 차단</t>
-        </is>
-      </c>
-      <c r="E95" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>C03(개인정보보호법 제26조)이 직접 제약: Member는 이 법이 다루는 개인정보 그 자체이고, 본사-지점 위탁관계 하에서 처리된다.</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr">
-        <is>
-          <t>POST /members</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>MEM-FN-03</t>
+          <t>MEM-INV-01</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
@@ -7433,12 +7433,12 @@
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>회원 상세 + 요약(수강·PT·예약) — 관리자가 열면 열람 기록(PHONE_VIEWED, D47)</t>
+          <t>BRANCH_ADMIN·MEMBER는 자기 소속 범위를 벗어난 회원 데이터에 접근할 수 없다. (CLAUDE.md 4대 불변식 — 지점 데이터 격리. F05b 원문이 괄호로 강조한 그 요구사항)</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
@@ -7448,19 +7448,19 @@
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>GET /members/:id</t>
+          <t>member-register·member-link·branches-public·member-detail-summary·members-validation·phone-masking·phone-view-audit·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>MEM-FN-04</t>
+          <t>MEM-INV-02</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>회원 정보 수정</t>
+          <t>위탁계약이 TERMINATED된 지점에는 신규 회원을 등록할 수 없다. (CLAUDE.md 4대 불변식 — 계약 종료 지점 차단)</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
@@ -7485,19 +7485,19 @@
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>PATCH /members/:id</t>
+          <t>member-register·member-link·branches-public·member-detail-summary·members-validation·phone-masking·phone-view-audit·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>MEM-FN-05</t>
+          <t>MEM-INV-03</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>수강 내역</t>
+          <t>만 19세 미만 회원은 법정대리인 동의 없이 등록될 수 없다. (민법상 미성년자 단독 계약 취소가능성 — RFP가 아니라 법이 정한 것이라 협의 대상이 아님)</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
@@ -7522,19 +7522,19 @@
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>GET /members/:id/enrollments</t>
+          <t>member-register·member-link·branches-public·member-detail-summary·members-validation·phone-masking·phone-view-audit·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>MEM-FN-06</t>
+          <t>MEM-FN-01</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>수강 등록</t>
+          <t>회원 목록(지점 범위) — 페이지네이션(D43), 전화번호 마스킹(ADR-MEM-04)</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
@@ -7564,14 +7564,14 @@
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>POST /members/:id/enrollments</t>
+          <t>GET /members</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>MEM-FN-07</t>
+          <t>MEM-FN-02</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>PT 세션권 목록</t>
+          <t>회원 등록 — 미성년 보호자 동의 확인, 계약 종료 지점 차단</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
@@ -7601,14 +7601,14 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>GET /members/:id/pt-sessions</t>
+          <t>POST /members</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>MEM-FN-08</t>
+          <t>MEM-FN-03</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>PT 세션권 등록</t>
+          <t>회원 상세 + 요약(수강·PT·예약) — 관리자가 열면 열람 기록(PHONE_VIEWED, D47)</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
@@ -7638,14 +7638,14 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>POST /members/:id/pt-sessions</t>
+          <t>GET /members/:id</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>MEM-FN-09</t>
+          <t>MEM-FN-04</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>PT 1회 차감</t>
+          <t>회원 정보 수정</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
@@ -7675,14 +7675,14 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>POST /members/:id/pt-sessions/:sessionId/use</t>
+          <t>PATCH /members/:id</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>MEM-FN-10</t>
+          <t>MEM-FN-05</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>회원 상태 전환(활성·휴면·탈퇴)</t>
+          <t>수강 내역</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
@@ -7712,14 +7712,14 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>PATCH /members/:id/status</t>
+          <t>GET /members/:id/enrollments</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>MEM-FN-11</t>
+          <t>MEM-FN-06</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>오프라인 회원 ↔ 온라인 계정 연동(공개, 회원번호+전화번호 동시 일치, 시도 제한) — 회원 웹 /link</t>
+          <t>수강 등록</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
@@ -7749,216 +7749,236 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>POST /members/link</t>
+          <t>POST /members/:id/enrollments</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
+          <t>MEM-FN-07</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>PT 세션권 목록</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>GET /members/:id/pt-sessions</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>MEM-FN-08</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>PT 세션권 등록</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>POST /members/:id/pt-sessions</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>MEM-FN-09</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>PT 1회 차감</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>POST /members/:id/pt-sessions/:sessionId/use</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>MEM-FN-10</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>회원 상태 전환(활성·휴면·탈퇴)</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>PATCH /members/:id/status</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>MEM-FN-11</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>오프라인 회원 ↔ 온라인 계정 연동(공개, 회원번호+전화번호 동시 일치, 시도 제한) — 회원 웹 /link</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>POST /members/link</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
           <t>MEM-FN-12</t>
         </is>
       </c>
-      <c r="B105" s="9" t="inlineStr">
+      <c r="B110" s="9" t="inlineStr">
         <is>
           <t>회원관리</t>
         </is>
       </c>
-      <c r="C105" s="9" t="inlineStr">
+      <c r="C110" s="9" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="D105" s="9" t="inlineStr">
+      <c r="D110" s="9" t="inlineStr">
         <is>
           <t>회원 자체 가입(공개) — 회원 웹 /signup(지점 선택은 공개 지점 목록, ADR-MEM-05)</t>
         </is>
       </c>
-      <c r="E105" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F105" s="9" t="inlineStr">
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="G105" s="9" t="inlineStr">
+      <c r="G110" s="9" t="inlineStr">
         <is>
           <t>POST /members/register</t>
         </is>
       </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>F06a</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>예약및결제</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>무/유료 프로그램 정보 게시 후 프로그램별 예약</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" s="4" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>F06b</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>예약및결제</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>모바일 결제 기능</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G107" s="4" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>F06c</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>예약및결제</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>결제내역 처리방법(RFP 원문 "추후 논의")</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G108" s="4" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>Q20</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>예약및결제</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>원문 품질</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>결제시스템은 금융·보안기관 시스템에 연계 가능 여부 확인</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G109" s="4" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t>RSV-C05</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>예약및결제</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>원문 제약</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="inlineStr">
-        <is>
-          <t>C01(과업 기간)·인프라 부재: 스케줄러가 없어 "5분 결제 미완료 자동취소", "노쇼 자동 처리"는 범위 제외(§8).</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>RSV-INV-01</t>
+          <t>F06a</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -7968,17 +7988,17 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>동일 회차의 정원을 초과해 예약이 확정될 수 없다. (영상의 "동일 좌석 중복판매 금지"와 완전히 같은 성격 — 몇 건이 초과되는 것도 협의 대상이 아니다)</t>
-        </is>
-      </c>
-      <c r="E111" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>무/유료 프로그램 정보 게시 후 프로그램별 예약</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -7986,16 +8006,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G111" s="4" t="inlineStr">
-        <is>
-          <t>reservation-capacity(실DB 동시성·결제 이중 승인)·catalog-flow·contract-termination·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>RSV-INV-02</t>
+          <t>F06b</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
@@ -8005,17 +8021,17 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>동일 회원이 같은 회차에 활성(REQUESTED/CONFIRMED) 예약을 중복으로 가질 수 없다.</t>
-        </is>
-      </c>
-      <c r="E112" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>모바일 결제 기능</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -8023,16 +8039,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G112" s="4" t="inlineStr">
-        <is>
-          <t>reservation-capacity(실DB 동시성·결제 이중 승인)·catalog-flow·contract-termination·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>RSV-INV-03</t>
+          <t>F06c</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -8042,17 +8054,17 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>위탁계약이 TERMINATED된 지점에는 신규 예약이 생성될 수 없다. (CLAUDE.md 4대 불변식 — 계약 종료 지점 차단)</t>
-        </is>
-      </c>
-      <c r="E113" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>결제내역 처리방법(RFP 원문 "추후 논의")</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
@@ -8060,16 +8072,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>reservation-capacity(실DB 동시성·결제 이중 승인)·catalog-flow·contract-termination·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>RSV-INV-04</t>
+          <t>Q20</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
@@ -8079,17 +8087,17 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 품질</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>결제 금액은 클라이언트가 아니라 서버가 Program 가격을 재조회해 결정한다. (기본적인 결제 보안 원칙 — 협의 대상 아님)</t>
-        </is>
-      </c>
-      <c r="E114" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>결제시스템은 금융·보안기관 시스템에 연계 가능 여부 확인</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
@@ -8097,16 +8105,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t>reservation-capacity(실DB 동시성·결제 이중 승인)·catalog-flow·contract-termination·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>RSV-FN-01</t>
+          <t>RSV-C05</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -8116,34 +8120,30 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 제약</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>예약 목록(범위별, 페이지네이션 D43)</t>
-        </is>
-      </c>
-      <c r="E115" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>C01(과업 기간)·인프라 부재: 스케줄러가 없어 "5분 결제 미완료 자동취소", "노쇼 자동 처리"는 범위 제외(§8).</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>GET /reservations</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>RSV-FN-02</t>
+          <t>RSV-INV-01</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>회차 예약 — 회차 잠금, 지점·계약·지난 회차(409)·중복·정원 확인</t>
+          <t>동일 회차의 정원을 초과해 예약이 확정될 수 없다. (영상의 "동일 좌석 중복판매 금지"와 완전히 같은 성격 — 몇 건이 초과되는 것도 협의 대상이 아니다)</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
@@ -8168,19 +8168,19 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>POST /reservations</t>
+          <t>reservation-capacity(실DB 동시성·결제 이중 승인)·catalog-flow·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>RSV-FN-03</t>
+          <t>RSV-INV-02</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>예약 취소 — 마감 전이면 환불</t>
+          <t>동일 회원이 같은 회차에 활성(REQUESTED/CONFIRMED) 예약을 중복으로 가질 수 없다.</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
@@ -8205,19 +8205,19 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>PATCH /reservations/:id/cancel</t>
+          <t>reservation-capacity(실DB 동시성·결제 이중 승인)·catalog-flow·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>RSV-FN-04</t>
+          <t>RSV-INV-03</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>현장 체크인(완료 처리)</t>
+          <t>위탁계약이 TERMINATED된 지점에는 신규 예약이 생성될 수 없다. (CLAUDE.md 4대 불변식 — 계약 종료 지점 차단)</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
@@ -8242,19 +8242,19 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>PATCH /reservations/:id/check-in</t>
+          <t>reservation-capacity(실DB 동시성·결제 이중 승인)·catalog-flow·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>RSV-FN-05</t>
+          <t>RSV-INV-04</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>결제 내역(매출, 기간 필터·페이지네이션)</t>
+          <t>결제 금액은 클라이언트가 아니라 서버가 Program 가격을 재조회해 결정한다. (기본적인 결제 보안 원칙 — 협의 대상 아님)</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
@@ -8279,229 +8279,241 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>GET /payments</t>
+          <t>reservation-capacity(실DB 동시성·결제 이중 승인)·catalog-flow·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
+          <t>RSV-FN-01</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>예약및결제</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>예약 목록(범위별, 페이지네이션 D43)</t>
+        </is>
+      </c>
+      <c r="E120" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>GET /reservations</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>RSV-FN-02</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>예약및결제</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>회차 예약 — 회차 잠금, 지점·계약·지난 회차(409)·중복·정원 확인</t>
+        </is>
+      </c>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>POST /reservations</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>RSV-FN-03</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>예약및결제</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>예약 취소 — 마감 전이면 환불</t>
+        </is>
+      </c>
+      <c r="E122" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /reservations/:id/cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>RSV-FN-04</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>예약및결제</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>현장 체크인(완료 처리)</t>
+        </is>
+      </c>
+      <c r="E123" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /reservations/:id/check-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>RSV-FN-05</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>예약및결제</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>결제 내역(매출, 기간 필터·페이지네이션)</t>
+        </is>
+      </c>
+      <c r="E124" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>GET /payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
           <t>RSV-FN-06</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>예약및결제</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D125" s="4" t="inlineStr">
         <is>
           <t>모의 결제 승인 → 예약 확정(대기일 때 한 번만)</t>
         </is>
       </c>
-      <c r="E120" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="G120" s="4" t="inlineStr">
+      <c r="G125" s="4" t="inlineStr">
         <is>
           <t>POST /payments/:reservationId/mock-pay</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>F07a</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>강사프로그램게시</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>각 현장의 종목별 강사·프로그램 정보 게시</t>
-        </is>
-      </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G121" s="9" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr">
-        <is>
-          <t>F07b</t>
-        </is>
-      </c>
-      <c r="B122" s="9" t="inlineStr">
-        <is>
-          <t>강사프로그램게시</t>
-        </is>
-      </c>
-      <c r="C122" s="9" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D122" s="9" t="inlineStr">
-        <is>
-          <t>종목별/시간대별/연령대별 프로그램 리스트 게시</t>
-        </is>
-      </c>
-      <c r="E122" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" s="9" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="9" t="inlineStr">
-        <is>
-          <t>PRG-C03</t>
-        </is>
-      </c>
-      <c r="B123" s="9" t="inlineStr">
-        <is>
-          <t>강사프로그램게시</t>
-        </is>
-      </c>
-      <c r="C123" s="9" t="inlineStr">
-        <is>
-          <t>원문 제약</t>
-        </is>
-      </c>
-      <c r="D123" s="9" t="inlineStr">
-        <is>
-          <t>없음(1인 개발 부담이 크지 않다고 §0이 이미 판단).</t>
-        </is>
-      </c>
-      <c r="E123" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G123" s="9" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="9" t="inlineStr">
-        <is>
-          <t>PRG-INV-01</t>
-        </is>
-      </c>
-      <c r="B124" s="9" t="inlineStr">
-        <is>
-          <t>강사프로그램게시</t>
-        </is>
-      </c>
-      <c r="C124" s="9" t="inlineStr">
-        <is>
-          <t>불변규칙</t>
-        </is>
-      </c>
-      <c r="D124" s="9" t="inlineStr">
-        <is>
-          <t>BRANCH_ADMIN은 자기 지점 강사·프로그램만 CRUD한다. (CLAUDE.md 4대 불변식 — 지점 데이터 격리)</t>
-        </is>
-      </c>
-      <c r="E124" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F124" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G124" s="9" t="inlineStr">
-        <is>
-          <t>program-integrity·catalog-flow·list-filters·branch-isolation spec</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="9" t="inlineStr">
-        <is>
-          <t>PRG-INV-02</t>
-        </is>
-      </c>
-      <c r="B125" s="9" t="inlineStr">
-        <is>
-          <t>강사프로그램게시</t>
-        </is>
-      </c>
-      <c r="C125" s="9" t="inlineStr">
-        <is>
-          <t>불변규칙</t>
-        </is>
-      </c>
-      <c r="D125" s="9" t="inlineStr">
-        <is>
-          <t>§3-2 표에 없는 프로그램 상태 전이는 성립하지 않는다. (예: ENDED에서 되돌아가는 전이는 없음 — 생애주기의 종결이라는 의미 자체가 깨짐)</t>
-        </is>
-      </c>
-      <c r="E125" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F125" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" s="9" t="inlineStr">
-        <is>
-          <t>program-integrity·catalog-flow·list-filters·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>PRG-FN-01</t>
+          <t>F07a</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
@@ -8511,34 +8523,30 @@
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>프로그램 목록</t>
-        </is>
-      </c>
-      <c r="E126" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>각 현장의 종목별 강사·프로그램 정보 게시</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G126" s="9" t="inlineStr">
-        <is>
-          <t>GET /programs</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>PRG-FN-02</t>
+          <t>F07b</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
@@ -8548,34 +8556,30 @@
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>프로그램 등록</t>
-        </is>
-      </c>
-      <c r="E127" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>종목별/시간대별/연령대별 프로그램 리스트 게시</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G127" s="9" t="inlineStr">
-        <is>
-          <t>POST /programs</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>PRG-FN-03</t>
+          <t>PRG-C03</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
@@ -8585,34 +8589,30 @@
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 제약</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>프로그램 종료(소프트)</t>
-        </is>
-      </c>
-      <c r="E128" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>없음(1인 개발 부담이 크지 않다고 §0이 이미 판단).</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G128" s="9" t="inlineStr">
-        <is>
-          <t>DELETE /programs/:id</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>PRG-FN-04</t>
+          <t>PRG-INV-01</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>프로그램 수정</t>
+          <t>BRANCH_ADMIN은 자기 지점 강사·프로그램만 CRUD한다. (CLAUDE.md 4대 불변식 — 지점 데이터 격리)</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
@@ -8637,19 +8637,19 @@
       </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>PATCH /programs/:id</t>
+          <t>program-integrity·catalog-flow·list-filters·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>PRG-FN-05</t>
+          <t>PRG-INV-02</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>회차 목록·잔여 좌석</t>
+          <t>§3-2 표에 없는 프로그램 상태 전이는 성립하지 않는다. (예: ENDED에서 되돌아가는 전이는 없음 — 생애주기의 종결이라는 의미 자체가 깨짐)</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
@@ -8674,19 +8674,19 @@
       </c>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>GET /programs/:id/slots</t>
+          <t>program-integrity·catalog-flow·list-filters·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>PRG-FN-06</t>
+          <t>PRG-FN-01</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>회차 등록</t>
+          <t>프로그램 목록</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
@@ -8716,14 +8716,14 @@
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>POST /programs/:id/slots</t>
+          <t>GET /programs</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>PRG-FN-07</t>
+          <t>PRG-FN-02</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>프로그램 상태 전이(준비중·진행중·휴강·종료) — 영향받는 예약 반환</t>
+          <t>프로그램 등록</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
@@ -8753,14 +8753,14 @@
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
-          <t>PATCH /programs/:id/status</t>
+          <t>POST /programs</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>PRG-FN-08</t>
+          <t>PRG-FN-03</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>강사 목록</t>
+          <t>프로그램 종료(소프트)</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
@@ -8790,14 +8790,14 @@
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
-          <t>GET /instructors</t>
+          <t>DELETE /programs/:id</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>PRG-FN-09</t>
+          <t>PRG-FN-04</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>강사 등록</t>
+          <t>프로그램 수정</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
@@ -8827,14 +8827,14 @@
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
-          <t>POST /instructors</t>
+          <t>PATCH /programs/:id</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>PRG-FN-10</t>
+          <t>PRG-FN-05</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>강사 비활성화</t>
+          <t>회차 목록·잔여 좌석</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
@@ -8864,14 +8864,14 @@
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>DELETE /instructors/:id</t>
+          <t>GET /programs/:id/slots</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>PRG-FN-11</t>
+          <t>PRG-FN-06</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>강사 수정</t>
+          <t>회차 등록</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
@@ -8901,220 +8901,236 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>PATCH /instructors/:id</t>
+          <t>POST /programs/:id/slots</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
+          <t>PRG-FN-07</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>강사프로그램게시</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>프로그램 상태 전이(준비중·진행중·휴강·종료) — 영향받는 예약 반환</t>
+        </is>
+      </c>
+      <c r="E137" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>PATCH /programs/:id/status</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>PRG-FN-08</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>강사프로그램게시</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>강사 목록</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>GET /instructors</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>PRG-FN-09</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>강사프로그램게시</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>강사 등록</t>
+        </is>
+      </c>
+      <c r="E139" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G139" s="9" t="inlineStr">
+        <is>
+          <t>POST /instructors</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>PRG-FN-10</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>강사프로그램게시</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>강사 비활성화</t>
+        </is>
+      </c>
+      <c r="E140" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>DELETE /instructors/:id</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>PRG-FN-11</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>강사프로그램게시</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>강사 수정</t>
+        </is>
+      </c>
+      <c r="E141" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="inlineStr">
+        <is>
+          <t>PATCH /instructors/:id</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
           <t>PRG-FN-12</t>
         </is>
       </c>
-      <c r="B137" s="9" t="inlineStr">
+      <c r="B142" s="9" t="inlineStr">
         <is>
           <t>강사프로그램게시</t>
         </is>
       </c>
-      <c r="C137" s="9" t="inlineStr">
+      <c r="C142" s="9" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="D137" s="9" t="inlineStr">
+      <c r="D142" s="9" t="inlineStr">
         <is>
           <t>지점별 프로그램 상태 요약</t>
         </is>
       </c>
-      <c r="E137" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F137" s="9" t="inlineStr">
+      <c r="E142" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="G137" s="9" t="inlineStr">
+      <c r="G142" s="9" t="inlineStr">
         <is>
           <t>GET /branches/:branchId/programs/summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t>F08a</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>혼잡도관리</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="inlineStr">
-        <is>
-          <t>시설별 이용현황·혼잡도를 5개 항목으로 나눠 게시</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G138" s="4" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>F08b</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>혼잡도관리</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="inlineStr">
-        <is>
-          <t>실시간 혹은 최대 30분 이내 이용현황 반영</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G139" s="4" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>FAC-C03</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>혼잡도관리</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>원문 제약</t>
-        </is>
-      </c>
-      <c r="D140" s="4" t="inlineStr">
-        <is>
-          <t>하드웨어(IoT 센서·CCTV) 기반 계측 불가 — §0이 이미 명시.</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G140" s="4" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>FAC-C04</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>혼잡도관리</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>원문 제약</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="inlineStr">
-        <is>
-          <t>스케줄러 인프라 없음(Phase 2 QR·자동계산이 이 제약으로 범위 제외됨).</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G141" s="4" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="4" t="inlineStr">
-        <is>
-          <t>FAC-INV-01</t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="inlineStr">
-        <is>
-          <t>혼잡도관리</t>
-        </is>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>불변규칙</t>
-        </is>
-      </c>
-      <c r="D142" s="4" t="inlineStr">
-        <is>
-          <t>BRANCH_ADMIN은 자기 지점 시설만 관리한다. (CLAUDE.md 4대 불변식 — 지점 데이터 격리)</t>
-        </is>
-      </c>
-      <c r="E142" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G142" s="4" t="inlineStr">
-        <is>
-          <t>facility-lifecycle·catalog-flow·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>FAC-INV-02</t>
+          <t>F08a</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -9124,17 +9140,17 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>정원(capacity)은 0이 될 수 없다. (0으로 나누면 계산 자체가 성립하지 않음 — 협의 대상이 아니라 수학적 제약)</t>
-        </is>
-      </c>
-      <c r="E143" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>시설별 이용현황·혼잡도를 5개 항목으로 나눠 게시</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
@@ -9142,16 +9158,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G143" s="4" t="inlineStr">
-        <is>
-          <t>facility-lifecycle·catalog-flow·contract-termination·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>FAC-FN-01</t>
+          <t>F08b</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -9161,34 +9173,30 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>시설 목록 + 현재 혼잡도</t>
-        </is>
-      </c>
-      <c r="E144" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>실시간 혹은 최대 30분 이내 이용현황 반영</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G144" s="4" t="inlineStr">
-        <is>
-          <t>GET /facilities</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>FAC-FN-02</t>
+          <t>FAC-C03</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -9198,34 +9206,30 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 제약</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>시설 등록</t>
-        </is>
-      </c>
-      <c r="E145" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>하드웨어(IoT 센서·CCTV) 기반 계측 불가 — §0이 이미 명시.</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G145" s="4" t="inlineStr">
-        <is>
-          <t>POST /facilities</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>FAC-FN-03</t>
+          <t>FAC-C04</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
@@ -9235,236 +9239,252 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 제약</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>시설 수정·비활성화</t>
-        </is>
-      </c>
-      <c r="E146" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>스케줄러 인프라 없음(Phase 2 QR·자동계산이 이 제약으로 범위 제외됨).</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G146" s="4" t="inlineStr">
-        <is>
-          <t>PATCH /facilities/:id</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
+          <t>FAC-INV-01</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>혼잡도관리</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>불변규칙</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>BRANCH_ADMIN은 자기 지점 시설만 관리한다. (CLAUDE.md 4대 불변식 — 지점 데이터 격리)</t>
+        </is>
+      </c>
+      <c r="E147" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>facility-lifecycle·catalog-flow·contract-termination·branch-isolation spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>FAC-INV-02</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>혼잡도관리</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>불변규칙</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>정원(capacity)은 0이 될 수 없다. (0으로 나누면 계산 자체가 성립하지 않음 — 협의 대상이 아니라 수학적 제약)</t>
+        </is>
+      </c>
+      <c r="E148" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>facility-lifecycle·catalog-flow·contract-termination·branch-isolation spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>FAC-FN-01</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>혼잡도관리</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>시설 목록 + 현재 혼잡도</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>GET /facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>FAC-FN-02</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>혼잡도관리</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>시설 등록</t>
+        </is>
+      </c>
+      <c r="E150" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>POST /facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>FAC-FN-03</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>혼잡도관리</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>시설 수정·비활성화</t>
+        </is>
+      </c>
+      <c r="E151" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /facilities/:id</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
           <t>FAC-FN-04</t>
         </is>
       </c>
-      <c r="B147" s="4" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>혼잡도관리</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="D152" s="4" t="inlineStr">
         <is>
           <t>혼잡도 수동 보정(인원 입력 → 5단계 자동 계산)</t>
         </is>
       </c>
-      <c r="E147" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
+      <c r="E152" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="G147" s="4" t="inlineStr">
+      <c r="G152" s="4" t="inlineStr">
         <is>
           <t>POST /facilities/:id/congestion/manual</t>
         </is>
       </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="9" t="inlineStr">
-        <is>
-          <t>F10a</t>
-        </is>
-      </c>
-      <c r="B148" s="9" t="inlineStr">
-        <is>
-          <t>자원문서관리</t>
-        </is>
-      </c>
-      <c r="C148" s="9" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D148" s="9" t="inlineStr">
-        <is>
-          <t>지점별 자산(운동기구·안전설비·비품)을 등록·조회·상태 관리</t>
-        </is>
-      </c>
-      <c r="E148" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F148" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G148" s="9" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="9" t="inlineStr">
-        <is>
-          <t>F10b</t>
-        </is>
-      </c>
-      <c r="B149" s="9" t="inlineStr">
-        <is>
-          <t>자원문서관리</t>
-        </is>
-      </c>
-      <c r="C149" s="9" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D149" s="9" t="inlineStr">
-        <is>
-          <t>자산 취득가액 기준 고정자산/소모품 자동 판정(100만원 초과 기준)</t>
-        </is>
-      </c>
-      <c r="E149" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F149" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G149" s="9" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="9" t="inlineStr">
-        <is>
-          <t>F10c</t>
-        </is>
-      </c>
-      <c r="B150" s="9" t="inlineStr">
-        <is>
-          <t>자원문서관리</t>
-        </is>
-      </c>
-      <c r="C150" s="9" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D150" s="9" t="inlineStr">
-        <is>
-          <t>계약서·인사서류 등 문서를 지점(또는 전사)에 연결해 보관, 카테고리별 보존기한 관리</t>
-        </is>
-      </c>
-      <c r="E150" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F150" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G150" s="9" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="9" t="inlineStr">
-        <is>
-          <t>F10d</t>
-        </is>
-      </c>
-      <c r="B151" s="9" t="inlineStr">
-        <is>
-          <t>자원문서관리</t>
-        </is>
-      </c>
-      <c r="C151" s="9" t="inlineStr">
-        <is>
-          <t>원문 기능</t>
-        </is>
-      </c>
-      <c r="D151" s="9" t="inlineStr">
-        <is>
-          <t>보존기한 임박 문서 목록</t>
-        </is>
-      </c>
-      <c r="E151" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F151" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G151" s="9" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="9" t="inlineStr">
-        <is>
-          <t>RES-C05</t>
-        </is>
-      </c>
-      <c r="B152" s="9" t="inlineStr">
-        <is>
-          <t>자원문서관리</t>
-        </is>
-      </c>
-      <c r="C152" s="9" t="inlineStr">
-        <is>
-          <t>원문 제약</t>
-        </is>
-      </c>
-      <c r="D152" s="9" t="inlineStr">
-        <is>
-          <t>실제 파일 업로드 인프라(스토리지·용량 제한·바이러스 검사) 없음 — fileUrl은 문자열만 받는다(부록 A-1, §7이 이미 범위 제외).</t>
-        </is>
-      </c>
-      <c r="E152" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F152" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G152" s="9" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>RES-C06</t>
+          <t>F10a</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -9474,12 +9494,12 @@
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
-          <t>원문 제약</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>회계 모듈이 없어 감가상각 정밀 계산(월할·자산군별 상각률)을 연동할 재무제표가 없음 — 부록 A-1이 이미 "연 1회 스냅샷" 수준으로 단순화하기로 조정했었고, 그마저도 2026-09-20에 완전히 범위 제외됨(§7).</t>
+          <t>지점별 자산(운동기구·안전설비·비품)을 등록·조회·상태 관리</t>
         </is>
       </c>
       <c r="E153" s="9" t="inlineStr">
@@ -9497,7 +9517,7 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>RES-INV-01</t>
+          <t>F10b</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
@@ -9507,17 +9527,17 @@
       </c>
       <c r="C154" s="9" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>BRANCH_ADMIN은 자기 지점 자산·문서만 CRUD한다. (CLAUDE.md 4대 불변식 — 지점 데이터 격리)</t>
-        </is>
-      </c>
-      <c r="E154" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>자산 취득가액 기준 고정자산/소모품 자동 판정(100만원 초과 기준)</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F154" s="9" t="inlineStr">
@@ -9525,16 +9545,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G154" s="9" t="inlineStr">
-        <is>
-          <t>asset-rules(동시 채번·자동 판정·수량·전이 경합)·document-rules·document-retention·contract-termination·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G154" s="9" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>RES-INV-02</t>
+          <t>F10c</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -9544,17 +9560,17 @@
       </c>
       <c r="C155" s="9" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>HR_RECORD(인사서류)는 대상 직원(relatedStaffId)을 반드시 지정해야 한다. (누구의 서류인지 모르는 인사서류는 존재 의미가 없음 — 부록 A-3이 이미 이렇게 설계)</t>
-        </is>
-      </c>
-      <c r="E155" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>계약서·인사서류 등 문서를 지점(또는 전사)에 연결해 보관, 카테고리별 보존기한 관리</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F155" s="9" t="inlineStr">
@@ -9562,16 +9578,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G155" s="9" t="inlineStr">
-        <is>
-          <t>asset-rules(동시 채번·자동 판정·수량·전이 경합)·document-rules·document-retention·contract-termination·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G155" s="9" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>RES-INV-03</t>
+          <t>F10d</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
@@ -9581,17 +9593,17 @@
       </c>
       <c r="C156" s="9" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 기능</t>
         </is>
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>문서 삭제는 SUPER_ADMIN 전용이다. (계약서·인사서류는 법적 증빙 성격이라 지점 관리자가 임의로 지울 수 없어야 함 — 부록 A-7)</t>
-        </is>
-      </c>
-      <c r="E156" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>보존기한 임박 문서 목록</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F156" s="9" t="inlineStr">
@@ -9599,16 +9611,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G156" s="9" t="inlineStr">
-        <is>
-          <t>asset-rules(동시 채번·자동 판정·수량·전이 경합)·document-rules·document-retention·contract-termination·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G156" s="9" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>RES-INV-04</t>
+          <t>RES-C05</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
@@ -9618,17 +9626,17 @@
       </c>
       <c r="C157" s="9" t="inlineStr">
         <is>
-          <t>불변규칙</t>
+          <t>원문 제약</t>
         </is>
       </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
-          <t>문서는 소프트 삭제(D9)를 따른다. (계약·인사 분쟁 시 감사 목적 복구 가능성 — 부록 A-6)</t>
-        </is>
-      </c>
-      <c r="E157" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>실제 파일 업로드 인프라(스토리지·용량 제한·바이러스 검사) 없음 — fileUrl은 문자열만 받는다(부록 A-1, §7이 이미 범위 제외).</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F157" s="9" t="inlineStr">
@@ -9636,16 +9644,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G157" s="9" t="inlineStr">
-        <is>
-          <t>asset-rules(동시 채번·자동 판정·수량·전이 경합)·document-rules·document-retention·contract-termination·branch-isolation spec</t>
-        </is>
-      </c>
+      <c r="G157" s="9" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>RES-FN-01</t>
+          <t>RES-C06</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
@@ -9655,34 +9659,30 @@
       </c>
       <c r="C158" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>원문 제약</t>
         </is>
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>자산·비품 목록(페이지네이션 D43)</t>
-        </is>
-      </c>
-      <c r="E158" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+          <t>회계 모듈이 없어 감가상각 정밀 계산(월할·자산군별 상각률)을 연동할 재무제표가 없음 — 부록 A-1이 이미 "연 1회 스냅샷" 수준으로 단순화하기로 조정했었고, 그마저도 2026-09-20에 완전히 범위 제외됨(§7).</t>
+        </is>
+      </c>
+      <c r="E158" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G158" s="9" t="inlineStr">
-        <is>
-          <t>GET /assets</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G158" s="9" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>RES-FN-02</t>
+          <t>RES-INV-01</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="C159" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>자산 등록 — 자산코드 자동 채번, 계약 종료 지점 차단</t>
+          <t>BRANCH_ADMIN은 자기 지점 자산·문서만 CRUD한다. (CLAUDE.md 4대 불변식 — 지점 데이터 격리)</t>
         </is>
       </c>
       <c r="E159" s="10" t="inlineStr">
@@ -9707,19 +9707,19 @@
       </c>
       <c r="F159" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>POST /assets</t>
+          <t>asset-rules(동시 채번·자동 판정·수량·전이 경합)·document-rules·document-retention·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>RES-FN-03</t>
+          <t>RES-INV-02</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
@@ -9729,12 +9729,12 @@
       </c>
       <c r="C160" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>자산 정보 수정</t>
+          <t>HR_RECORD(인사서류)는 대상 직원(relatedStaffId)을 반드시 지정해야 한다. (누구의 서류인지 모르는 인사서류는 존재 의미가 없음 — 부록 A-3이 이미 이렇게 설계)</t>
         </is>
       </c>
       <c r="E160" s="10" t="inlineStr">
@@ -9744,19 +9744,19 @@
       </c>
       <c r="F160" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G160" s="9" t="inlineStr">
         <is>
-          <t>PATCH /assets/:id</t>
+          <t>asset-rules(동시 채번·자동 판정·수량·전이 경합)·document-rules·document-retention·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>RES-FN-04</t>
+          <t>RES-INV-03</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="C161" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>자산 상태 전이(사용·수리·폐기 등)</t>
+          <t>문서 삭제는 SUPER_ADMIN 전용이다. (계약서·인사서류는 법적 증빙 성격이라 지점 관리자가 임의로 지울 수 없어야 함 — 부록 A-7)</t>
         </is>
       </c>
       <c r="E161" s="10" t="inlineStr">
@@ -9781,19 +9781,19 @@
       </c>
       <c r="F161" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
-          <t>PATCH /assets/:id/status</t>
+          <t>asset-rules(동시 채번·자동 판정·수량·전이 경합)·document-rules·document-retention·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>RES-FN-05</t>
+          <t>RES-INV-04</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -9803,12 +9803,12 @@
       </c>
       <c r="C162" s="9" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>불변규칙</t>
         </is>
       </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>문서 목록</t>
+          <t>문서는 소프트 삭제(D9)를 따른다. (계약·인사 분쟁 시 감사 목적 복구 가능성 — 부록 A-6)</t>
         </is>
       </c>
       <c r="E162" s="10" t="inlineStr">
@@ -9818,19 +9818,19 @@
       </c>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G162" s="9" t="inlineStr">
         <is>
-          <t>GET /documents</t>
+          <t>asset-rules(동시 채번·자동 판정·수량·전이 경합)·document-rules·document-retention·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>RES-FN-06</t>
+          <t>RES-FN-01</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>문서 등록 — 계약서 보존기한 필수, 계약 종료 지점 차단</t>
+          <t>자산·비품 목록(페이지네이션 D43)</t>
         </is>
       </c>
       <c r="E163" s="10" t="inlineStr">
@@ -9860,14 +9860,14 @@
       </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
-          <t>POST /documents</t>
+          <t>GET /assets</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>RES-FN-07</t>
+          <t>RES-FN-02</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>문서 삭제(소프트, 본사)</t>
+          <t>자산 등록 — 자산코드 자동 채번, 계약 종료 지점 차단</t>
         </is>
       </c>
       <c r="E164" s="10" t="inlineStr">
@@ -9897,14 +9897,14 @@
       </c>
       <c r="G164" s="9" t="inlineStr">
         <is>
-          <t>DELETE /documents/:id</t>
+          <t>POST /assets</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>RES-FN-08</t>
+          <t>RES-FN-03</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
-          <t>문서 상세</t>
+          <t>자산 정보 수정</t>
         </is>
       </c>
       <c r="E165" s="10" t="inlineStr">
@@ -9934,236 +9934,236 @@
       </c>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>GET /documents/:id</t>
+          <t>PATCH /assets/:id</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
+          <t>RES-FN-04</t>
+        </is>
+      </c>
+      <c r="B166" s="9" t="inlineStr">
+        <is>
+          <t>자원문서관리</t>
+        </is>
+      </c>
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="inlineStr">
+        <is>
+          <t>자산 상태 전이(사용·수리·폐기 등)</t>
+        </is>
+      </c>
+      <c r="E166" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F166" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G166" s="9" t="inlineStr">
+        <is>
+          <t>PATCH /assets/:id/status</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>RES-FN-05</t>
+        </is>
+      </c>
+      <c r="B167" s="9" t="inlineStr">
+        <is>
+          <t>자원문서관리</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>문서 목록</t>
+        </is>
+      </c>
+      <c r="E167" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F167" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G167" s="9" t="inlineStr">
+        <is>
+          <t>GET /documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="9" t="inlineStr">
+        <is>
+          <t>RES-FN-06</t>
+        </is>
+      </c>
+      <c r="B168" s="9" t="inlineStr">
+        <is>
+          <t>자원문서관리</t>
+        </is>
+      </c>
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="inlineStr">
+        <is>
+          <t>문서 등록 — 계약서 보존기한 필수, 계약 종료 지점 차단</t>
+        </is>
+      </c>
+      <c r="E168" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F168" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G168" s="9" t="inlineStr">
+        <is>
+          <t>POST /documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>RES-FN-07</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="inlineStr">
+        <is>
+          <t>자원문서관리</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>문서 삭제(소프트, 본사)</t>
+        </is>
+      </c>
+      <c r="E169" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="inlineStr">
+        <is>
+          <t>DELETE /documents/:id</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>RES-FN-08</t>
+        </is>
+      </c>
+      <c r="B170" s="9" t="inlineStr">
+        <is>
+          <t>자원문서관리</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="inlineStr">
+        <is>
+          <t>문서 상세</t>
+        </is>
+      </c>
+      <c r="E170" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F170" s="9" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G170" s="9" t="inlineStr">
+        <is>
+          <t>GET /documents/:id</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
           <t>RES-FN-09</t>
         </is>
       </c>
-      <c r="B166" s="9" t="inlineStr">
+      <c r="B171" s="9" t="inlineStr">
         <is>
           <t>자원문서관리</t>
         </is>
       </c>
-      <c r="C166" s="9" t="inlineStr">
+      <c r="C171" s="9" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="D166" s="9" t="inlineStr">
+      <c r="D171" s="9" t="inlineStr">
         <is>
           <t>보존기한 임박 문서(본사)</t>
         </is>
       </c>
-      <c r="E166" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F166" s="9" t="inlineStr">
+      <c r="E171" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F171" s="9" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="G166" s="9" t="inlineStr">
+      <c r="G171" s="9" t="inlineStr">
         <is>
           <t>GET /documents/retention-alerts</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>COM-FN-01</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>헬스체크(DB 미경유)</t>
-        </is>
-      </c>
-      <c r="E167" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F167" s="4" t="inlineStr">
-        <is>
-          <t>불필요</t>
-        </is>
-      </c>
-      <c r="G167" s="4" t="inlineStr">
-        <is>
-          <t>GET /health</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="4" t="inlineStr">
-        <is>
-          <t>COM-FN-02</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>변경 이력 조회(본사) — 역할 전환·퇴사·파견 발령·파견 종료·전화번호 열람(D44·D47)</t>
-        </is>
-      </c>
-      <c r="E168" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F168" s="4" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G168" s="4" t="inlineStr">
-        <is>
-          <t>GET /audit-logs</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="4" t="inlineStr">
-        <is>
-          <t>COM-FN-03</t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>공개 지점 목록(이름·지역만, 계약 종료 지점 제외) — 회원 웹 가입용(ADR-MEM-05)</t>
-        </is>
-      </c>
-      <c r="E169" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F169" s="4" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G169" s="4" t="inlineStr">
-        <is>
-          <t>GET /branches/public</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t>COM-FN-04</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>지점 목록(계약 정보 포함)</t>
-        </is>
-      </c>
-      <c r="E170" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F170" s="4" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G170" s="4" t="inlineStr">
-        <is>
-          <t>GET /branches</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>COM-FN-05</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>계약 상태 변경(본사) — TERMINATED 전이 시 진행 중 파견 종료·재배치 대기 반환(ADR-STF-07)</t>
-        </is>
-      </c>
-      <c r="E171" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F171" s="4" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="G171" s="4" t="inlineStr">
-        <is>
-          <t>PATCH /branches/:branchId/contract-status</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>COM-FN-06</t>
+          <t>COM-FN-01</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>지점 운영 실적 — 최근 3개월 매출·예약·완료·신규 회원(KST 월 기준)</t>
+          <t>헬스체크(DB 미경유)</t>
         </is>
       </c>
       <c r="E172" s="10" t="inlineStr">
@@ -10188,19 +10188,19 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>불필요</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>GET /branches/:branchId/performance</t>
+          <t>GET /health</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>COM-FN-07</t>
+          <t>COM-FN-02</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>업무지원 요청 등록(지점 관리자 → 본사, D56)</t>
+          <t>변경 이력 조회(본사) — 역할 전환·퇴사·파견 발령·파견 종료·전화번호 열람(D44·D47)</t>
         </is>
       </c>
       <c r="E173" s="10" t="inlineStr">
@@ -10230,14 +10230,14 @@
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>POST /support-requests</t>
+          <t>GET /audit-logs</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>COM-FN-08</t>
+          <t>COM-FN-03</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>업무지원 요청 목록(지점은 자기 지점, 본사는 전체)</t>
+          <t>공개 지점 목록(이름·지역만, 계약 종료 지점 제외) — 회원 웹 가입용(ADR-MEM-05)</t>
         </is>
       </c>
       <c r="E174" s="10" t="inlineStr">
@@ -10267,14 +10267,14 @@
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>GET /support-requests</t>
+          <t>GET /branches/public</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>COM-FN-09</t>
+          <t>COM-FN-04</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>업무지원 요청 상세</t>
+          <t>지점 목록(계약 정보 포함)</t>
         </is>
       </c>
       <c r="E175" s="10" t="inlineStr">
@@ -10299,239 +10299,424 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>GET /support-requests/:id</t>
+          <t>GET /branches</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
+          <t>COM-FN-05</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>계약 상태 변경(본사) — TERMINATED 전이 시 진행 중 파견 종료·재배치 대기 반환(ADR-STF-07)</t>
+        </is>
+      </c>
+      <c r="E176" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /branches/:branchId/contract-status</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>COM-FN-06</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>지점 운영 실적 — 최근 3개월 매출·예약·완료·신규 회원(KST 월 기준)</t>
+        </is>
+      </c>
+      <c r="E177" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>GET /branches/:branchId/performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>COM-FN-07</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>업무지원 요청 등록(지점 관리자 → 본사, D56)</t>
+        </is>
+      </c>
+      <c r="E178" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>POST /support-requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>COM-FN-08</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>업무지원 요청 목록(지점은 자기 지점, 본사는 전체)</t>
+        </is>
+      </c>
+      <c r="E179" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>GET /support-requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>COM-FN-09</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>업무지원 요청 상세</t>
+        </is>
+      </c>
+      <c r="E180" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>GET /support-requests/:id</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
           <t>COM-FN-10</t>
         </is>
       </c>
-      <c r="B176" s="4" t="inlineStr">
+      <c r="B181" s="4" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C181" s="4" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="D176" s="4" t="inlineStr">
+      <c r="D181" s="4" t="inlineStr">
         <is>
           <t>업무지원 요청 처리 상태 변경(본사)</t>
         </is>
       </c>
-      <c r="E176" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr">
+      <c r="E181" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="G176" s="4" t="inlineStr">
+      <c r="G181" s="4" t="inlineStr">
         <is>
           <t>PATCH /support-requests/:id/status</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="9" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="9" t="inlineStr">
         <is>
           <t>GAP-01</t>
         </is>
       </c>
-      <c r="B177" s="9" t="inlineStr">
+      <c r="B182" s="9" t="inlineStr">
         <is>
           <t>RFP 공통</t>
         </is>
       </c>
-      <c r="C177" s="9" t="inlineStr">
+      <c r="C182" s="9" t="inlineStr">
         <is>
           <t>미구현</t>
         </is>
       </c>
-      <c r="D177" s="9" t="inlineStr">
+      <c r="D182" s="9" t="inlineStr">
         <is>
           <t>사용자별·프로그램별 세부 권한(입력·수정·삭제·조회·출력), 개인별·기능별 접근 통제 — 부분 — 역할 4개 + 지점 격리로 조정(D1). 출력은 회원·근태 요약·결제 CSV를 역할 기준으로만(D54), 인쇄용 화면 없음</t>
         </is>
       </c>
-      <c r="E177" s="11" t="inlineStr">
+      <c r="E182" s="11" t="inlineStr">
         <is>
           <t>부분</t>
         </is>
       </c>
-      <c r="F177" s="9" t="inlineStr">
+      <c r="F182" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G177" s="9" t="inlineStr">
+      <c r="G182" s="9" t="inlineStr">
         <is>
           <t>권한관리(1-1 #1)·UI 보안(1-2 #7)</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="9" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="9" t="inlineStr">
         <is>
           <t>GAP-02</t>
         </is>
       </c>
-      <c r="B178" s="9" t="inlineStr">
+      <c r="B183" s="9" t="inlineStr">
         <is>
           <t>RFP 공통</t>
         </is>
       </c>
-      <c r="C178" s="9" t="inlineStr">
+      <c r="C183" s="9" t="inlineStr">
         <is>
           <t>미구현</t>
         </is>
       </c>
-      <c r="D178" s="9" t="inlineStr">
+      <c r="D183" s="9" t="inlineStr">
         <is>
           <t>메모리 평균 85% 이하 유지 — 부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
         </is>
       </c>
-      <c r="E178" s="11" t="inlineStr">
+      <c r="E183" s="11" t="inlineStr">
         <is>
           <t>부분</t>
         </is>
       </c>
-      <c r="F178" s="9" t="inlineStr">
+      <c r="F183" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G178" s="9" t="inlineStr">
+      <c r="G183" s="9" t="inlineStr">
         <is>
           <t>시스템가용성(1-1 #10)</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="9" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="9" t="inlineStr">
         <is>
           <t>GAP-03</t>
         </is>
       </c>
-      <c r="B179" s="9" t="inlineStr">
+      <c r="B184" s="9" t="inlineStr">
         <is>
           <t>RFP 공통</t>
         </is>
       </c>
-      <c r="C179" s="9" t="inlineStr">
+      <c r="C184" s="9" t="inlineStr">
         <is>
           <t>미구현</t>
         </is>
       </c>
-      <c r="D179" s="9" t="inlineStr">
+      <c r="D184" s="9" t="inlineStr">
         <is>
           <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인 — 부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
         </is>
       </c>
-      <c r="E179" s="11" t="inlineStr">
+      <c r="E184" s="11" t="inlineStr">
         <is>
           <t>부분</t>
         </is>
       </c>
-      <c r="F179" s="9" t="inlineStr">
+      <c r="F184" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G179" s="9" t="inlineStr">
+      <c r="G184" s="9" t="inlineStr">
         <is>
           <t>UI 보안(1-2 #7)</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="9" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="9" t="inlineStr">
         <is>
           <t>GAP-04</t>
         </is>
       </c>
-      <c r="B180" s="9" t="inlineStr">
+      <c r="B185" s="9" t="inlineStr">
         <is>
           <t>RFP 공통</t>
         </is>
       </c>
-      <c r="C180" s="9" t="inlineStr">
+      <c r="C185" s="9" t="inlineStr">
         <is>
           <t>미구현</t>
         </is>
       </c>
-      <c r="D180" s="9" t="inlineStr">
+      <c r="D185" s="9" t="inlineStr">
         <is>
           <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료 — 부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
         </is>
       </c>
-      <c r="E180" s="11" t="inlineStr">
+      <c r="E185" s="11" t="inlineStr">
         <is>
           <t>부분</t>
         </is>
       </c>
-      <c r="F180" s="9" t="inlineStr">
+      <c r="F185" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G180" s="9" t="inlineStr">
+      <c r="G185" s="9" t="inlineStr">
         <is>
           <t>과업4·산출물5(p.4·p.7)</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="9" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="9" t="inlineStr">
         <is>
           <t>GAP-05</t>
         </is>
       </c>
-      <c r="B181" s="9" t="inlineStr">
+      <c r="B186" s="9" t="inlineStr">
         <is>
           <t>RFP 공통</t>
         </is>
       </c>
-      <c r="C181" s="9" t="inlineStr">
+      <c r="C186" s="9" t="inlineStr">
         <is>
           <t>미구현</t>
         </is>
       </c>
-      <c r="D181" s="9" t="inlineStr">
+      <c r="D186" s="9" t="inlineStr">
         <is>
           <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
         </is>
       </c>
-      <c r="E181" s="11" t="inlineStr">
+      <c r="E186" s="11" t="inlineStr">
         <is>
           <t>부분</t>
         </is>
       </c>
-      <c r="F181" s="9" t="inlineStr">
+      <c r="F186" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G181" s="9" t="inlineStr">
+      <c r="G186" s="9" t="inlineStr">
         <is>
           <t>산출물4(p.7)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A11:G181"/>
+  <autoFilter ref="A11:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11839,7 +12024,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>D60(D1 대체) 1단계 — 서버가 기능×동작 권한을 역할 기본값·개인 예외로 판정(log/146). 본사가 바꾸는 화면·API는 2단계</t>
+          <t>D60(D1 대체) — 서버가 기능×동작 권한을 역할 기본값·개인 예외로 판정(log/146), 본사가 권한 관리 화면·직원 상세에서 바꾼다(log/147). 관리자 웹이 권한대로 버튼을 숨기는 3단계 뒤 구현 판정</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13239,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>역할·지점 단위 + 서버의 역할별·개인별·기능별 판정(D60 1단계, log/146). 설정 화면은 2단계</t>
+          <t>역할·지점 단위 + 서버의 역할별·개인별·기능별 판정과 본사 설정 화면(D60, log/146·147). 화면 숨김은 3단계</t>
         </is>
       </c>
     </row>
@@ -13745,7 +13930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14099,7 +14284,7 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>permission-matrix·permission-coverage·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
+          <t>permission-matrix·permission-coverage·permission-admin·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
         </is>
       </c>
     </row>
@@ -14310,7 +14495,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>직원 계정과 역할 목록(본사)</t>
+          <t>(설명 없음)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -14320,7 +14505,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>/permissions/staff</t>
+          <t>/permissions/catalog</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -14342,17 +14527,17 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>직원 역할 전환(지점 관리자 ↔ 직원, 본사)</t>
+          <t>(설명 없음)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>/permissions/staff/:staffId/role</t>
+          <t>/permissions/roles</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -14366,142 +14551,202 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>AUTH-FN-08</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>(설명 없음)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>/permissions/roles/:role</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>본사</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>구현(API+화면: 관리자 웹)</t>
+        </is>
+      </c>
+    </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>설계 결정(ADR)</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>AUTH-FN-09</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>직원 계정과 역할 목록(본사)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>/permissions/staff</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>본사</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>구현(API+화면: 관리자 웹)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>ADR</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>결정</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr"/>
-      <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="6" t="inlineStr"/>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>상태</t>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>AUTH-FN-10</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>(설명 없음)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>/permissions/staff/:staffId/overrides</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>본사</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>구현(API+화면: 관리자 웹)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>ADR-AUTH-01</t>
+          <t>AUTH-FN-11</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>매 요청 Account 재조회로 퇴사·Role 변경 즉시 반영</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n"/>
-      <c r="D40" s="14" t="n"/>
-      <c r="E40" s="15" t="n"/>
+          <t>(설명 없음)</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>/permissions/staff/:staffId/overrides</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>본사</t>
+        </is>
+      </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>구현</t>
+          <t>구현(API+화면: 관리자 웹)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>ADR-AUTH-02</t>
+          <t>AUTH-FN-12</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>계약 종료 지점 계정 — 쓰기 차단 + 수동 비활성화</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n"/>
-      <c r="D41" s="14" t="n"/>
-      <c r="E41" s="15" t="n"/>
+          <t>직원 역할 전환(지점 관리자 ↔ 직원, 본사)</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>/permissions/staff/:staffId/role</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>본사</t>
+        </is>
+      </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>구현(수단은 본사 퇴사 처리, 인사정보관리 ADR-STF-08·log/103)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>ADR-AUTH-03</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>4-Role 고정 RBAC(개별 ACL 없음)</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n"/>
-      <c r="D42" s="14" t="n"/>
-      <c r="E42" s="15" t="n"/>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>ADR-AUTH-07이 대체(D60) — 역할 상한으로 유지</t>
+          <t>구현(API+화면: 관리자 웹)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>ADR-AUTH-04</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Refresh Token 발급 시 그 계정의 만료·폐기 토큰 정리</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n"/>
-      <c r="D43" s="14" t="n"/>
-      <c r="E43" s="15" t="n"/>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>설계 결정(ADR)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>ADR-AUTH-05</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>비밀번호 변경 — 데모 계정 403, 불일치 400, 변경 시 refresh token 전부 폐기</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="n"/>
-      <c r="D44" s="14" t="n"/>
-      <c r="E44" s="15" t="n"/>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>구현(log/091)</t>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>ADR</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr"/>
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>상태</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>ADR-AUTH-06</t>
+          <t>ADR-AUTH-01</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>갱신 토큰 원자적 폐기 — 동시 갱신은 한 요청만 성공(재사용 탐지는 안 함)</t>
+          <t>매 요청 Account 재조회로 퇴사·Role 변경 즉시 반영</t>
         </is>
       </c>
       <c r="C45" s="14" t="n"/>
@@ -14509,39 +14754,139 @@
       <c r="E45" s="15" t="n"/>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>구현(log/123)</t>
+          <t>구현</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>ADR-AUTH-07</t>
+          <t>ADR-AUTH-02</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>세부 권한 — 역할 상한 안에서 역할 기본값 + 개인 예외(조회·입력·수정·삭제·출력), 전역 PermissionGuard</t>
+          <t>계약 종료 지점 계정 — 쓰기 차단 + 수동 비활성화</t>
         </is>
       </c>
       <c r="C46" s="14" t="n"/>
       <c r="D46" s="14" t="n"/>
       <c r="E46" s="15" t="n"/>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>1단계 구현(log/146, 서버 판정) — 설정 화면·변경 API는 2단계</t>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>구현(수단은 본사 퇴사 처리, 인사정보관리 ADR-STF-08·log/103)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>ADR-AUTH-03</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>4-Role 고정 RBAC(개별 ACL 없음)</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="14" t="n"/>
+      <c r="E47" s="15" t="n"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>ADR-AUTH-07이 대체(D60) — 역할 상한으로 유지</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ADR-AUTH-04</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Refresh Token 발급 시 그 계정의 만료·폐기 토큰 정리</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="15" t="n"/>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>ADR-AUTH-05</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>비밀번호 변경 — 데모 계정 403, 불일치 400, 변경 시 refresh token 전부 폐기</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="15" t="n"/>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>구현(log/091)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ADR-AUTH-06</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>갱신 토큰 원자적 폐기 — 동시 갱신은 한 요청만 성공(재사용 탐지는 안 함)</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="n"/>
+      <c r="D50" s="14" t="n"/>
+      <c r="E50" s="15" t="n"/>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>구현(log/123)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>ADR-AUTH-07</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>세부 권한 — 역할 상한 안에서 역할 기본값 + 개인 예외(조회·입력·수정·삭제·출력), 전역 PermissionGuard</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="n"/>
+      <c r="D51" s="14" t="n"/>
+      <c r="E51" s="15" t="n"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>1·2단계 구현(log/146 서버 판정, log/147 본사 관리 API·화면·변경 이력) — 관리자 웹 숨김은 3단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>미구현·범위 제외(도메인 문서 기준)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="16" t="inlineStr">
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>로그인 잠금, /accounts 범용 API, 비밀번호 재설정·로그인 이력 화면</t>
         </is>
@@ -14549,28 +14894,28 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C17:F17"/>
+    <mergeCell ref="B49:E49"/>
     <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B51:E51"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="B45:E45"/>
     <mergeCell ref="C18:F18"/>
-    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B50:E50"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="C15:F15"/>
+    <mergeCell ref="B47:E47"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B48:E48"/>
     <mergeCell ref="C16:F16"/>
-    <mergeCell ref="B42:E42"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A49:F49"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B44:E44"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B26:F26"/>
   </mergeCells>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -4953,7 +4953,7 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>(설명 없음)</t>
+          <t>세부 권한 기능·동작 목록과 역할별 상한(본사, D60)</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>(설명 없음)</t>
+          <t>역할 기본 권한 표 — 지점 관리자·직원(본사, D60)</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>(설명 없음)</t>
+          <t>역할 기본 권한 한 칸 변경(본사, 변경 이력, D60)</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>(설명 없음)</t>
+          <t>직원 개인 권한 — 역할 기본값·개인 예외·적용 값(본사, D60)</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>(설명 없음)</t>
+          <t>직원 개인 권한 한 칸 변경(기본/허용/차단, 본사, 변경 이력, D60)</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>(설명 없음)</t>
+          <t>세부 권한 기능·동작 목록과 역할별 상한(본사, D60)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>(설명 없음)</t>
+          <t>역할 기본 권한 표 — 지점 관리자·직원(본사, D60)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>(설명 없음)</t>
+          <t>역할 기본 권한 한 칸 변경(본사, 변경 이력, D60)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>(설명 없음)</t>
+          <t>직원 개인 권한 — 역할 기본값·개인 예외·적용 값(본사, D60)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>(설명 없음)</t>
+          <t>직원 개인 권한 한 칸 변경(기본/허용/차단, 본사, 변경 이력, D60)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -24,7 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범위 제외" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$185</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RFP 충족 판정'!$A$17:$E$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 저장소(dev 브랜치) — 도메인 문서·요구사항추적표·실제 API 라우트에서 자동 생성</t>
+          <t>2026-10-21 저장소(dev 브랜치) — 도메인 문서·요구사항추적표·실제 API 라우트에서 자동 생성</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>도메인 9개 · 기능(API) 102개 · 불변규칙 26개 · RFP 미구현·부분 5건 · 자동 테스트 파일 48개</t>
+          <t>도메인 9개 · 기능(API) 102개 · 불변규칙 26개 · RFP 미구현·부분 4건 · 자동 테스트 파일 48개</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 52/64 = 81% / 95%(구현+조정 / 부분 포함)</t>
+          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 54/64 = 84% / 95%(구현+조정 / 부분 포함)</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/예약및결제.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
+          <t>원천: docs/domains/예약및결제.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/강사프로그램게시.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
+          <t>원천: docs/domains/강사프로그램게시.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/혼잡도관리.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
+          <t>원천: docs/domains/혼잡도관리.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/자원문서관리.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
+          <t>원천: docs/domains/자원문서관리.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3922,17 +3922,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>권한관리(1-1 #1)·UI 보안(1-2 #7)</t>
+          <t>시스템가용성(1-1 #10)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>사용자별·프로그램별 세부 권한(입력·수정·삭제·조회·출력), 개인별·기능별 접근 통제</t>
+          <t>메모리 평균 85% 이하 유지</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>부분 — 역할 4개 + 지점 격리로 조정(D1). 출력은 회원·근태 요약·결제 CSV를 역할 기준으로만(D54), 인쇄용 화면 없음</t>
+          <t>부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>시스템가용성(1-1 #10)</t>
+          <t>UI 보안(1-2 #7)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>메모리 평균 85% 이하 유지</t>
+          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
+          <t>부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -3976,17 +3976,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>UI 보안(1-2 #7)</t>
+          <t>과업4·산출물5(p.4·p.7)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인</t>
+          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
+          <t>부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>과업4·산출물5(p.4·p.7)</t>
+          <t>산출물4(p.7)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료</t>
+          <t>단계별 개발 진행 보고서 5부</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
+          <t>부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -4022,56 +4022,29 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>GAP-05</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>산출물4(p.7)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>단계별 개발 진행 보고서 5부</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>API는 있고 화면이 없는 것</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>지금은 없다(로컬 전용 dev-storage 경로 제외). 마지막 항목이던 관리자의 직원 업무일지 열람은 2026-10-14 직원 상세에 붙였다(D51, log/112).</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>설계는 있지만 미구현인 도메인 규칙</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>결제 PaymentGateway 어댑터(ADR-RSV-03) — 실 PG를 붙일 때 필요하다.</t>
         </is>
@@ -4079,8 +4052,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4278,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4323,7 +4296,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>COUNTIF($C$12:$C$187,"기능")</f>
+        <f>COUNTIF($C$12:$C$186,"기능")</f>
         <v/>
       </c>
     </row>
@@ -4334,7 +4307,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>COUNTIFS($C$12:$C$187,"기능",$F$12:$F$187,"있음")</f>
+        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"있음")</f>
         <v/>
       </c>
     </row>
@@ -4345,7 +4318,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIFS($C$12:$C$187,"기능",$F$12:$F$187,"없음")</f>
+        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"없음")</f>
         <v/>
       </c>
     </row>
@@ -4356,7 +4329,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF($C$12:$C$187,"불변규칙")</f>
+        <f>COUNTIF($C$12:$C$186,"불변규칙")</f>
         <v/>
       </c>
     </row>
@@ -4367,7 +4340,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF($C$12:$C$187,"미구현")</f>
+        <f>COUNTIF($C$12:$C$186,"미구현")</f>
         <v/>
       </c>
     </row>
@@ -10548,7 +10521,7 @@
       </c>
       <c r="D182" s="9" t="inlineStr">
         <is>
-          <t>사용자별·프로그램별 세부 권한(입력·수정·삭제·조회·출력), 개인별·기능별 접근 통제 — 부분 — 역할 4개 + 지점 격리로 조정(D1). 출력은 회원·근태 요약·결제 CSV를 역할 기준으로만(D54), 인쇄용 화면 없음</t>
+          <t>메모리 평균 85% 이하 유지 — 부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
@@ -10563,7 +10536,7 @@
       </c>
       <c r="G182" s="9" t="inlineStr">
         <is>
-          <t>권한관리(1-1 #1)·UI 보안(1-2 #7)</t>
+          <t>시스템가용성(1-1 #10)</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10558,7 @@
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>메모리 평균 85% 이하 유지 — 부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
+          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인 — 부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
@@ -10600,7 +10573,7 @@
       </c>
       <c r="G183" s="9" t="inlineStr">
         <is>
-          <t>시스템가용성(1-1 #10)</t>
+          <t>UI 보안(1-2 #7)</t>
         </is>
       </c>
     </row>
@@ -10622,7 +10595,7 @@
       </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인 — 부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
+          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료 — 부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
@@ -10637,7 +10610,7 @@
       </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>UI 보안(1-2 #7)</t>
+          <t>과업4·산출물5(p.4·p.7)</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10632,7 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료 — 부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
+          <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
@@ -10674,49 +10647,12 @@
       </c>
       <c r="G185" s="9" t="inlineStr">
         <is>
-          <t>과업4·산출물5(p.4·p.7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="9" t="inlineStr">
-        <is>
-          <t>GAP-05</t>
-        </is>
-      </c>
-      <c r="B186" s="9" t="inlineStr">
-        <is>
-          <t>RFP 공통</t>
-        </is>
-      </c>
-      <c r="C186" s="9" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-      <c r="D186" s="9" t="inlineStr">
-        <is>
-          <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
-        </is>
-      </c>
-      <c r="E186" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="F186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G186" s="9" t="inlineStr">
-        <is>
           <t>산출물4(p.7)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A11:G186"/>
+  <autoFilter ref="A11:G185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10825,12 +10761,12 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>세부 ACL → 4-Role 고정 RBAC로 단순화. 지점 간 격리(전역 가드, D46)·퇴사 즉시 차단은 그대로 구현. "출력"은 목록 CSV를 역할 기준으로(D54)</t>
+          <t>4-Role(D1)을 역할 상한으로 두고 그 안에서 기능×동작 세부 권한을 역할 기본값·개인 예외로(D60, D1 대체). 지점 간 격리(전역 가드, D46)·퇴사 즉시 차단은 그대로. "출력"은 목록 CSV(D54) + 출력 권한</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>D1, D12, D46, D54</t>
+          <t>D1, D12, D46, D54, D60</t>
         </is>
       </c>
     </row>
@@ -11386,7 +11322,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>목록 응답 전화번호 마스킹(회원관리 ADR-MEM-04), 상세 전화번호 열람은 관리자가 열 때마다 AuditLog에 남고 본사만 본다(D47). 접근통제는 역할 4개 + 지점 격리(개인별·기능별 세부 권한은 없음, D1). 금융기관 연계는 결제 어댑터 설계(ADR-RSV-03)만</t>
+          <t>목록 응답 전화번호 마스킹(회원관리 ADR-MEM-04), 상세 전화번호 열람은 관리자가 열 때마다 AuditLog에 남고 본사만 본다(D47). 접근통제는 역할 상한 + 역할별·개인별·기능별 세부 권한(D60) + 지점 격리(D46). 금융기관 연계는 결제 어댑터 설계(ADR-RSV-03)만</t>
         </is>
       </c>
     </row>
@@ -11732,7 +11668,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -11742,7 +11678,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -11757,7 +11693,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>26/28 = 93% / 100%</t>
+          <t>27/28 = 96% / 100%</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11710,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -11784,7 +11720,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -11799,7 +11735,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>16/19 = 84% / 100%</t>
+          <t>17/19 = 89% / 100%</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11794,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -11868,7 +11804,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -11883,7 +11819,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>52/64 = 81% / 95%</t>
+          <t>54/64 = 84% / 95%</t>
         </is>
       </c>
     </row>
@@ -12017,14 +11953,14 @@
           <t>사용자별·프로그램별 권한 설정(입력·수정·삭제·조회·출력)</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>D60(D1 대체) — 서버가 기능×동작 권한을 역할 기본값·개인 예외로 판정(log/146), 본사가 권한 관리 화면·직원 상세에서 바꾼다(log/147). 관리자 웹이 권한대로 버튼을 숨기는 3단계 뒤 구현 판정</t>
+          <t>D60(D1 대체) — 기능 15개 × 조회·입력·수정·삭제·출력을 역할 기본값·개인 예외로 본사가 설정(권한 관리 화면·직원 상세), 서버가 판정, 관리자 웹이 메뉴·버튼·CSV를 권한대로 숨김(log/146~148). 역할 상한 안에서만</t>
         </is>
       </c>
     </row>
@@ -13232,14 +13168,14 @@
           <t>권한에 의한 접근 통제 — 그룹별·개인별·기능별</t>
         </is>
       </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>역할·지점 단위 + 서버의 역할별·개인별·기능별 판정과 본사 설정 화면(D60, log/146·147). 화면 숨김은 3단계</t>
+          <t>그룹(역할)별·개인별·기능별 판정(전역 PermissionGuard)과 화면 숨김(D60, log/146~148) + 지점 단위 격리(D46)</t>
         </is>
       </c>
     </row>
@@ -13951,7 +13887,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/권한관리.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
+          <t>원천: docs/domains/권한관리.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -14872,9 +14808,9 @@
       <c r="C51" s="14" t="n"/>
       <c r="D51" s="14" t="n"/>
       <c r="E51" s="15" t="n"/>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>1·2단계 구현(log/146 서버 판정, log/147 본사 관리 API·화면·변경 이력) — 관리자 웹 숨김은 3단계</t>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>구현(log/146 서버 판정, log/147 본사 관리 API·화면·변경 이력, log/148 적용 권한 → 관리자 웹 메뉴·버튼·CSV 숨김)</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14886,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/인사정보관리.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
+          <t>원천: docs/domains/인사정보관리.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -16005,7 +15941,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/근태관리.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
+          <t>원천: docs/domains/근태관리.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -16935,7 +16871,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/게시판.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
+          <t>원천: docs/domains/게시판.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -17686,7 +17622,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/회원관리.md · 기능 명세는 코드 실측(2026-10-20 저장소 기준)</t>
+          <t>원천: docs/domains/회원관리.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -24,7 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범위 제외" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$186</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RFP 충족 판정'!$A$17:$E$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>도메인 9개 · 기능(API) 102개 · 불변규칙 26개 · RFP 미구현·부분 4건 · 자동 테스트 파일 48개</t>
+          <t>도메인 9개 · 기능(API) 103개 · 불변규칙 26개 · RFP 미구현·부분 4건 · 자동 테스트 파일 49개</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>COUNTIF($C$12:$C$186,"기능")</f>
+        <f>COUNTIF($C$12:$C$187,"기능")</f>
         <v/>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"있음")</f>
+        <f>COUNTIFS($C$12:$C$187,"기능",$F$12:$F$187,"있음")</f>
         <v/>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"없음")</f>
+        <f>COUNTIFS($C$12:$C$187,"기능",$F$12:$F$187,"없음")</f>
         <v/>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF($C$12:$C$186,"불변규칙")</f>
+        <f>COUNTIF($C$12:$C$187,"불변규칙")</f>
         <v/>
       </c>
     </row>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF($C$12:$C$186,"미구현")</f>
+        <f>COUNTIF($C$12:$C$187,"미구현")</f>
         <v/>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>업무지원 요청 등록(지점 관리자 → 본사, D56)</t>
+          <t>처리 대기함 — 역할별 지금 처리할 일 건수(D61)</t>
         </is>
       </c>
       <c r="E178" s="10" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>POST /support-requests</t>
+          <t>GET /inbox</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>업무지원 요청 목록(지점은 자기 지점, 본사는 전체)</t>
+          <t>업무지원 요청 등록(지점 관리자 → 본사, D56)</t>
         </is>
       </c>
       <c r="E179" s="10" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>GET /support-requests</t>
+          <t>POST /support-requests</t>
         </is>
       </c>
     </row>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>업무지원 요청 상세</t>
+          <t>업무지원 요청 목록(지점은 자기 지점, 본사는 전체)</t>
         </is>
       </c>
       <c r="E180" s="10" t="inlineStr">
@@ -10457,12 +10457,12 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>GET /support-requests/:id</t>
+          <t>GET /support-requests</t>
         </is>
       </c>
     </row>
@@ -10484,66 +10484,66 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
+          <t>업무지원 요청 상세</t>
+        </is>
+      </c>
+      <c r="E181" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>GET /support-requests/:id</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>COM-FN-11</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
           <t>업무지원 요청 처리 상태 변경(본사)</t>
         </is>
       </c>
-      <c r="E181" s="10" t="inlineStr">
-        <is>
-          <t>구현</t>
-        </is>
-      </c>
-      <c r="F181" s="4" t="inlineStr">
+      <c r="E182" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="G181" s="4" t="inlineStr">
+      <c r="G182" s="4" t="inlineStr">
         <is>
           <t>PATCH /support-requests/:id/status</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="9" t="inlineStr">
-        <is>
-          <t>GAP-01</t>
-        </is>
-      </c>
-      <c r="B182" s="9" t="inlineStr">
-        <is>
-          <t>RFP 공통</t>
-        </is>
-      </c>
-      <c r="C182" s="9" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-      <c r="D182" s="9" t="inlineStr">
-        <is>
-          <t>메모리 평균 85% 이하 유지 — 부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
-        </is>
-      </c>
-      <c r="E182" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="F182" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G182" s="9" t="inlineStr">
-        <is>
-          <t>시스템가용성(1-1 #10)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>GAP-02</t>
+          <t>GAP-01</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인 — 부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
+          <t>메모리 평균 85% 이하 유지 — 부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
@@ -10573,14 +10573,14 @@
       </c>
       <c r="G183" s="9" t="inlineStr">
         <is>
-          <t>UI 보안(1-2 #7)</t>
+          <t>시스템가용성(1-1 #10)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>GAP-03</t>
+          <t>GAP-02</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료 — 부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
+          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인 — 부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
@@ -10610,49 +10610,86 @@
       </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>과업4·산출물5(p.4·p.7)</t>
+          <t>UI 보안(1-2 #7)</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
+          <t>GAP-03</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t>RFP 공통</t>
+        </is>
+      </c>
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료 — 부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
+        </is>
+      </c>
+      <c r="E185" s="11" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="F185" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G185" s="9" t="inlineStr">
+        <is>
+          <t>과업4·산출물5(p.4·p.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="9" t="inlineStr">
+        <is>
           <t>GAP-04</t>
         </is>
       </c>
-      <c r="B185" s="9" t="inlineStr">
+      <c r="B186" s="9" t="inlineStr">
         <is>
           <t>RFP 공통</t>
         </is>
       </c>
-      <c r="C185" s="9" t="inlineStr">
+      <c r="C186" s="9" t="inlineStr">
         <is>
           <t>미구현</t>
         </is>
       </c>
-      <c r="D185" s="9" t="inlineStr">
+      <c r="D186" s="9" t="inlineStr">
         <is>
           <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
         </is>
       </c>
-      <c r="E185" s="11" t="inlineStr">
+      <c r="E186" s="11" t="inlineStr">
         <is>
           <t>부분</t>
         </is>
       </c>
-      <c r="F185" s="9" t="inlineStr">
+      <c r="F186" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G185" s="9" t="inlineStr">
+      <c r="G186" s="9" t="inlineStr">
         <is>
           <t>산출물4(p.7)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A11:G185"/>
+  <autoFilter ref="A11:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 54/64 = 84% / 95%(구현+조정 / 부분 포함)</t>
+          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 55/64 = 86% / 95%(구현+조정 / 부분 포함)</t>
         </is>
       </c>
     </row>
@@ -3976,17 +3976,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>과업4·산출물5(p.4·p.7)</t>
+          <t>산출물5(p.7)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료</t>
+          <t>어플 사용 교육 자료 — 게시판 탑재</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
+          <t>부분 — 교육 자료(역할별 빠른 시작, docs/deliverables/교육자료_빠른시작.pdf)는 만들었다(log/152). 운영 게시판에 올리는 것(본사 공지 "직원 교육자료" 분류에 첨부)은 사용자 작업 — 아직</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>이용자 매뉴얼 제작·게시판 탑재, 어플 사용 교육 자료 — 부분 — 관리자 웹 화면별 도움말과 회원 웹 이용 안내는 있다. 별도 사용자 매뉴얼(교육 자료 1편)과 게시판 탑재는 없다. 대면 교육은 해당 없음</t>
+          <t>어플 사용 교육 자료 — 게시판 탑재 — 부분 — 교육 자료(역할별 빠른 시작, docs/deliverables/교육자료_빠른시작.pdf)는 만들었다(log/152). 운영 게시판에 올리는 것(본사 공지 "직원 교육자료" 분류에 첨부)은 사용자 작업 — 아직</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="G185" s="9" t="inlineStr">
         <is>
-          <t>과업4·산출물5(p.4·p.7)</t>
+          <t>산출물5(p.7)</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>10/17 = 59% / 82%</t>
+          <t>11/17 = 65% / 82%</t>
         </is>
       </c>
     </row>
@@ -11831,7 +11831,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>54/64 = 84% / 95%</t>
+          <t>55/64 = 86% / 95%</t>
         </is>
       </c>
     </row>
@@ -13637,14 +13637,14 @@
           <t>이용자 매뉴얼 제작·탑재</t>
         </is>
       </c>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>화면 도움말·이용 안내만, 별도 매뉴얼 없음</t>
+          <t>사용자 매뉴얼(Word, 역할별 4장·화면 캡처·오류 해결 부록 — 화면 도움말을 원천으로 생성, log/152) + 앱 안 탑재(관리자 웹 화면별 도움말, 회원 웹 이용 안내)</t>
         </is>
       </c>
     </row>
@@ -13860,7 +13860,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>화면 도움말·이용 안내만(§2-3)</t>
+          <t>역할별 빠른 시작 1편(PDF, log/152) 작성. 운영 게시판 탑재는 사용자 작업 — 아직</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -24,7 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범위 제외" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$185</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RFP 충족 판정'!$A$17:$E$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 저장소(dev 브랜치) — 도메인 문서·요구사항추적표·실제 API 라우트에서 자동 생성</t>
+          <t>2026-10-22 저장소(dev 브랜치) — 도메인 문서·요구사항추적표·실제 API 라우트에서 자동 생성</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>도메인 9개 · 기능(API) 103개 · 불변규칙 26개 · RFP 미구현·부분 4건 · 자동 테스트 파일 49개</t>
+          <t>도메인 9개 · 기능(API) 103개 · 불변규칙 26개 · RFP 미구현·부분 3건 · 자동 테스트 파일 49개</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 55/64 = 86% / 95%(구현+조정 / 부분 포함)</t>
+          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 56/64 = 88% / 95%(구현+조정 / 부분 포함)</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/예약및결제.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
+          <t>원천: docs/domains/예약및결제.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/강사프로그램게시.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
+          <t>원천: docs/domains/강사프로그램게시.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/혼잡도관리.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
+          <t>원천: docs/domains/혼잡도관리.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/자원문서관리.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
+          <t>원천: docs/domains/자원문서관리.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3976,17 +3976,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>산출물5(p.7)</t>
+          <t>산출물4(p.7)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>어플 사용 교육 자료 — 게시판 탑재</t>
+          <t>단계별 개발 진행 보고서 5부</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>부분 — 교육 자료(역할별 빠른 시작, docs/deliverables/교육자료_빠른시작.pdf)는 만들었다(log/152). 운영 게시판에 올리는 것(본사 공지 "직원 교육자료" 분류에 첨부)은 사용자 작업 — 아직</t>
+          <t>부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -3995,56 +3995,29 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>GAP-04</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>산출물4(p.7)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>단계별 개발 진행 보고서 5부</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>API는 있고 화면이 없는 것</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>지금은 없다(로컬 전용 dev-storage 경로 제외). 마지막 항목이던 관리자의 직원 업무일지 열람은 2026-10-14 직원 상세에 붙였다(D51, log/112).</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>설계는 있지만 미구현인 도메인 규칙</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>결제 PaymentGateway 어댑터(ADR-RSV-03) — 실 PG를 붙일 때 필요하다.</t>
         </is>
@@ -4052,8 +4025,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4251,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4296,7 +4269,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>COUNTIF($C$12:$C$187,"기능")</f>
+        <f>COUNTIF($C$12:$C$186,"기능")</f>
         <v/>
       </c>
     </row>
@@ -4307,7 +4280,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>COUNTIFS($C$12:$C$187,"기능",$F$12:$F$187,"있음")</f>
+        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"있음")</f>
         <v/>
       </c>
     </row>
@@ -4318,7 +4291,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIFS($C$12:$C$187,"기능",$F$12:$F$187,"없음")</f>
+        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"없음")</f>
         <v/>
       </c>
     </row>
@@ -4329,7 +4302,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF($C$12:$C$187,"불변규칙")</f>
+        <f>COUNTIF($C$12:$C$186,"불변규칙")</f>
         <v/>
       </c>
     </row>
@@ -4340,7 +4313,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF($C$12:$C$187,"미구현")</f>
+        <f>COUNTIF($C$12:$C$186,"미구현")</f>
         <v/>
       </c>
     </row>
@@ -10632,7 +10605,7 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>어플 사용 교육 자료 — 게시판 탑재 — 부분 — 교육 자료(역할별 빠른 시작, docs/deliverables/교육자료_빠른시작.pdf)는 만들었다(log/152). 운영 게시판에 올리는 것(본사 공지 "직원 교육자료" 분류에 첨부)은 사용자 작업 — 아직</t>
+          <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
@@ -10647,49 +10620,12 @@
       </c>
       <c r="G185" s="9" t="inlineStr">
         <is>
-          <t>산출물5(p.7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="9" t="inlineStr">
-        <is>
-          <t>GAP-04</t>
-        </is>
-      </c>
-      <c r="B186" s="9" t="inlineStr">
-        <is>
-          <t>RFP 공통</t>
-        </is>
-      </c>
-      <c r="C186" s="9" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-      <c r="D186" s="9" t="inlineStr">
-        <is>
-          <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
-        </is>
-      </c>
-      <c r="E186" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="F186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G186" s="9" t="inlineStr">
-        <is>
           <t>산출물4(p.7)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A11:G186"/>
+  <autoFilter ref="A11:G185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11789,7 +11725,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -11799,14 +11735,14 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>1</t>
@@ -11814,7 +11750,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>11/17 = 65% / 82%</t>
+          <t>12/17 = 71% / 82%</t>
         </is>
       </c>
     </row>
@@ -11831,7 +11767,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -11841,7 +11777,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -11856,7 +11792,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>55/64 = 86% / 95%</t>
+          <t>56/64 = 88% / 95%</t>
         </is>
       </c>
     </row>
@@ -13853,14 +13789,14 @@
           <t>어플 사용 교육 자료 1편(게시판 탑재)</t>
         </is>
       </c>
-      <c r="D88" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>역할별 빠른 시작 1편(PDF, log/152) 작성. 운영 게시판 탑재는 사용자 작업 — 아직</t>
+          <t>역할별 빠른 시작 1편(PDF, log/152)을 운영 게시판 본사 공지 "교육자료" 분류(직원 교육자료 탭)에 첨부(2026-10-22, log/153) — 지점 관리자·직원 열람, 회원 비공개</t>
         </is>
       </c>
     </row>
@@ -13924,7 +13860,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/권한관리.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
+          <t>원천: docs/domains/권한관리.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -14923,7 +14859,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/인사정보관리.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
+          <t>원천: docs/domains/인사정보관리.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -15978,7 +15914,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/근태관리.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
+          <t>원천: docs/domains/근태관리.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -16908,7 +16844,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/게시판.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
+          <t>원천: docs/domains/게시판.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -17659,7 +17595,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/회원관리.md · 기능 명세는 코드 실측(2026-10-21 저장소 기준)</t>
+          <t>원천: docs/domains/회원관리.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -24,7 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범위 제외" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$187</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RFP 충족 판정'!$A$17:$E$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>도메인 9개 · 기능(API) 103개 · 불변규칙 26개 · RFP 미구현·부분 3건 · 자동 테스트 파일 49개</t>
+          <t>도메인 9개 · 기능(API) 103개 · 불변규칙 26개 · RFP 미구현·부분 5건 · 자동 테스트 파일 50개</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
+          <t>부분 — 진행 기록(docs/log/ 150여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -3995,29 +3995,83 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>GAP-04</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>과업3(p.3)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>앱 개발 → 테스트 → 검수 → 완료 → 도입 → 경영개선 기대효과 분석</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>부분 — 개발·테스트·운영 배포까지. 검수(발주기관)·도입·기대효과 분석은 없다(기대효과는 P2-2와 같은 이유로 의도적 제외)</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>GAP-05</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>보안요건(1-2 #8)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>개인정보보호법 제26조(업무위탁) 준수</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>부분 — 처리방침의 위탁 고지(D51)·수탁자 표(security-plan §7)만. 위탁 계약 문서 보관·수탁자 감독 기록은 실데이터 운영 전 조치</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>API는 있고 화면이 없는 것</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>지금은 없다(로컬 전용 dev-storage 경로 제외). 마지막 항목이던 관리자의 직원 업무일지 열람은 2026-10-14 직원 상세에 붙였다(D51, log/112).</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>설계는 있지만 미구현인 도메인 규칙</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>결제 PaymentGateway 어댑터(ADR-RSV-03) — 실 PG를 붙일 때 필요하다.</t>
         </is>
@@ -4025,8 +4079,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4224,7 +4278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4269,7 +4323,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>COUNTIF($C$12:$C$186,"기능")</f>
+        <f>COUNTIF($C$12:$C$188,"기능")</f>
         <v/>
       </c>
     </row>
@@ -4280,7 +4334,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"있음")</f>
+        <f>COUNTIFS($C$12:$C$188,"기능",$F$12:$F$188,"있음")</f>
         <v/>
       </c>
     </row>
@@ -4291,7 +4345,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"없음")</f>
+        <f>COUNTIFS($C$12:$C$188,"기능",$F$12:$F$188,"없음")</f>
         <v/>
       </c>
     </row>
@@ -4302,7 +4356,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF($C$12:$C$186,"불변규칙")</f>
+        <f>COUNTIF($C$12:$C$188,"불변규칙")</f>
         <v/>
       </c>
     </row>
@@ -4313,7 +4367,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF($C$12:$C$186,"미구현")</f>
+        <f>COUNTIF($C$12:$C$188,"미구현")</f>
         <v/>
       </c>
     </row>
@@ -6827,7 +6881,7 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>post-facility·post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
+          <t>post-rich-content·post-facility·post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
@@ -6864,7 +6918,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>post-facility·post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
+          <t>post-rich-content·post-facility·post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10659,7 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 130여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
+          <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 150여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
@@ -10624,8 +10678,82 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" s="9" t="inlineStr">
+        <is>
+          <t>GAP-04</t>
+        </is>
+      </c>
+      <c r="B186" s="9" t="inlineStr">
+        <is>
+          <t>RFP 공통</t>
+        </is>
+      </c>
+      <c r="C186" s="9" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="inlineStr">
+        <is>
+          <t>앱 개발 → 테스트 → 검수 → 완료 → 도입 → 경영개선 기대효과 분석 — 부분 — 개발·테스트·운영 배포까지. 검수(발주기관)·도입·기대효과 분석은 없다(기대효과는 P2-2와 같은 이유로 의도적 제외)</t>
+        </is>
+      </c>
+      <c r="E186" s="11" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="F186" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G186" s="9" t="inlineStr">
+        <is>
+          <t>과업3(p.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>GAP-05</t>
+        </is>
+      </c>
+      <c r="B187" s="9" t="inlineStr">
+        <is>
+          <t>RFP 공통</t>
+        </is>
+      </c>
+      <c r="C187" s="9" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="inlineStr">
+        <is>
+          <t>개인정보보호법 제26조(업무위탁) 준수 — 부분 — 처리방침의 위탁 고지(D51)·수탁자 표(security-plan §7)만. 위탁 계약 문서 보관·수탁자 감독 기록은 실데이터 운영 전 조치</t>
+        </is>
+      </c>
+      <c r="E187" s="11" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="F187" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" s="9" t="inlineStr">
+        <is>
+          <t>보안요건(1-2 #8)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A11:G185"/>
+  <autoFilter ref="A11:G187"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10845,12 +10973,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>댓글/좋아요 등 커뮤니티 부가기능만 범위 제외. 교육자료는 "직원 교육자료" 탭 + 첨부(서명 URL 저장소, ADR-BRD-04·D57). 공지는 지점 단위(시설 지정 없음)</t>
+          <t>댓글/좋아요 등 커뮤니티 부가기능만 범위 제외. 교육자료는 "직원 교육자료" 탭 + 첨부(서명 URL 저장소, ADR-BRD-04·D57). 지점 공지에 대상 시설 지정(ADR-BRD-05). 본문은 작성·수정 화면의 서식 편집기 + 허용 목록 정화 두 겹(D62) — 이미지는 본문이 아니라 첨부로</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>D57, ADR-BRD-04</t>
+          <t>D57, D62, ADR-BRD-04, ADR-BRD-05</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11288,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1인 개발 구조상 "발주기관/전문가 검증" 주체가 없음 — CI(lint·빌드·jest·문서 검사)와 커밋 전 hook, 도메인 문서 §11 검증현황으로 대체. 개발보안은 행안부 구현단계 보안약점 49개로 점검했다(secure-coding-checklist — 대응 34·부분 4·해당 없음 11, 점검 중 찾은 문서 주소 XSS는 수정, log/139)</t>
+          <t>1인 개발 구조상 "발주기관/전문가 검증" 주체가 없음 — CI(lint·빌드·jest·문서 검사)와 커밋 전 hook, 도메인 문서 §11 검증현황으로 대체. 개발보안은 행안부 구현단계 보안약점 49개로 점검했다(secure-coding-checklist — 대응 34·부분 4·해당 없음 11, 점검 중 찾은 문서 주소 XSS는 수정, log/139). 의존성 알려진 취약점은 npm audit로 대조해 운영 18 → 4건(도달 불가, D63)·개발 도구 고친 판 없는 2건 수용(D64)</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11396,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>admin-web 디자인 토큰화(D15)로 통일성 확보. "페이지 위치 정보를 MAP형태로"는 현재 화면의 경로 표시로 해석해 구현(D51 — 홈 › 메뉴 › 화면). 예약 달력은 회원 웹 날짜 띠·관리자 주간 시간표(ADR-RSV-06). 입력 필드는 전화·숫자·이메일·URL에 맞는 자판과 자동완성 속성을 두 앱 모두에 지정(log/137)</t>
+          <t>admin-web 디자인 토큰화(D15)로 통일성 확보. "페이지 위치 정보를 MAP형태로"는 현재 화면의 경로 표시로 해석해 구현(D51 — 홈 › 메뉴 › 화면). 예약 달력은 회원 웹 날짜 띠·관리자 주간 시간표(ADR-RSV-06). 버튼은 세부 권한대로 숨긴다(D60). 입력 필드는 전화·숫자·이메일·URL에 맞는 자판과 자동완성 속성을 두 앱 모두에 지정(log/137)</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11450,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>개인정보처리방침을 회원 웹 화면(/m/privacy)으로 작성 — 수집 항목·열람 범위·보관·처리 위탁(26조: Supabase·AWS·Cloudflare). 시연용 초안, 가입 시 동의는 화면에서만 받음(D51). 보안관리계획은 security-plan(인원·문서·장비·비밀값·위탁, 지금 약점 9건과 조치 계획 — log/139)</t>
+          <t>개인정보처리방침을 회원 웹 화면(/m/privacy)으로 작성 — 수집 항목·열람 범위·보관·처리 위탁(26조: Supabase·AWS·Cloudflare). 시연용 초안, 가입 시 동의는 화면에서만 받음(D51). 보안관리계획은 security-plan(인원·문서·장비·비밀값·위탁, 지금 약점 10건과 조치 계획 — log/139, S10 의존성 취약점은 D63)</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11504,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>운영 의존성 219개가 모두 허용형 라이선스(MIT·ISC·Apache-2.0·BSD 등, copyleft 없음) — dependency-licenses를 scripts/license-report.mjs가 만들고 --check로 다시 점검(log/139). 이미지·아이콘은 자체 제작</t>
+          <t>운영 의존성 243개(2026-10-22 재생성, log/158)가 모두 허용형 라이선스(MIT·ISC·Apache-2.0·BSD 등, copyleft 없음) — dependency-licenses를 scripts/license-report.mjs가 만들고 --check로 다시 점검(log/139). 이미지·아이콘은 자체 제작</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12358,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>"직원 교육자료" 탭, 첨부(ADR-BRD-04). 배포 저장소의 실제 파일은 검증 전</t>
+          <t>"직원 교육자료" 탭, 첨부(ADR-BRD-04) — 배포 저장소 올리기·내려받기 확인(log/144), 교육 자료 PDF 운영 탑재(log/153)</t>
         </is>
       </c>
     </row>
@@ -12257,7 +12385,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>지점 공지에 대상 시설 지정(게시판 ADR-BRD-05, log/145) — 관리자 웹 글쓰기·수정에서 선택, 회원 웹 시설로 거르기·표시. 이미지는 두 웹 모두 바로 표시(log/137·144)</t>
+          <t>지점 공지에 대상 시설 지정(게시판 ADR-BRD-05, log/145) — 관리자 웹 글쓰기·수정에서 선택, 회원 웹 시설로 거르기·표시. 글은 작성·수정 화면의 서식 편집기(D62, ADR-BRD-06 — post-rich-content), 이미지는 첨부로 올려 두 웹 모두 바로 표시(log/137·144)</t>
         </is>
       </c>
     </row>
@@ -12743,7 +12871,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>행안부 구현단계 보안약점 49개 점검표(secure-coding-checklist — 대응 34·부분 4·해당 없음 11), 남은 조치 4건 표로 관리, 점검 중 찾은 XSS 수정(document-rules)</t>
+          <t>행안부 구현단계 보안약점 49개 점검표(secure-coding-checklist — 대응 34·부분 4·해당 없음 11), 남은 조치 4건 표로 관리, 점검 중 찾은 XSS 수정(document-rules). 의존성 취약점 대조(API-2 — 운영 18 → 4건은 도달 불가 D63, 개발 도구 D64)</t>
         </is>
       </c>
     </row>
@@ -13040,7 +13168,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>역할별 메뉴·버튼 표시, 서버는 @Roles로 다시 거부</t>
+          <t>세부 권한대로 메뉴·등록·수정·삭제·CSV 버튼을 숨기고(useCan, D60, log/148) 서버가 @Roles·PermissionGuard로 다시 거부</t>
         </is>
       </c>
     </row>
@@ -13202,7 +13330,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>security-plan — 인원·문서·장비·비밀값·운영 보호·위탁, 지금 약점 9건과 조치 계획</t>
+          <t>security-plan — 인원·문서·장비·비밀값·운영 보호·위탁, 지금 약점 10건(S10 의존성 취약점, D63)과 조치 계획</t>
         </is>
       </c>
     </row>
@@ -13310,7 +13438,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>운영 의존성 219개 라이선스 목록·허용형 점검(dependency-licenses, license-report.mjs --check)</t>
+          <t>운영 의존성 243개 라이선스 목록(log/158 재생성)·허용형 점검(dependency-licenses, license-report.mjs --check)</t>
         </is>
       </c>
     </row>
@@ -16823,7 +16951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17073,7 +17201,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>post-facility·post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
+          <t>post-rich-content·post-facility·post-attachments·post-rules(동시 조회수·소프트 삭제·수정/삭제 권한·작성 범위)·posts-member-visibility·contract-termination·branch-isolation spec</t>
         </is>
       </c>
     </row>
@@ -17531,29 +17659,51 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>ADR-BRD-06</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>본문 서식 HTML — 별도 작성·수정 화면(편집기 + 첨부 한곳), 저장 전 허용 목록 정화 + 보일 때 DOMPurify(D62)</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>구현(log/154)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>미구현·범위 제외(도메인 문서 기준)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>pinned·읽음 확인(범위 제외), category 필터 UI, TrainingLog</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="B36:E36"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B20:F20"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="B38:E38"/>
@@ -17562,7 +17712,6 @@
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -24,7 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범위 제외" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$186</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RFP 충족 판정'!$A$17:$E$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>도메인 9개 · 기능(API) 103개 · 불변규칙 26개 · RFP 미구현·부분 5건 · 자동 테스트 파일 50개</t>
+          <t>도메인 9개 · 기능(API) 103개 · 불변규칙 26개 · RFP 미구현·부분 4건 · 자동 테스트 파일 50개</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 56/64 = 88% / 95%(구현+조정 / 부분 포함)</t>
+          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 57/64 = 89% / 95%(구현+조정 / 부분 포함)</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3976,17 +3976,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>산출물4(p.7)</t>
+          <t>과업3(p.3)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>단계별 개발 진행 보고서 5부</t>
+          <t>앱 개발 → 테스트 → 검수 → 완료 → 도입 → 경영개선 기대효과 분석</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>부분 — 진행 기록(docs/log/ 150여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
+          <t>부분 — 개발·테스트·운영 배포까지. 검수(발주기관)·도입·기대효과 분석은 없다(기대효과는 P2-2와 같은 이유로 의도적 제외)</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>과업3(p.3)</t>
+          <t>보안요건(1-2 #8)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>앱 개발 → 테스트 → 검수 → 완료 → 도입 → 경영개선 기대효과 분석</t>
+          <t>개인정보보호법 제26조(업무위탁) 준수</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>부분 — 개발·테스트·운영 배포까지. 검수(발주기관)·도입·기대효과 분석은 없다(기대효과는 P2-2와 같은 이유로 의도적 제외)</t>
+          <t>부분 — 처리방침의 위탁 고지(D51)·수탁자 표(security-plan §7)만. 위탁 계약 문서 보관·수탁자 감독 기록은 실데이터 운영 전 조치</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -4022,56 +4022,29 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>GAP-05</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>보안요건(1-2 #8)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>개인정보보호법 제26조(업무위탁) 준수</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>부분 — 처리방침의 위탁 고지(D51)·수탁자 표(security-plan §7)만. 위탁 계약 문서 보관·수탁자 감독 기록은 실데이터 운영 전 조치</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>API는 있고 화면이 없는 것</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>지금은 없다(로컬 전용 dev-storage 경로 제외). 마지막 항목이던 관리자의 직원 업무일지 열람은 2026-10-14 직원 상세에 붙였다(D51, log/112).</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>설계는 있지만 미구현인 도메인 규칙</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>결제 PaymentGateway 어댑터(ADR-RSV-03) — 실 PG를 붙일 때 필요하다.</t>
         </is>
@@ -4079,8 +4052,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4278,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G187"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4323,7 +4296,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>COUNTIF($C$12:$C$188,"기능")</f>
+        <f>COUNTIF($C$12:$C$187,"기능")</f>
         <v/>
       </c>
     </row>
@@ -4334,7 +4307,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>COUNTIFS($C$12:$C$188,"기능",$F$12:$F$188,"있음")</f>
+        <f>COUNTIFS($C$12:$C$187,"기능",$F$12:$F$187,"있음")</f>
         <v/>
       </c>
     </row>
@@ -4345,7 +4318,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIFS($C$12:$C$188,"기능",$F$12:$F$188,"없음")</f>
+        <f>COUNTIFS($C$12:$C$187,"기능",$F$12:$F$187,"없음")</f>
         <v/>
       </c>
     </row>
@@ -4356,7 +4329,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF($C$12:$C$188,"불변규칙")</f>
+        <f>COUNTIF($C$12:$C$187,"불변규칙")</f>
         <v/>
       </c>
     </row>
@@ -4367,7 +4340,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF($C$12:$C$188,"미구현")</f>
+        <f>COUNTIF($C$12:$C$187,"미구현")</f>
         <v/>
       </c>
     </row>
@@ -10659,7 +10632,7 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>단계별 개발 진행 보고서 5부 — 부분 — 진행 기록(docs/log/ 150여 건)·발표 자료는 있지만 개발·테스트·검수·도입·기대효과 단계별 보고서 형식은 없다</t>
+          <t>앱 개발 → 테스트 → 검수 → 완료 → 도입 → 경영개선 기대효과 분석 — 부분 — 개발·테스트·운영 배포까지. 검수(발주기관)·도입·기대효과 분석은 없다(기대효과는 P2-2와 같은 이유로 의도적 제외)</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
@@ -10674,7 +10647,7 @@
       </c>
       <c r="G185" s="9" t="inlineStr">
         <is>
-          <t>산출물4(p.7)</t>
+          <t>과업3(p.3)</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10669,7 @@
       </c>
       <c r="D186" s="9" t="inlineStr">
         <is>
-          <t>앱 개발 → 테스트 → 검수 → 완료 → 도입 → 경영개선 기대효과 분석 — 부분 — 개발·테스트·운영 배포까지. 검수(발주기관)·도입·기대효과 분석은 없다(기대효과는 P2-2와 같은 이유로 의도적 제외)</t>
+          <t>개인정보보호법 제26조(업무위탁) 준수 — 부분 — 처리방침의 위탁 고지(D51)·수탁자 표(security-plan §7)만. 위탁 계약 문서 보관·수탁자 감독 기록은 실데이터 운영 전 조치</t>
         </is>
       </c>
       <c r="E186" s="11" t="inlineStr">
@@ -10711,49 +10684,12 @@
       </c>
       <c r="G186" s="9" t="inlineStr">
         <is>
-          <t>과업3(p.3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="9" t="inlineStr">
-        <is>
-          <t>GAP-05</t>
-        </is>
-      </c>
-      <c r="B187" s="9" t="inlineStr">
-        <is>
-          <t>RFP 공통</t>
-        </is>
-      </c>
-      <c r="C187" s="9" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-      <c r="D187" s="9" t="inlineStr">
-        <is>
-          <t>개인정보보호법 제26조(업무위탁) 준수 — 부분 — 처리방침의 위탁 고지(D51)·수탁자 표(security-plan §7)만. 위탁 계약 문서 보관·수탁자 감독 기록은 실데이터 운영 전 조치</t>
-        </is>
-      </c>
-      <c r="E187" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="F187" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G187" s="9" t="inlineStr">
-        <is>
           <t>보안요건(1-2 #8)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A11:G187"/>
+  <autoFilter ref="A11:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11853,7 +11789,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -11863,7 +11799,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -11878,7 +11814,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>12/17 = 71% / 82%</t>
+          <t>13/17 = 76% / 82%</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11831,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -11905,7 +11841,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -11920,7 +11856,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>56/64 = 88% / 95%</t>
+          <t>57/64 = 89% / 95%</t>
         </is>
       </c>
     </row>
@@ -13890,14 +13826,14 @@
           <t>단계별 개발 진행 보고서 5부</t>
         </is>
       </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>진행 기록·발표 자료만(§2-3)</t>
+          <t>진행보고서 1~5(Word) — 분석·설계 / 실DB 전환·배포 / 기능 구현·RFP / 테스트·검증 / 완성·산출물, 단계마다 목표·결과·결정·검증·문제와 대응·넘긴 것 + 작업 기록 부록. 진행 기록·결정 인덱스에서 생성(scripts/deliverables/progress-reports.js, log/161)</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -24,7 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범위 제외" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요구사항 총괄'!$A$11:$G$185</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RFP 충족 판정'!$A$17:$E$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>도메인 9개 · 기능(API) 103개 · 불변규칙 26개 · RFP 미구현·부분 4건 · 자동 테스트 파일 50개</t>
+          <t>도메인 9개 · 기능(API) 103개 · 불변규칙 26개 · RFP 미구현·부분 3건 · 자동 테스트 파일 52개</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 57/64 = 89% / 95%(구현+조정 / 부분 포함)</t>
+          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 58/64 = 91% / 95%(구현+조정 / 부분 포함)</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3922,17 +3922,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>시스템가용성(1-1 #10)</t>
+          <t>UI 보안(1-2 #7)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>메모리 평균 85% 이하 유지</t>
+          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
+          <t>부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03), 연계 확인 문서(pg-integration-check, log/165 — 카드 정보는 우리 서버를 거치지 않고 승인 API만 부르는 구조, 테스트 키는 계약 없이 발급). 남은 것: 테스트 키로 실제 승인·취소 1회(사용자 PC — 세션은 PG 주소 접속 불가)</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>UI 보안(1-2 #7)</t>
+          <t>과업3(p.3)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인</t>
+          <t>앱 개발 → 테스트 → 검수 → 완료 → 도입 → 경영개선 기대효과 분석</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
+          <t>부분 — 개발·테스트·운영 배포까지. 검수(발주기관)·도입·기대효과 분석은 없다(기대효과는 P2-2와 같은 이유로 의도적 제외)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -3976,17 +3976,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>과업3(p.3)</t>
+          <t>보안요건(1-2 #8)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>앱 개발 → 테스트 → 검수 → 완료 → 도입 → 경영개선 기대효과 분석</t>
+          <t>개인정보보호법 제26조(업무위탁) 준수</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>부분 — 개발·테스트·운영 배포까지. 검수(발주기관)·도입·기대효과 분석은 없다(기대효과는 P2-2와 같은 이유로 의도적 제외)</t>
+          <t>부분 — 처리방침의 위탁 고지(D51)·수탁자 표, 위탁 문서 항목과 서비스별 DPA 맺는 법·연 1회 감독 절차(security-plan §7-1·7-2, log/165). 남은 것: Supabase DPA 서명과 세 서비스 DPA 보관, 첫 감독 기록(실데이터 운영 전, 사용자)</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -3995,56 +3995,29 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>GAP-04</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>보안요건(1-2 #8)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>개인정보보호법 제26조(업무위탁) 준수</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>부분 — 처리방침의 위탁 고지(D51)·수탁자 표(security-plan §7)만. 위탁 계약 문서 보관·수탁자 감독 기록은 실데이터 운영 전 조치</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>API는 있고 화면이 없는 것</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>지금은 없다(로컬 전용 dev-storage 경로 제외). 마지막 항목이던 관리자의 직원 업무일지 열람은 2026-10-14 직원 상세에 붙였다(D51, log/112).</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>설계는 있지만 미구현인 도메인 규칙</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>결제 PaymentGateway 어댑터(ADR-RSV-03) — 실 PG를 붙일 때 필요하다.</t>
         </is>
@@ -4052,8 +4025,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4251,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4296,7 +4269,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>COUNTIF($C$12:$C$187,"기능")</f>
+        <f>COUNTIF($C$12:$C$186,"기능")</f>
         <v/>
       </c>
     </row>
@@ -4307,7 +4280,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>COUNTIFS($C$12:$C$187,"기능",$F$12:$F$187,"있음")</f>
+        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"있음")</f>
         <v/>
       </c>
     </row>
@@ -4318,7 +4291,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIFS($C$12:$C$187,"기능",$F$12:$F$187,"없음")</f>
+        <f>COUNTIFS($C$12:$C$186,"기능",$F$12:$F$186,"없음")</f>
         <v/>
       </c>
     </row>
@@ -4329,7 +4302,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF($C$12:$C$187,"불변규칙")</f>
+        <f>COUNTIF($C$12:$C$186,"불변규칙")</f>
         <v/>
       </c>
     </row>
@@ -4340,7 +4313,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF($C$12:$C$187,"미구현")</f>
+        <f>COUNTIF($C$12:$C$186,"미구현")</f>
         <v/>
       </c>
     </row>
@@ -4645,7 +4618,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>permission-matrix·permission-coverage·permission-admin·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
+          <t>password-change-required·permission-matrix·permission-coverage·permission-admin·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4655,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>permission-matrix·permission-coverage·permission-admin·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
+          <t>password-change-required·permission-matrix·permission-coverage·permission-admin·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4692,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>permission-matrix·permission-coverage·permission-admin·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
+          <t>password-change-required·permission-matrix·permission-coverage·permission-admin·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10531,7 @@
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>메모리 평균 85% 이하 유지 — 부분 — 경보 절차는 작성(aws-lambda/README §6). AWS 콘솔 적용은 사용자 작업 — 아직 없음</t>
+          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인 — 부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03), 연계 확인 문서(pg-integration-check, log/165 — 카드 정보는 우리 서버를 거치지 않고 승인 API만 부르는 구조, 테스트 키는 계약 없이 발급). 남은 것: 테스트 키로 실제 승인·취소 1회(사용자 PC — 세션은 PG 주소 접속 불가)</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
@@ -10573,7 +10546,7 @@
       </c>
       <c r="G183" s="9" t="inlineStr">
         <is>
-          <t>시스템가용성(1-1 #10)</t>
+          <t>UI 보안(1-2 #7)</t>
         </is>
       </c>
     </row>
@@ -10595,7 +10568,7 @@
       </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>결제 시스템의 금융·보안기관 연계 가능 여부 확인 — 부분 — 모의 결제와 결제 어댑터 설계(ADR-RSV-03)만. PG사 연계 요건 확인 문서 없음</t>
+          <t>앱 개발 → 테스트 → 검수 → 완료 → 도입 → 경영개선 기대효과 분석 — 부분 — 개발·테스트·운영 배포까지. 검수(발주기관)·도입·기대효과 분석은 없다(기대효과는 P2-2와 같은 이유로 의도적 제외)</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
@@ -10610,7 +10583,7 @@
       </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>UI 보안(1-2 #7)</t>
+          <t>과업3(p.3)</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10605,7 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>앱 개발 → 테스트 → 검수 → 완료 → 도입 → 경영개선 기대효과 분석 — 부분 — 개발·테스트·운영 배포까지. 검수(발주기관)·도입·기대효과 분석은 없다(기대효과는 P2-2와 같은 이유로 의도적 제외)</t>
+          <t>개인정보보호법 제26조(업무위탁) 준수 — 부분 — 처리방침의 위탁 고지(D51)·수탁자 표, 위탁 문서 항목과 서비스별 DPA 맺는 법·연 1회 감독 절차(security-plan §7-1·7-2, log/165). 남은 것: Supabase DPA 서명과 세 서비스 DPA 보관, 첫 감독 기록(실데이터 운영 전, 사용자)</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
@@ -10647,49 +10620,12 @@
       </c>
       <c r="G185" s="9" t="inlineStr">
         <is>
-          <t>과업3(p.3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="9" t="inlineStr">
-        <is>
-          <t>GAP-04</t>
-        </is>
-      </c>
-      <c r="B186" s="9" t="inlineStr">
-        <is>
-          <t>RFP 공통</t>
-        </is>
-      </c>
-      <c r="C186" s="9" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-      <c r="D186" s="9" t="inlineStr">
-        <is>
-          <t>개인정보보호법 제26조(업무위탁) 준수 — 부분 — 처리방침의 위탁 고지(D51)·수탁자 표(security-plan §7)만. 위탁 계약 문서 보관·수탁자 감독 기록은 실데이터 운영 전 조치</t>
-        </is>
-      </c>
-      <c r="E186" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="F186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G186" s="9" t="inlineStr">
-        <is>
           <t>보안요건(1-2 #8)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A11:G186"/>
+  <autoFilter ref="A11:G185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11224,7 +11160,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1인 개발 구조상 "발주기관/전문가 검증" 주체가 없음 — CI(lint·빌드·jest·문서 검사)와 커밋 전 hook, 도메인 문서 §11 검증현황으로 대체. 개발보안은 행안부 구현단계 보안약점 49개로 점검했다(secure-coding-checklist — 대응 34·부분 4·해당 없음 11, 점검 중 찾은 문서 주소 XSS는 수정, log/139). 의존성 알려진 취약점은 npm audit로 대조해 운영 18 → 4건(도달 불가, D63)·개발 도구 고친 판 없는 2건 수용(D64)</t>
+          <t>1인 개발 구조상 "발주기관/전문가 검증" 주체가 없음 — CI(lint·빌드·jest·문서 검사)와 커밋 전 hook, 도메인 문서 §11 검증현황으로 대체. 개발보안은 행안부 구현단계 보안약점 49개로 점검했다(secure-coding-checklist — 대응 37·부분 1·해당 없음 11 — 2026-10-22 정수 상한·임시 비밀번호·비밀번호 조합 반영, log/164, 점검 중 찾은 문서 주소 XSS는 수정, log/139). 의존성 알려진 취약점은 npm audit로 대조해 운영 18 → 4건(D63) → 메이저 업그레이드로 0건(D65)·개발 도구 고친 판 없는 2건 수용(D64)</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11641,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -11715,22 +11651,22 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/28 = 96% / 100%</t>
+          <t>28/28 = 100% / 100%</t>
         </is>
       </c>
     </row>
@@ -11831,7 +11767,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -11841,7 +11777,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -11856,7 +11792,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>57/64 = 89% / 95%</t>
+          <t>58/64 = 91% / 95%</t>
         </is>
       </c>
     </row>
@@ -12584,14 +12520,14 @@
           <t>메모리 평균 사용률 85% 이하</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>부분</t>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>구현</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>경보 절차만(aws-lambda/README §6), 콘솔 미적용</t>
+          <t>실측 최대 167MB/1,024MB(약 16%) + CloudWatch 경보(REPORT 줄 지표 필터 → 5분 평균 &gt; 870MB, 이메일) 운영 적용(2026-10-22, aws-lambda/README §6, log/169)</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12743,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>행안부 구현단계 보안약점 49개 점검표(secure-coding-checklist — 대응 34·부분 4·해당 없음 11), 남은 조치 4건 표로 관리, 점검 중 찾은 XSS 수정(document-rules). 의존성 취약점 대조(API-2 — 운영 18 → 4건은 도달 불가 D63, 개발 도구 D64)</t>
+          <t>행안부 구현단계 보안약점 49개 점검표(secure-coding-checklist — 대응 37·부분 1·해당 없음 11 — 2026-10-22 정수 상한·임시 비밀번호·비밀번호 조합 반영, log/164), 남은 조치는 계정별 로그인 제한 1건(수용), 점검 중 찾은 XSS 수정(document-rules). 의존성 취약점 대조(API-2 — 운영 18 → 0건 D63·D65, 개발 도구 D64)</t>
         </is>
       </c>
     </row>
@@ -13239,7 +13175,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>결제 어댑터 설계만(ADR-RSV-03)</t>
+          <t>결제 어댑터 설계(ADR-RSV-03) + 연계 확인 문서(pg-integration-check, log/165). 테스트 키 실제 호출 전이라 부분</t>
         </is>
       </c>
     </row>
@@ -13293,7 +13229,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>처리방침 초안의 위탁 고지(D51), 수탁자·업무·위치 표(security-plan §7). 위탁 계약 문서 보관·수탁자 감독 기록은 없음(실데이터 운영 전 조치)</t>
+          <t>처리방침의 위탁 고지(D51), 수탁자 표·위탁 문서 항목·DPA 맺는 법·감독 절차(security-plan §7, log/165). DPA 서명·보관·감독 기록은 실데이터 운영 전(사용자)</t>
         </is>
       </c>
     </row>
@@ -13903,7 +13839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14257,7 +14193,7 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>permission-matrix·permission-coverage·permission-admin·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
+          <t>password-change-required·permission-matrix·permission-coverage·permission-admin·auth-lifecycle·auth-refresh-token·auth-password·hr-authority·contract-termination·branch-isolation·branch-scope-coverage spec</t>
         </is>
       </c>
     </row>
@@ -14851,29 +14787,49 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>ADR-AUTH-08</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>새 비밀번호 영문·숫자 8~72자, 채용 계정은 무작위 임시 비밀번호 + 첫 로그인 변경 강제(mustChangePassword, 그 전엔 403)</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="n"/>
+      <c r="D52" s="14" t="n"/>
+      <c r="E52" s="15" t="n"/>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>구현(log/164)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>미구현·범위 제외(도메인 문서 기준)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="16" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>로그인 잠금, /accounts 범용 API, 비밀번호 재설정·로그인 이력 화면</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A54:F54"/>
+  <mergeCells count="25">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="B49:E49"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B51:E51"/>
     <mergeCell ref="C19:F19"/>
+    <mergeCell ref="A55:F55"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="B45:E45"/>
     <mergeCell ref="C18:F18"/>
@@ -14884,6 +14840,7 @@
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="C14:F14"/>
+    <mergeCell ref="B52:E52"/>
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="B9:F9"/>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>도메인 9개 · 기능(API) 103개 · 불변규칙 26개 · RFP 미구현·부분 3건 · 자동 테스트 파일 52개</t>
+          <t>도메인 9개 · 기능(API) 103개 · 불변규칙 26개 · RFP 미구현·부분 3건 · 자동 테스트 파일 53개</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>구현(API+화면: 관리자 웹·회원 웹)</t>
+          <t>구현(API+화면: 회원 웹)</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>구현(API+화면: 관리자 웹·회원 웹)</t>
+          <t>구현(API+화면: 회원 웹)</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>facility-lifecycle·catalog-flow·contract-termination·branch-isolation spec</t>
+          <t>facility-lifecycle·facility-occupancy·catalog-flow·contract-termination·branch-isolation spec, e2e admin-congestion·member-congestion</t>
         </is>
       </c>
     </row>
@@ -2996,32 +2996,53 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ADR-FAC-05</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>혼잡도 = 진행 중 회차의 예약 인원(조회 때 자동) + 예약 외 현장 인원(관리자 입력). 키오스크 입장 방식은 검토 후 보류</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>구현(2026-10-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>미구현·범위 제외(도메인 문서 기준)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>QR 체크인/아웃, 5분 주기 자동계산, 미체크아웃 자동 마감 — 구현하려면 사용자 승인</t>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>QR 체크인/아웃, 5분 주기 자동계산(스케줄러), 미체크아웃 자동 마감, 키오스크 입장(ADR-FAC-05 보류) — 구현하려면 사용자 승인</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="B31:E31"/>
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B35:E35"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A37:F37"/>
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B19:E19"/>
@@ -9238,7 +9259,7 @@
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>facility-lifecycle·catalog-flow·contract-termination·branch-isolation spec</t>
+          <t>facility-lifecycle·facility-occupancy·catalog-flow·contract-termination·branch-isolation spec, e2e admin-congestion·member-congestion</t>
         </is>
       </c>
     </row>
@@ -9275,7 +9296,7 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>facility-lifecycle·catalog-flow·contract-termination·branch-isolation spec</t>
+          <t>facility-lifecycle·facility-occupancy·catalog-flow·contract-termination·branch-isolation spec, e2e admin-congestion·member-congestion</t>
         </is>
       </c>
     </row>
@@ -10993,12 +11014,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>IoT 계측 장비 없음 → 관리자 수동 입력 + 정원 기준 5단계 자동 판정(입력 즉시 반영). 입력 후 30분이 지나면 관리자·회원 화면에 경고(log/114). 체크인 기반 5분 주기 자동계산은 범위 제외</t>
+          <t>IoT 계측 장비 없음 → 진행 중 강습의 예약 인원(조회 때 자동) + 예약 외 현장 인원(관리자 입력) + 정원 기준 5단계 자동 판정(ADR-FAC-05). 현장 입력 후 30분이 지나면 관리자·회원 화면에 경고(log/114). 입장 기록(키오스크) 기반·5분 주기 자동계산은 보류·범위 제외</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>D10, 혼잡도관리 A-8</t>
+          <t>D10, 혼잡도관리 ADR-FAC-05·A-8</t>
         </is>
       </c>
     </row>
@@ -12473,7 +12494,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>수동 입력 즉시 반영 + 30분 경과 경고(D10, log/114). 자동 계측은 범위 제외</t>
+          <t>강습 예약 인원은 회차 시작과 함께 자동 반영(ADR-FAC-05, facility-occupancy), 예약 외 현장 인원은 수동 입력 즉시 반영 + 30분 경과 경고(D10, log/114). 인원 대부분이 현장 입력이라 조정 유지. 입장 기록 기반은 보류</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/요구사항정의서.xlsx
+++ b/docs/deliverables/요구사항정의서.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 저장소(dev 브랜치) — 도메인 문서·요구사항추적표·실제 API 라우트에서 자동 생성</t>
+          <t>2026-10-24 저장소(dev 브랜치) — 도메인 문서·요구사항추적표·실제 API 라우트에서 자동 생성</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>조항 72개 중 해당 없음 8개를 뺀 충족률 58/64 = 91% / 95%(구현+조정 / 부분 포함)</t>
+          <t>조항 72개 중 구현+조정 58/72 = 81%</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/예약및결제.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
+          <t>원천: docs/domains/예약및결제.md · 기능 명세는 코드 실측(2026-10-24 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/강사프로그램게시.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
+          <t>원천: docs/domains/강사프로그램게시.md · 기능 명세는 코드 실측(2026-10-24 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/혼잡도관리.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
+          <t>원천: docs/domains/혼잡도관리.md · 기능 명세는 코드 실측(2026-10-24 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/자원문서관리.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
+          <t>원천: docs/domains/자원문서관리.md · 기능 명세는 코드 실측(2026-10-24 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>집계 — 충족률은 (구현+조정) / (전체−해당 없음), 뒤 값은 부분까지 포함</t>
+          <t>집계 — 충족률은 (구현+조정) / 조항 수(해당 없음·미구현도 분모에 남긴다)</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>28/28 = 100% / 100%</t>
+          <t>28/29 = 97%</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>17/19 = 89% / 100%</t>
+          <t>17/25 = 68%</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>13/17 = 76% / 82%</t>
+          <t>13/18 = 72%</t>
         </is>
       </c>
     </row>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>58/64 = 91% / 95%</t>
+          <t>58/72 = 81%</t>
         </is>
       </c>
     </row>
@@ -11873,7 +11873,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>발주기관·계약·대면 행위처럼 대상이 없다 — 분모에서 뺀다</t>
+          <t>발주기관·계약·대면 행위처럼 대상이 없다 — 분모에는 남긴다</t>
         </is>
       </c>
     </row>
@@ -13881,7 +13881,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/권한관리.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
+          <t>원천: docs/domains/권한관리.md · 기능 명세는 코드 실측(2026-10-24 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14901,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/인사정보관리.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
+          <t>원천: docs/domains/인사정보관리.md · 기능 명세는 코드 실측(2026-10-24 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -15956,7 +15956,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/근태관리.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
+          <t>원천: docs/domains/근태관리.md · 기능 명세는 코드 실측(2026-10-24 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -16886,7 +16886,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/게시판.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
+          <t>원천: docs/domains/게시판.md · 기능 명세는 코드 실측(2026-10-24 저장소 기준)</t>
         </is>
       </c>
     </row>
@@ -17658,7 +17658,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원천: docs/domains/회원관리.md · 기능 명세는 코드 실측(2026-10-22 저장소 기준)</t>
+          <t>원천: docs/domains/회원관리.md · 기능 명세는 코드 실측(2026-10-24 저장소 기준)</t>
         </is>
       </c>
     </row>
